--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,16 +456,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2009-03-11</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -473,22 +473,22 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2009年3月11日，苏州众勤会计师事务所有限公司出具苏众勤（2009）第2047号《验资报告》，截至2009年3月10日，赛分有限（筹）已收到股东以货币资金缴付的注册资本（实收资本）合计4,000,000元。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2009-03-11</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>沈建林</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -496,22 +496,22 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2009年3月11日，苏州众勤会计师事务所有限公司出具苏众勤（2009）第2047号《验资报告》，截至2009年3月10日，赛分有限（筹）已收到股东以货币资金缴付的注册资本（实收资本）合计4,000,000元。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2009-03-11</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>潘鼎</t>
+          <t>唐斌</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -519,22 +519,22 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2009年3月11日，苏州众勤会计师事务所有限公司出具苏众勤（2009）第2047号《验资报告》，截至2009年3月10日，赛分有限（筹）已收到股东以货币资金缴付的注册资本（实收资本）合计4,000,000元。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>张敏</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -542,22 +542,22 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2010年6月17日，苏州建信会计师事务所有限公司出具建信内验（2010）字第153号《验资报告》，截至2010年6月17日，赛分有限已收到黄学英第二期缴纳的注册资本（实收资本）合计1,000,000元整，全部以货币出资。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2011-04-19</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>源峰磐赛</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -565,22 +565,22 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2011年4月19日，苏州建信会计师事务所有限公司出具建信内验（2011）字第065号《验资报告》，截至2011年4月18日，赛分有限已收到黄学英、沈建林、潘鼎第三期缴纳的注册资本（实收资本）合计5,000,000元整，全部以货币出资。至此，赛分有限注册资本实缴完毕。</t>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2011-04-19</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>沈建林</t>
+          <t>珠海峦恒</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -588,22 +588,22 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2011年4月19日，苏州建信会计师事务所有限公司出具建信内验（2011）字第065号《验资报告》，截至2011年4月18日，赛分有限已收到黄学英、沈建林、潘鼎第三期缴纳的注册资本（实收资本）合计5,000,000元整，全部以货币出资。至此，赛分有限注册资本实缴完毕。</t>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2011-04-19</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>潘鼎</t>
+          <t>高瓴祈睿</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -611,22 +611,22 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2011年4月19日，苏州建信会计师事务所有限公司出具建信内验（2011）字第065号《验资报告》，截至2011年4月18日，赛分有限已收到黄学英、沈建林、潘鼎第三期缴纳的注册资本（实收资本）合计5,000,000元整，全部以货币出资。至此，赛分有限注册资本实缴完毕。</t>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>国药中生</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -634,22 +634,22 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2021年2月22日，赛分有限召开股东会并作出决议，同意黄学英将其持有的赛分有限58.2243万元注册资本分别转让给复星惟盈、朱勤华、唐斌及张敏。</t>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>朱勤华</t>
+          <t>圣成投资</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -657,22 +657,22 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2021年2月22日，赛分有限召开股东会并作出决议，同意黄学英将其持有的赛分有限58.2243万元注册资本分别转让给复星惟盈、朱勤华、唐斌及张敏。</t>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>唐斌</t>
+          <t>国药二期</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -680,22 +680,22 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2021年2月22日，赛分有限召开股东会并作出决议，同意黄学英将其持有的赛分有限58.2243万元注册资本分别转让给复星惟盈、朱勤华、唐斌及张敏。</t>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>张敏</t>
+          <t>圣祁投资</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -703,7 +703,101 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2021年2月22日，赛分有限召开股东会并作出决议，同意黄学英将其持有的赛分有限58.2243万元注册资本分别转让给复星惟盈、朱勤华、唐斌及张敏。</t>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>59</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>59</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>60</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2021-12-06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2021年11月22日，赛分科技召开 2021年第二次临时股东大会，决议同意赛分科技增发股份 117,886 股，新增股份由新增股东聚贝投资以人民币 1,500 万元认购。</t>
         </is>
       </c>
     </row>
@@ -718,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,12 +890,14 @@
           <t>黄学英</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1035</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>报告期初，公司注册资本2,408.00万元，其股权结构如下：</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
@@ -825,15 +921,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>沈建林</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>322</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>报告期初，公司注册资本2,408.00万元，其股权结构如下：</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
@@ -857,15 +955,17 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>潘鼎</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>220</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>报告期初，公司注册资本2,408.00万元，其股权结构如下：</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
@@ -889,15 +989,17 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>194.5</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>报告期初，公司注册资本2,408.00万元，其股权结构如下：</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
@@ -921,15 +1023,17 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>132.5</v>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>报告期初，公司注册资本2,408.00万元，其股权结构如下：</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
@@ -953,15 +1057,17 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>101.3</v>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>报告期初，公司注册资本2,408.00万元，其股权结构如下：</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
@@ -985,213 +1091,227 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>87</v>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>报告期初，公司注册资本2,408.00万元，其股权结构如下：</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2021年8月整体变更后股权结构</t>
+          <t>报告期初公司股权结构</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2750.6769</v>
+        <v>2408</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>52.5</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2021年8月25日，容诚会计师事务所（特殊普通合伙）对本次整体变更进行了验资，并出具容诚验字[2021]210Z0020号《验资报告》。经审验，截至2021年8月25日，赛分科技各发起人以其拥有的赛分有限截至2021年5月31日经审计的账面净资产295,800,700.26元（评估值为330,045,075.98元）折股投入，其中27,506,769.00元折合为赛分科技的股本，股本总额27,506,769股，每股面值1元，净资产折合股本后的余额计入资本公积。</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2021年8月整体变更后股权结构</t>
+          <t>报告期初公司股权结构</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2750.6769</v>
+        <v>2408</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>沈建林</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>36</v>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2021年8月25日，容诚会计师事务所（特殊普通合伙）对本次整体变更进行了验资，并出具容诚验字[2021]210Z0020号《验资报告》。经审验，截至2021年8月25日，赛分科技各发起人以其拥有的赛分有限截至2021年5月31日经审计的账面净资产295,800,700.26元（评估值为330,045,075.98元）折股投入，其中27,506,769.00元折合为赛分科技的股本，股本总额27,506,769股，每股面值1元，净资产折合股本后的余额计入资本公积。</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2021年8月整体变更后股权结构</t>
+          <t>报告期初公司股权结构</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2750.6769</v>
+        <v>2408</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>潘鼎</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2021年8月25日，容诚会计师事务所（特殊普通合伙）对本次整体变更进行了验资，并出具容诚验字[2021]210Z0020号《验资报告》。经审验，截至2021年8月25日，赛分科技各发起人以其拥有的赛分有限截至2021年5月31日经审计的账面净资产295,800,700.26元（评估值为330,045,075.98元）折股投入，其中27,506,769.00元折合为赛分科技的股本，股本总额27,506,769股，每股面值1元，净资产折合股本后的余额计入资本公积。</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2021年8月整体变更后股权结构</t>
+          <t>报告期初公司股权结构</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2750.6769</v>
+        <v>2408</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>72</v>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2021年8月25日，容诚会计师事务所（特殊普通合伙）对本次整体变更进行了验资，并出具容诚验字[2021]210Z0020号《验资报告》。经审验，截至2021年8月25日，赛分科技各发起人以其拥有的赛分有限截至2021年5月31日经审计的账面净资产295,800,700.26元（评估值为330,045,075.98元）折股投入，其中27,506,769.00元折合为赛分科技的股本，股本总额27,506,769股，每股面值1元，净资产折合股本后的余额计入资本公积。</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2021年8月整体变更后股权结构</t>
+          <t>报告期初公司股权结构</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2750.6769</v>
+        <v>2408</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>72</v>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2021年8月25日，容诚会计师事务所（特殊普通合伙）对本次整体变更进行了验资，并出具容诚验字[2021]210Z0020号《验资报告》。经审验，截至2021年8月25日，赛分科技各发起人以其拥有的赛分有限截至2021年5月31日经审计的账面净资产295,800,700.26元（评估值为330,045,075.98元）折股投入，其中27,506,769.00元折合为赛分科技的股本，股本总额27,506,769股，每股面值1元，净资产折合股本后的余额计入资本公积。</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2021年8月整体变更后股权结构</t>
+          <t>报告期初公司股权结构</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2750.6769</v>
+        <v>2408</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>74</v>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2021年8月25日，容诚会计师事务所（特殊普通合伙）对本次整体变更进行了验资，并出具容诚验字[2021]210Z0020号《验资报告》。经审验，截至2021年8月25日，赛分科技各发起人以其拥有的赛分有限截至2021年5月31日经审计的账面净资产295,800,700.26元（评估值为330,045,075.98元）折股投入，其中27,506,769.00元折合为赛分科技的股本，股本总额27,506,769股，每股面值1元，净资产折合股本后的余额计入资本公积。</t>
+          <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1200,7 +1320,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2021年8月整体变更后股权结构</t>
+          <t>2021年4月第一次增资后股权结构</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1209,15 +1329,4743 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>976.7757</v>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2021年8月25日，容诚会计师事务所（特殊普通合伙）对本次整体变更进行了验资，并出具容诚验字[2021]210Z0020号《验资报告》。经审验，截至2021年8月25日，赛分科技各发起人以其拥有的赛分有限截至2021年5月31日经审计的账面净资产295,800,700.26元（评估值为330,045,075.98元）折股投入，其中27,506,769.00元折合为赛分科技的股本，股本总额27,506,769股，每股面值1元，净资产折合股本后的余额计入资本公积。</t>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>57</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>322</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>57</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>220</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>57</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>57</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>57</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>57</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>57</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>87</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>57</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>80</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>57</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>74</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>57</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>72</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>57</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>72</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>57</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>57</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>36</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>57</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>57</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>57</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>57</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2021年4月第一次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>58</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>58</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>322</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>58</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>242</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>58</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>58</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>58</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>58</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>58</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>87</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>58</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>80</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>58</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>74</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>58</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>72</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>58</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>72</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>58</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>58</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>36</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>58</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>58</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>58</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>58</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2021年8月第二次股权转让后股权结构</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>本次股权转让后，赛分有限的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>52</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>322</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>242</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>87</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>52</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>80</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>74</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>52</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>72</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>52</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>72</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>52</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>52</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>36</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>52</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>52</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>20</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>52</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>20</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>52</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2021年9月整体变更为股份公司后股权结构</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2750.6769</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>59</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>59</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>322</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>59</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>242</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>59</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>59</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>59</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>59</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>59</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>87</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>59</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>80</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>59</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>74</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>59</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>72</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>59</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>72</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>59</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>59</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>36</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>59</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>59</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>20</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>59</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>20</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>59</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>59</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>100</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>59</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>80</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>59</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>60</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>59</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>50</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>59</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>40</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>59</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>59</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>20</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>59</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>20</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>59</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>20</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>59</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2021年11月第二次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>61</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>61</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>322</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>61</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>242</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>61</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>61</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>61</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>61</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>61</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>87</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>61</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>80</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>61</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>74</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>61</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>72</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>61</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>72</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>61</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>61</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>36</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>61</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>61</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>20</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>61</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>20</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>61</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>61</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>100</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>61</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>80</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>61</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>60</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>61</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>50</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>61</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>40</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>61</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>30</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>61</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>20</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>61</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>20</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>61</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>20</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>61</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>61</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>t5</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2021年12月第三次增资后股权结构</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>3186.8556</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>本次增资完成后，赛分科技的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>63</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>9236.4177</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>63</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>3220</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>63</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>3102</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>63</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>2960</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>63</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>2875</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>63</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>63</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1542</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>63</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1322</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>63</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>63</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1125</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>63</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>63</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>63</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>798</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>63</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>547</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>63</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>140</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>63</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>304</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>63</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>304</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>63</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>407</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>63</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1520</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>63</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>63</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>912</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>63</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>760</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>63</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>608</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>63</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>456</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>63</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>304</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>63</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>304</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>63</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>304</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>63</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>370.8394</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>63</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>179</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -468,8 +468,12 @@
           <t>国寿疌泉</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13500</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
@@ -488,11 +492,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E3" t="n">
+        <v>13500</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -511,11 +519,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E4" t="n">
+        <v>13500</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
@@ -534,11 +546,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13500</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
@@ -548,256 +564,298 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13500</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13500</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>高瓴祈睿</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13500</v>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13500</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13500</v>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13500</v>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13500</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13500</v>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E14" t="n">
+        <v>13500</v>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13500</v>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2021 年 10 月 28 日，赛分科技召开 2021 年第一次临时股东大会，决议同意赛分科技增发股份 4,243,901 股，新增股份由新增股东源峰磐赛、珠海峦恒、高瓴祈睿、国药中生、圣成投资、国药二期、圣祁投资、夏尔巴二期、甘李药业、吴征涛认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2021-12-06</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>聚贝投资</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>250.0615</v>
+      </c>
       <c r="E16" t="n">
-        <v>1500</v>
+        <v>13500</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2021年11月22日，赛分科技召开 2021年第二次临时股东大会，决议同意赛分科技增发股份 117,886 股，新增股份由新增股东聚贝投资以人民币 1,500 万元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6127,6 +6127,1122 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>59</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>803.1668</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="n">
+        <v>25.2961</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东黄学英持有8031668股，持股比例25.2961%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>59</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>280</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="n">
+        <v>8.8187</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东周金清持有2800000股，持股比例8.8187%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>59</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>270</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="n">
+        <v>8.5038</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东高新同华持有2700000股，持股比例8.5038%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>59</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="n">
+        <v>8.1069</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东陆民持有2574000股，持股比例8.1069%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>59</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="n">
+        <v>7.8758</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东国寿疌泉持有2500615股，持股比例7.8758%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>59</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>175.1887</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="n">
+        <v>5.5176</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东华泰大健康一号持有1751887股，持股比例5.5176%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>59</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>157.1815</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="n">
+        <v>4.9505</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东源峰磐赛持有1571815股，持股比例4.9505%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>59</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="n">
+        <v>4.2251</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东苏州贤达持有1341500股，持股比例4.2251%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>59</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>126.3621</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="n">
+        <v>3.9798</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东复星惟盈持有1263621股，持股比例3.9798%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>59</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>114.9389</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东苏州博达持有1149389股，持股比例3.62%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>59</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="n">
+        <v>2.1883</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东苏州杰贤持有694800股，持股比例2.1883%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>59</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>潘鼎</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="n">
+        <v>1.9905</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东潘鼎持有632000股，持股比例1.9905%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>59</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>62.8726</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="n">
+        <v>1.9802</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东珠海峦恒持有628726股，持股比例1.9802%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>59</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>62.8726</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="n">
+        <v>1.9802</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东高瓴祈睿持有628726股，持股比例1.9802%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>59</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="n">
+        <v>1.4929</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东海佳同康持有474000股，持股比例1.4929%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>59</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>46.1846</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="n">
+        <v>1.4546</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东国药中生持有461846股，持股比例1.4546%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>59</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>40</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="n">
+        <v>1.2598</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东苏州敦行持有400000股，持股比例1.2598%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>59</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>39.2954</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="n">
+        <v>1.2376</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东夏尔巴二期持有392954股，持股比例1.2376%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>59</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>陈志华</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东陈志华持有300400股，持股比例0.9461%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>59</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>耿卫东</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>30</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东耿卫东持有300000股，持股比例0.9449%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>59</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>23.5772</v>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="n">
+        <v>0.7426</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东甘李药业持有235772股，持股比例0.7426%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>59</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>20</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="n">
+        <v>0.6299</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东骏耀投资持有200000股，持股比例0.6299%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>59</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东朱勤华持有194081股，持股比例0.6113%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>59</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>15.7182</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="n">
+        <v>0.4951</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东吴征涛持有157182股，持股比例0.4951%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>59</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>15.5625</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东国药二期持有155625股，持股比例0.4901%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>59</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>12.0034</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东华泰大健康二号持有120034股，持股比例0.3781%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>59</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>3.0041</v>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东唐斌持有30041股，持股比例0.0946%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>59</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>2.8079</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东道兴投资持有28079股，持股比例0.0884%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>59</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>2.0654</v>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东张敏持有20654股，持股比例0.0651%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>59</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣成投资持有9699股，持股比例0.0305%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>59</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +475,6 @@
       <c r="E2" t="n">
         <v>13500</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -501,7 +501,6 @@
       <c r="E3" t="n">
         <v>13500</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -528,7 +527,6 @@
       <c r="E4" t="n">
         <v>13500</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -555,7 +553,6 @@
       <c r="E5" t="n">
         <v>13500</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -582,7 +579,6 @@
       <c r="E6" t="n">
         <v>13500</v>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -609,7 +605,6 @@
       <c r="E7" t="n">
         <v>13500</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -636,7 +631,6 @@
       <c r="E8" t="n">
         <v>13500</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -663,7 +657,6 @@
       <c r="E9" t="n">
         <v>13500</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -690,7 +683,6 @@
       <c r="E10" t="n">
         <v>13500</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -717,7 +709,6 @@
       <c r="E11" t="n">
         <v>13500</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -744,7 +735,6 @@
       <c r="E12" t="n">
         <v>13500</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -771,7 +761,6 @@
       <c r="E13" t="n">
         <v>13500</v>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -798,7 +787,6 @@
       <c r="E14" t="n">
         <v>13500</v>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -825,7 +813,6 @@
       <c r="E15" t="n">
         <v>13500</v>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -852,7 +839,6 @@
       <c r="E16" t="n">
         <v>13500</v>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -942,7 +928,6 @@
       <c r="D2" t="n">
         <v>2408</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -951,8 +936,6 @@
       <c r="G2" t="n">
         <v>1035</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -976,7 +959,6 @@
       <c r="D3" t="n">
         <v>2408</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -985,8 +967,6 @@
       <c r="G3" t="n">
         <v>322</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1010,7 +990,6 @@
       <c r="D4" t="n">
         <v>2408</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1019,8 +998,6 @@
       <c r="G4" t="n">
         <v>220</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1044,7 +1021,6 @@
       <c r="D5" t="n">
         <v>2408</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1053,8 +1029,6 @@
       <c r="G5" t="n">
         <v>194.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1078,7 +1052,6 @@
       <c r="D6" t="n">
         <v>2408</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1087,8 +1060,6 @@
       <c r="G6" t="n">
         <v>132.5</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1112,7 +1083,6 @@
       <c r="D7" t="n">
         <v>2408</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1121,8 +1091,6 @@
       <c r="G7" t="n">
         <v>101.3</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1146,7 +1114,6 @@
       <c r="D8" t="n">
         <v>2408</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1155,8 +1122,6 @@
       <c r="G8" t="n">
         <v>87</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1180,7 +1145,6 @@
       <c r="D9" t="n">
         <v>2408</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1189,8 +1153,6 @@
       <c r="G9" t="n">
         <v>52.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1214,7 +1176,6 @@
       <c r="D10" t="n">
         <v>2408</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1223,8 +1184,6 @@
       <c r="G10" t="n">
         <v>36</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1248,7 +1207,6 @@
       <c r="D11" t="n">
         <v>2408</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1257,8 +1215,6 @@
       <c r="G11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1282,7 +1238,6 @@
       <c r="D12" t="n">
         <v>2408</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1291,8 +1246,6 @@
       <c r="G12" t="n">
         <v>72</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1316,7 +1269,6 @@
       <c r="D13" t="n">
         <v>2408</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1325,8 +1277,6 @@
       <c r="G13" t="n">
         <v>72</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1350,7 +1300,6 @@
       <c r="D14" t="n">
         <v>2408</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1359,8 +1308,6 @@
       <c r="G14" t="n">
         <v>74</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1384,7 +1331,6 @@
       <c r="D15" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1393,8 +1339,6 @@
       <c r="G15" t="n">
         <v>976.7757</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1418,7 +1362,6 @@
       <c r="D16" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1427,8 +1370,6 @@
       <c r="G16" t="n">
         <v>322</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1452,7 +1393,6 @@
       <c r="D17" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1461,8 +1401,6 @@
       <c r="G17" t="n">
         <v>220</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1486,7 +1424,6 @@
       <c r="D18" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1495,8 +1432,6 @@
       <c r="G18" t="n">
         <v>194.5</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1520,7 +1455,6 @@
       <c r="D19" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -1529,8 +1463,6 @@
       <c r="G19" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1554,7 +1486,6 @@
       <c r="D20" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1563,8 +1494,6 @@
       <c r="G20" t="n">
         <v>132.5</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1588,7 +1517,6 @@
       <c r="D21" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1597,8 +1525,6 @@
       <c r="G21" t="n">
         <v>101.3</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1622,7 +1548,6 @@
       <c r="D22" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1631,8 +1556,6 @@
       <c r="G22" t="n">
         <v>87</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1656,7 +1579,6 @@
       <c r="D23" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -1665,8 +1587,6 @@
       <c r="G23" t="n">
         <v>80</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1690,7 +1610,6 @@
       <c r="D24" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1699,8 +1618,6 @@
       <c r="G24" t="n">
         <v>74</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1724,7 +1641,6 @@
       <c r="D25" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1733,8 +1649,6 @@
       <c r="G25" t="n">
         <v>72</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1758,7 +1672,6 @@
       <c r="D26" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1767,8 +1680,6 @@
       <c r="G26" t="n">
         <v>72</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1792,7 +1703,6 @@
       <c r="D27" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1801,8 +1711,6 @@
       <c r="G27" t="n">
         <v>52.5</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1826,7 +1734,6 @@
       <c r="D28" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1835,8 +1742,6 @@
       <c r="G28" t="n">
         <v>36</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1860,7 +1765,6 @@
       <c r="D29" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1869,8 +1773,6 @@
       <c r="G29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1894,7 +1796,6 @@
       <c r="D30" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -1903,8 +1804,6 @@
       <c r="G30" t="n">
         <v>20</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1928,7 +1827,6 @@
       <c r="D31" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -1937,8 +1835,6 @@
       <c r="G31" t="n">
         <v>20</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1962,7 +1858,6 @@
       <c r="D32" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -1971,8 +1866,6 @@
       <c r="G32" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1996,7 +1889,6 @@
       <c r="D33" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2005,8 +1897,6 @@
       <c r="G33" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2030,7 +1920,6 @@
       <c r="D34" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2039,8 +1928,6 @@
       <c r="G34" t="n">
         <v>322</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2064,7 +1951,6 @@
       <c r="D35" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2073,8 +1959,6 @@
       <c r="G35" t="n">
         <v>242</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2098,7 +1982,6 @@
       <c r="D36" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2107,8 +1990,6 @@
       <c r="G36" t="n">
         <v>194.5</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2132,7 +2013,6 @@
       <c r="D37" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2141,8 +2021,6 @@
       <c r="G37" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2166,7 +2044,6 @@
       <c r="D38" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2175,8 +2052,6 @@
       <c r="G38" t="n">
         <v>132.5</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2200,7 +2075,6 @@
       <c r="D39" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2209,8 +2083,6 @@
       <c r="G39" t="n">
         <v>101.3</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2234,7 +2106,6 @@
       <c r="D40" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2243,8 +2114,6 @@
       <c r="G40" t="n">
         <v>87</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2268,7 +2137,6 @@
       <c r="D41" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2277,8 +2145,6 @@
       <c r="G41" t="n">
         <v>80</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2302,7 +2168,6 @@
       <c r="D42" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2311,8 +2176,6 @@
       <c r="G42" t="n">
         <v>74</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2336,7 +2199,6 @@
       <c r="D43" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2345,8 +2207,6 @@
       <c r="G43" t="n">
         <v>72</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2370,7 +2230,6 @@
       <c r="D44" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2379,8 +2238,6 @@
       <c r="G44" t="n">
         <v>72</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2404,7 +2261,6 @@
       <c r="D45" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2413,8 +2269,6 @@
       <c r="G45" t="n">
         <v>52.5</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2438,7 +2292,6 @@
       <c r="D46" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2447,8 +2300,6 @@
       <c r="G46" t="n">
         <v>36</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2472,7 +2323,6 @@
       <c r="D47" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2481,8 +2331,6 @@
       <c r="G47" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2506,7 +2354,6 @@
       <c r="D48" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2515,8 +2362,6 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2540,7 +2385,6 @@
       <c r="D49" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2549,8 +2393,6 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2574,7 +2416,6 @@
       <c r="D50" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2583,8 +2424,6 @@
       <c r="G50" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2608,7 +2447,6 @@
       <c r="D51" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2617,8 +2455,6 @@
       <c r="G51" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2642,7 +2478,6 @@
       <c r="D52" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2651,8 +2486,6 @@
       <c r="G52" t="n">
         <v>322</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2676,7 +2509,6 @@
       <c r="D53" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2685,8 +2517,6 @@
       <c r="G53" t="n">
         <v>242</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2710,7 +2540,6 @@
       <c r="D54" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2719,8 +2548,6 @@
       <c r="G54" t="n">
         <v>194.5</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2744,7 +2571,6 @@
       <c r="D55" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2753,8 +2579,6 @@
       <c r="G55" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2778,7 +2602,6 @@
       <c r="D56" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2787,8 +2610,6 @@
       <c r="G56" t="n">
         <v>132.5</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2812,7 +2633,6 @@
       <c r="D57" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2821,8 +2641,6 @@
       <c r="G57" t="n">
         <v>101.3</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2846,7 +2664,6 @@
       <c r="D58" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2855,8 +2672,6 @@
       <c r="G58" t="n">
         <v>87</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2880,7 +2695,6 @@
       <c r="D59" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2889,8 +2703,6 @@
       <c r="G59" t="n">
         <v>80</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2914,7 +2726,6 @@
       <c r="D60" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2923,8 +2734,6 @@
       <c r="G60" t="n">
         <v>74</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2948,7 +2757,6 @@
       <c r="D61" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2957,8 +2765,6 @@
       <c r="G61" t="n">
         <v>72</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2982,7 +2788,6 @@
       <c r="D62" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2991,8 +2796,6 @@
       <c r="G62" t="n">
         <v>72</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3016,7 +2819,6 @@
       <c r="D63" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3025,8 +2827,6 @@
       <c r="G63" t="n">
         <v>52.5</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3050,7 +2850,6 @@
       <c r="D64" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3059,8 +2858,6 @@
       <c r="G64" t="n">
         <v>36</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3084,7 +2881,6 @@
       <c r="D65" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3093,8 +2889,6 @@
       <c r="G65" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3118,7 +2912,6 @@
       <c r="D66" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3127,8 +2920,6 @@
       <c r="G66" t="n">
         <v>20</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3152,7 +2943,6 @@
       <c r="D67" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3161,8 +2951,6 @@
       <c r="G67" t="n">
         <v>20</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3186,7 +2974,6 @@
       <c r="D68" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3195,8 +2982,6 @@
       <c r="G68" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3220,7 +3005,6 @@
       <c r="D69" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3229,8 +3013,6 @@
       <c r="G69" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3254,7 +3036,6 @@
       <c r="D70" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3263,8 +3044,6 @@
       <c r="G70" t="n">
         <v>322</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3288,7 +3067,6 @@
       <c r="D71" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3297,8 +3075,6 @@
       <c r="G71" t="n">
         <v>242</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3322,7 +3098,6 @@
       <c r="D72" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3331,8 +3106,6 @@
       <c r="G72" t="n">
         <v>194.5</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3356,7 +3129,6 @@
       <c r="D73" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -3365,8 +3137,6 @@
       <c r="G73" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3390,7 +3160,6 @@
       <c r="D74" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -3399,8 +3168,6 @@
       <c r="G74" t="n">
         <v>132.5</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3424,7 +3191,6 @@
       <c r="D75" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -3433,8 +3199,6 @@
       <c r="G75" t="n">
         <v>101.3</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3458,7 +3222,6 @@
       <c r="D76" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -3467,8 +3230,6 @@
       <c r="G76" t="n">
         <v>87</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3492,7 +3253,6 @@
       <c r="D77" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -3501,8 +3261,6 @@
       <c r="G77" t="n">
         <v>80</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3526,7 +3284,6 @@
       <c r="D78" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -3535,8 +3292,6 @@
       <c r="G78" t="n">
         <v>74</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3560,7 +3315,6 @@
       <c r="D79" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -3569,8 +3323,6 @@
       <c r="G79" t="n">
         <v>72</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3594,7 +3346,6 @@
       <c r="D80" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -3603,8 +3354,6 @@
       <c r="G80" t="n">
         <v>72</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3628,7 +3377,6 @@
       <c r="D81" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3637,8 +3385,6 @@
       <c r="G81" t="n">
         <v>52.5</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3662,7 +3408,6 @@
       <c r="D82" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3671,8 +3416,6 @@
       <c r="G82" t="n">
         <v>36</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3696,7 +3439,6 @@
       <c r="D83" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3705,8 +3447,6 @@
       <c r="G83" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3730,7 +3470,6 @@
       <c r="D84" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3739,8 +3478,6 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3764,7 +3501,6 @@
       <c r="D85" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3773,8 +3509,6 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3798,7 +3532,6 @@
       <c r="D86" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3807,8 +3540,6 @@
       <c r="G86" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3832,7 +3563,6 @@
       <c r="D87" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -3841,8 +3571,6 @@
       <c r="G87" t="n">
         <v>100</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3866,7 +3594,6 @@
       <c r="D88" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -3875,8 +3602,6 @@
       <c r="G88" t="n">
         <v>80</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3900,7 +3625,6 @@
       <c r="D89" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -3909,8 +3633,6 @@
       <c r="G89" t="n">
         <v>60</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3934,7 +3656,6 @@
       <c r="D90" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -3943,8 +3664,6 @@
       <c r="G90" t="n">
         <v>50</v>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3968,7 +3687,6 @@
       <c r="D91" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -3977,8 +3695,6 @@
       <c r="G91" t="n">
         <v>40</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4002,7 +3718,6 @@
       <c r="D92" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4011,8 +3726,6 @@
       <c r="G92" t="n">
         <v>30</v>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4036,7 +3749,6 @@
       <c r="D93" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4045,8 +3757,6 @@
       <c r="G93" t="n">
         <v>20</v>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4070,7 +3780,6 @@
       <c r="D94" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -4079,8 +3788,6 @@
       <c r="G94" t="n">
         <v>20</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4104,7 +3811,6 @@
       <c r="D95" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -4113,8 +3819,6 @@
       <c r="G95" t="n">
         <v>20</v>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4138,7 +3842,6 @@
       <c r="D96" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -4147,8 +3850,6 @@
       <c r="G96" t="n">
         <v>24.3901</v>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4172,7 +3873,6 @@
       <c r="D97" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -4181,8 +3881,6 @@
       <c r="G97" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4206,7 +3904,6 @@
       <c r="D98" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -4215,8 +3912,6 @@
       <c r="G98" t="n">
         <v>322</v>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4240,7 +3935,6 @@
       <c r="D99" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -4249,8 +3943,6 @@
       <c r="G99" t="n">
         <v>242</v>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4274,7 +3966,6 @@
       <c r="D100" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -4283,8 +3974,6 @@
       <c r="G100" t="n">
         <v>194.5</v>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4308,7 +3997,6 @@
       <c r="D101" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4317,8 +4005,6 @@
       <c r="G101" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4342,7 +4028,6 @@
       <c r="D102" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4351,8 +4036,6 @@
       <c r="G102" t="n">
         <v>132.5</v>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4376,7 +4059,6 @@
       <c r="D103" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4385,8 +4067,6 @@
       <c r="G103" t="n">
         <v>101.3</v>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4410,7 +4090,6 @@
       <c r="D104" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4419,8 +4098,6 @@
       <c r="G104" t="n">
         <v>87</v>
       </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4444,7 +4121,6 @@
       <c r="D105" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -4453,8 +4129,6 @@
       <c r="G105" t="n">
         <v>80</v>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4478,7 +4152,6 @@
       <c r="D106" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -4487,8 +4160,6 @@
       <c r="G106" t="n">
         <v>74</v>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4512,7 +4183,6 @@
       <c r="D107" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -4521,8 +4191,6 @@
       <c r="G107" t="n">
         <v>72</v>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4546,7 +4214,6 @@
       <c r="D108" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -4555,8 +4222,6 @@
       <c r="G108" t="n">
         <v>72</v>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4580,7 +4245,6 @@
       <c r="D109" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -4589,8 +4253,6 @@
       <c r="G109" t="n">
         <v>52.5</v>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4614,7 +4276,6 @@
       <c r="D110" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -4623,8 +4284,6 @@
       <c r="G110" t="n">
         <v>36</v>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4648,7 +4307,6 @@
       <c r="D111" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -4657,8 +4315,6 @@
       <c r="G111" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4682,7 +4338,6 @@
       <c r="D112" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -4691,8 +4346,6 @@
       <c r="G112" t="n">
         <v>20</v>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4716,7 +4369,6 @@
       <c r="D113" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -4725,8 +4377,6 @@
       <c r="G113" t="n">
         <v>20</v>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4750,7 +4400,6 @@
       <c r="D114" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -4759,8 +4408,6 @@
       <c r="G114" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4784,7 +4431,6 @@
       <c r="D115" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -4793,8 +4439,6 @@
       <c r="G115" t="n">
         <v>100</v>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4818,7 +4462,6 @@
       <c r="D116" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -4827,8 +4470,6 @@
       <c r="G116" t="n">
         <v>80</v>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4852,7 +4493,6 @@
       <c r="D117" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -4861,8 +4501,6 @@
       <c r="G117" t="n">
         <v>60</v>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4886,7 +4524,6 @@
       <c r="D118" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -4895,8 +4532,6 @@
       <c r="G118" t="n">
         <v>50</v>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4920,7 +4555,6 @@
       <c r="D119" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -4929,8 +4563,6 @@
       <c r="G119" t="n">
         <v>40</v>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4954,7 +4586,6 @@
       <c r="D120" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4963,8 +4594,6 @@
       <c r="G120" t="n">
         <v>30</v>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4988,7 +4617,6 @@
       <c r="D121" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4997,8 +4625,6 @@
       <c r="G121" t="n">
         <v>20</v>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5022,7 +4648,6 @@
       <c r="D122" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -5031,8 +4656,6 @@
       <c r="G122" t="n">
         <v>20</v>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5056,7 +4679,6 @@
       <c r="D123" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -5065,8 +4687,6 @@
       <c r="G123" t="n">
         <v>20</v>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5090,7 +4710,6 @@
       <c r="D124" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -5099,8 +4718,6 @@
       <c r="G124" t="n">
         <v>24.3901</v>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5124,7 +4741,6 @@
       <c r="D125" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -5133,8 +4749,6 @@
       <c r="G125" t="n">
         <v>11.7886</v>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5158,7 +4772,6 @@
       <c r="D126" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -5167,8 +4780,6 @@
       <c r="G126" t="n">
         <v>9236.4177</v>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5192,7 +4803,6 @@
       <c r="D127" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -5201,8 +4811,6 @@
       <c r="G127" t="n">
         <v>3220</v>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5226,7 +4834,6 @@
       <c r="D128" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -5235,8 +4842,6 @@
       <c r="G128" t="n">
         <v>3102</v>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5260,7 +4865,6 @@
       <c r="D129" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -5269,8 +4873,6 @@
       <c r="G129" t="n">
         <v>2960</v>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5294,7 +4896,6 @@
       <c r="D130" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -5303,8 +4904,6 @@
       <c r="G130" t="n">
         <v>2875</v>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5328,7 +4927,6 @@
       <c r="D131" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -5337,8 +4935,6 @@
       <c r="G131" t="n">
         <v>2015</v>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5362,7 +4958,6 @@
       <c r="D132" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -5371,8 +4966,6 @@
       <c r="G132" t="n">
         <v>1542</v>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5396,7 +4989,6 @@
       <c r="D133" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -5405,8 +4997,6 @@
       <c r="G133" t="n">
         <v>1322</v>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5430,7 +5020,6 @@
       <c r="D134" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5439,8 +5028,6 @@
       <c r="G134" t="n">
         <v>1216</v>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5464,7 +5051,6 @@
       <c r="D135" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -5473,8 +5059,6 @@
       <c r="G135" t="n">
         <v>1125</v>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5498,7 +5082,6 @@
       <c r="D136" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -5507,8 +5090,6 @@
       <c r="G136" t="n">
         <v>1095</v>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5532,7 +5113,6 @@
       <c r="D137" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -5541,8 +5121,6 @@
       <c r="G137" t="n">
         <v>1095</v>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5566,7 +5144,6 @@
       <c r="D138" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -5575,8 +5152,6 @@
       <c r="G138" t="n">
         <v>798</v>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5600,7 +5175,6 @@
       <c r="D139" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -5609,8 +5183,6 @@
       <c r="G139" t="n">
         <v>547</v>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5634,7 +5206,6 @@
       <c r="D140" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -5643,8 +5214,6 @@
       <c r="G140" t="n">
         <v>140</v>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5668,7 +5237,6 @@
       <c r="D141" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -5677,8 +5245,6 @@
       <c r="G141" t="n">
         <v>304</v>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5702,7 +5268,6 @@
       <c r="D142" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -5711,8 +5276,6 @@
       <c r="G142" t="n">
         <v>304</v>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5736,7 +5299,6 @@
       <c r="D143" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -5745,8 +5307,6 @@
       <c r="G143" t="n">
         <v>407</v>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5770,7 +5330,6 @@
       <c r="D144" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5779,8 +5338,6 @@
       <c r="G144" t="n">
         <v>1520</v>
       </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5804,7 +5361,6 @@
       <c r="D145" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -5813,8 +5369,6 @@
       <c r="G145" t="n">
         <v>1216</v>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5838,7 +5392,6 @@
       <c r="D146" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -5847,8 +5400,6 @@
       <c r="G146" t="n">
         <v>912</v>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5872,7 +5423,6 @@
       <c r="D147" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -5881,8 +5431,6 @@
       <c r="G147" t="n">
         <v>760</v>
       </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5906,7 +5454,6 @@
       <c r="D148" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -5915,8 +5462,6 @@
       <c r="G148" t="n">
         <v>608</v>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5940,7 +5485,6 @@
       <c r="D149" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -5949,8 +5493,6 @@
       <c r="G149" t="n">
         <v>456</v>
       </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5974,7 +5516,6 @@
       <c r="D150" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -5983,8 +5524,6 @@
       <c r="G150" t="n">
         <v>304</v>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6008,7 +5547,6 @@
       <c r="D151" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6017,8 +5555,6 @@
       <c r="G151" t="n">
         <v>304</v>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6042,7 +5578,6 @@
       <c r="D152" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6051,8 +5586,6 @@
       <c r="G152" t="n">
         <v>304</v>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6076,7 +5609,6 @@
       <c r="D153" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6085,8 +5617,6 @@
       <c r="G153" t="n">
         <v>370.8394</v>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6110,7 +5640,6 @@
       <c r="D154" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -6119,8 +5648,6 @@
       <c r="G154" t="n">
         <v>179</v>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6144,7 +5671,6 @@
       <c r="D155" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -6153,7 +5679,6 @@
       <c r="G155" t="n">
         <v>803.1668</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>25.2961</v>
       </c>
@@ -6180,7 +5705,6 @@
       <c r="D156" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -6189,7 +5713,6 @@
       <c r="G156" t="n">
         <v>280</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
         <v>8.8187</v>
       </c>
@@ -6216,7 +5739,6 @@
       <c r="D157" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -6225,7 +5747,6 @@
       <c r="G157" t="n">
         <v>270</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
         <v>8.5038</v>
       </c>
@@ -6252,7 +5773,6 @@
       <c r="D158" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -6261,7 +5781,6 @@
       <c r="G158" t="n">
         <v>257.4</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
         <v>8.1069</v>
       </c>
@@ -6288,7 +5807,6 @@
       <c r="D159" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -6297,7 +5815,6 @@
       <c r="G159" t="n">
         <v>250.0615</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
         <v>7.8758</v>
       </c>
@@ -6324,7 +5841,6 @@
       <c r="D160" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -6333,7 +5849,6 @@
       <c r="G160" t="n">
         <v>175.1887</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
         <v>5.5176</v>
       </c>
@@ -6360,7 +5875,6 @@
       <c r="D161" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -6369,7 +5883,6 @@
       <c r="G161" t="n">
         <v>157.1815</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
         <v>4.9505</v>
       </c>
@@ -6396,7 +5909,6 @@
       <c r="D162" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -6405,7 +5917,6 @@
       <c r="G162" t="n">
         <v>134.15</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
         <v>4.2251</v>
       </c>
@@ -6432,7 +5943,6 @@
       <c r="D163" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -6441,7 +5951,6 @@
       <c r="G163" t="n">
         <v>126.3621</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
         <v>3.9798</v>
       </c>
@@ -6468,7 +5977,6 @@
       <c r="D164" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -6477,7 +5985,6 @@
       <c r="G164" t="n">
         <v>114.9389</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>3.62</v>
       </c>
@@ -6504,7 +6011,6 @@
       <c r="D165" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -6513,7 +6019,6 @@
       <c r="G165" t="n">
         <v>69.48</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>2.1883</v>
       </c>
@@ -6540,7 +6045,6 @@
       <c r="D166" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>潘鼎</t>
@@ -6549,7 +6053,6 @@
       <c r="G166" t="n">
         <v>63.2</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>1.9905</v>
       </c>
@@ -6576,7 +6079,6 @@
       <c r="D167" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -6585,7 +6087,6 @@
       <c r="G167" t="n">
         <v>62.8726</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>1.9802</v>
       </c>
@@ -6612,7 +6113,6 @@
       <c r="D168" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -6621,7 +6121,6 @@
       <c r="G168" t="n">
         <v>62.8726</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>1.9802</v>
       </c>
@@ -6648,7 +6147,6 @@
       <c r="D169" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -6657,7 +6155,6 @@
       <c r="G169" t="n">
         <v>47.4</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>1.4929</v>
       </c>
@@ -6684,7 +6181,6 @@
       <c r="D170" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -6693,7 +6189,6 @@
       <c r="G170" t="n">
         <v>46.1846</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>1.4546</v>
       </c>
@@ -6720,7 +6215,6 @@
       <c r="D171" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -6729,7 +6223,6 @@
       <c r="G171" t="n">
         <v>40</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>1.2598</v>
       </c>
@@ -6756,7 +6249,6 @@
       <c r="D172" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6765,7 +6257,6 @@
       <c r="G172" t="n">
         <v>39.2954</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>1.2376</v>
       </c>
@@ -6792,7 +6283,6 @@
       <c r="D173" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>陈志华</t>
@@ -6801,7 +6291,6 @@
       <c r="G173" t="n">
         <v>30.04</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>0.9461000000000001</v>
       </c>
@@ -6828,7 +6317,6 @@
       <c r="D174" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>耿卫东</t>
@@ -6837,7 +6325,6 @@
       <c r="G174" t="n">
         <v>30</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>0.9449</v>
       </c>
@@ -6864,7 +6351,6 @@
       <c r="D175" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6873,7 +6359,6 @@
       <c r="G175" t="n">
         <v>23.5772</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0.7426</v>
       </c>
@@ -6900,7 +6385,6 @@
       <c r="D176" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -6909,7 +6393,6 @@
       <c r="G176" t="n">
         <v>20</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
         <v>0.6299</v>
       </c>
@@ -6936,7 +6419,6 @@
       <c r="D177" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -6945,7 +6427,6 @@
       <c r="G177" t="n">
         <v>19.4081</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>0.6113</v>
       </c>
@@ -6972,7 +6453,6 @@
       <c r="D178" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6981,7 +6461,6 @@
       <c r="G178" t="n">
         <v>15.7182</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0.4951</v>
       </c>
@@ -7008,7 +6487,6 @@
       <c r="D179" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -7017,7 +6495,6 @@
       <c r="G179" t="n">
         <v>15.5625</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>0.4901</v>
       </c>
@@ -7044,7 +6521,6 @@
       <c r="D180" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -7053,7 +6529,6 @@
       <c r="G180" t="n">
         <v>12.0034</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>0.3781</v>
       </c>
@@ -7080,7 +6555,6 @@
       <c r="D181" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -7089,7 +6563,6 @@
       <c r="G181" t="n">
         <v>3.0041</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>0.0946</v>
       </c>
@@ -7116,7 +6589,6 @@
       <c r="D182" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -7125,7 +6597,6 @@
       <c r="G182" t="n">
         <v>2.8079</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
         <v>0.08840000000000001</v>
       </c>
@@ -7152,7 +6623,6 @@
       <c r="D183" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -7161,7 +6631,6 @@
       <c r="G183" t="n">
         <v>2.0654</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
         <v>0.06510000000000001</v>
       </c>
@@ -7188,7 +6657,6 @@
       <c r="D184" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -7197,7 +6665,6 @@
       <c r="G184" t="n">
         <v>0.9699</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>0.0305</v>
       </c>
@@ -7224,7 +6691,6 @@
       <c r="D185" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -7233,7 +6699,6 @@
       <c r="G185" t="n">
         <v>0.1556</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.0049</v>
       </c>
@@ -7242,6 +6707,5842 @@
           <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J144"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴流量15条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>股权存量184条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>字段类型+t0存在检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2408</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6158.9225</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-3446.4699</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3156.8427</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-3306.5324</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3156.8427</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6907.7652</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3168.6313</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-3739.1339</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3168.6313</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6919.5538</v>
+      </c>
+      <c r="G9" t="n">
+        <v>40237.2571</v>
+      </c>
+      <c r="H9" t="n">
+        <v>33317.7033</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>40237.2571</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43988.1796</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-40813.1126</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>322</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>322</v>
+      </c>
+      <c r="G13" t="n">
+        <v>322</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="G15" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-3535.0134</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>80</v>
+      </c>
+      <c r="H16" t="n">
+        <v>80</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H17" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>36</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>36</v>
+      </c>
+      <c r="G19" t="n">
+        <v>36</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>87</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>87</v>
+      </c>
+      <c r="G20" t="n">
+        <v>87</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>74</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>74</v>
+      </c>
+      <c r="G21" t="n">
+        <v>74</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>72</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>72</v>
+      </c>
+      <c r="G24" t="n">
+        <v>72</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>72</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>72</v>
+      </c>
+      <c r="G26" t="n">
+        <v>72</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>220</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>220</v>
+      </c>
+      <c r="G27" t="n">
+        <v>220</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1035</v>
+      </c>
+      <c r="G28" t="n">
+        <v>976.7757</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-58.2243</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>322</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>322</v>
+      </c>
+      <c r="G31" t="n">
+        <v>322</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>20</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G33" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>80</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>80</v>
+      </c>
+      <c r="G34" t="n">
+        <v>80</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G35" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>20</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>36</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>36</v>
+      </c>
+      <c r="G37" t="n">
+        <v>36</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>87</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>87</v>
+      </c>
+      <c r="G38" t="n">
+        <v>87</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>74</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>74</v>
+      </c>
+      <c r="G39" t="n">
+        <v>74</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>72</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>72</v>
+      </c>
+      <c r="G42" t="n">
+        <v>72</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>72</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>72</v>
+      </c>
+      <c r="G44" t="n">
+        <v>72</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>220</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>220</v>
+      </c>
+      <c r="G45" t="n">
+        <v>242</v>
+      </c>
+      <c r="H45" t="n">
+        <v>22</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>976.7757</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>976.7757</v>
+      </c>
+      <c r="G46" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>322</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>322</v>
+      </c>
+      <c r="G49" t="n">
+        <v>322</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" t="n">
+        <v>20</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G51" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>80</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>80</v>
+      </c>
+      <c r="G52" t="n">
+        <v>80</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G53" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>20</v>
+      </c>
+      <c r="G54" t="n">
+        <v>20</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>36</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>36</v>
+      </c>
+      <c r="G55" t="n">
+        <v>36</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>87</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>87</v>
+      </c>
+      <c r="G56" t="n">
+        <v>87</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>74</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>74</v>
+      </c>
+      <c r="G57" t="n">
+        <v>74</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>72</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>72</v>
+      </c>
+      <c r="G60" t="n">
+        <v>72</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>72</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>72</v>
+      </c>
+      <c r="G62" t="n">
+        <v>72</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>242</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>242</v>
+      </c>
+      <c r="G63" t="n">
+        <v>242</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="G64" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>20</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>20</v>
+      </c>
+      <c r="G66" t="n">
+        <v>20</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G67" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>40</v>
+      </c>
+      <c r="H68" t="n">
+        <v>40</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>20</v>
+      </c>
+      <c r="H69" t="n">
+        <v>20</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>80</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>80</v>
+      </c>
+      <c r="G70" t="n">
+        <v>80</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>20</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>20</v>
+      </c>
+      <c r="G71" t="n">
+        <v>20</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>36</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>36</v>
+      </c>
+      <c r="G72" t="n">
+        <v>36</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>100</v>
+      </c>
+      <c r="H73" t="n">
+        <v>100</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>80</v>
+      </c>
+      <c r="H74" t="n">
+        <v>80</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="n">
+        <v>20</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>87</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>87</v>
+      </c>
+      <c r="G76" t="n">
+        <v>87</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>74</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>74</v>
+      </c>
+      <c r="G77" t="n">
+        <v>74</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G79" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>72</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>72</v>
+      </c>
+      <c r="G80" t="n">
+        <v>72</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>72</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>72</v>
+      </c>
+      <c r="G82" t="n">
+        <v>72</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>242</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>242</v>
+      </c>
+      <c r="G83" t="n">
+        <v>242</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>60</v>
+      </c>
+      <c r="H84" t="n">
+        <v>60</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>20</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>20</v>
+      </c>
+      <c r="G86" t="n">
+        <v>20</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G87" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>40</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>40</v>
+      </c>
+      <c r="G88" t="n">
+        <v>40</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>20</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>20</v>
+      </c>
+      <c r="G89" t="n">
+        <v>20</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>80</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>80</v>
+      </c>
+      <c r="G90" t="n">
+        <v>80</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>20</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>20</v>
+      </c>
+      <c r="G91" t="n">
+        <v>20</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>36</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>36</v>
+      </c>
+      <c r="G92" t="n">
+        <v>36</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>100</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>100</v>
+      </c>
+      <c r="G93" t="n">
+        <v>100</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>80</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>80</v>
+      </c>
+      <c r="G94" t="n">
+        <v>80</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>20</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>20</v>
+      </c>
+      <c r="G95" t="n">
+        <v>20</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>87</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>87</v>
+      </c>
+      <c r="G96" t="n">
+        <v>87</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>74</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>74</v>
+      </c>
+      <c r="G97" t="n">
+        <v>74</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G99" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>72</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>72</v>
+      </c>
+      <c r="G100" t="n">
+        <v>72</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G101" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>72</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>72</v>
+      </c>
+      <c r="G102" t="n">
+        <v>72</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>242</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>242</v>
+      </c>
+      <c r="G103" t="n">
+        <v>242</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>60</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>60</v>
+      </c>
+      <c r="G104" t="n">
+        <v>60</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1882.5</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>20</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>20</v>
+      </c>
+      <c r="G106" t="n">
+        <v>304</v>
+      </c>
+      <c r="H106" t="n">
+        <v>284</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E107" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2875</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-1091.8316</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>40</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>40</v>
+      </c>
+      <c r="G108" t="n">
+        <v>608</v>
+      </c>
+      <c r="H108" t="n">
+        <v>568</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>20</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>20</v>
+      </c>
+      <c r="G109" t="n">
+        <v>304</v>
+      </c>
+      <c r="H109" t="n">
+        <v>284</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>80</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>80</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1136</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>20</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>20</v>
+      </c>
+      <c r="G111" t="n">
+        <v>304</v>
+      </c>
+      <c r="H111" t="n">
+        <v>284</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>36</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>36</v>
+      </c>
+      <c r="G112" t="n">
+        <v>547</v>
+      </c>
+      <c r="H112" t="n">
+        <v>511</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>100</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>100</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1520</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>80</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>80</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1136</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>20</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>20</v>
+      </c>
+      <c r="G115" t="n">
+        <v>304</v>
+      </c>
+      <c r="H115" t="n">
+        <v>284</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>87</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>87</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1322</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1235</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>74</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>74</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1125</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1051</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G118" t="n">
+        <v>798</v>
+      </c>
+      <c r="H118" t="n">
+        <v>745.5</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1542</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1440.7</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>72</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>72</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1023</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2960</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2765.5</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>72</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>72</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1023</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>242</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>242</v>
+      </c>
+      <c r="G123" t="n">
+        <v>3102</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2860</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>60</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>60</v>
+      </c>
+      <c r="G124" t="n">
+        <v>912</v>
+      </c>
+      <c r="H124" t="n">
+        <v>852</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G125" t="n">
+        <v>175.1887</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-1839.8113</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>304</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>304</v>
+      </c>
+      <c r="G126" t="n">
+        <v>3.0041</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-300.9959</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>2875</v>
+      </c>
+      <c r="E127" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6625.9225</v>
+      </c>
+      <c r="G127" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-6375.861</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>608</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>608</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-607.0300999999999</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>304</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>304</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-303.8444</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1216</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1216</v>
+      </c>
+      <c r="G130" t="n">
+        <v>126.3621</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-1089.6379</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>304</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>304</v>
+      </c>
+      <c r="G131" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-284.5919</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>547</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>547</v>
+      </c>
+      <c r="G132" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-499.6</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1520</v>
+      </c>
+      <c r="G133" t="n">
+        <v>157.1815</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-1362.8185</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>潘鼎</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>304</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>304</v>
+      </c>
+      <c r="G135" t="n">
+        <v>23.5772</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-280.4228</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1322</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1322</v>
+      </c>
+      <c r="G136" t="n">
+        <v>114.9389</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-1207.0611</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1125</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1125</v>
+      </c>
+      <c r="G137" t="n">
+        <v>40</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-1085</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>798</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>798</v>
+      </c>
+      <c r="G138" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-728.52</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1542</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1542</v>
+      </c>
+      <c r="G139" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-1407.85</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1095</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1095</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2.8079</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-1092.1921</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>陈志华</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="H141" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1095</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1095</v>
+      </c>
+      <c r="G142" t="n">
+        <v>20</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-1075</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>3102</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3102</v>
+      </c>
+      <c r="G143" t="n">
+        <v>270</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-2832</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>912</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>912</v>
+      </c>
+      <c r="G144" t="n">
+        <v>62.8726</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-849.1274</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,6 +474,7 @@
       <c r="E2" t="n">
         <v>13500</v>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -501,6 +501,7 @@
       <c r="E3" t="n">
         <v>13500</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -527,6 +528,7 @@
       <c r="E4" t="n">
         <v>13500</v>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -553,6 +555,7 @@
       <c r="E5" t="n">
         <v>13500</v>
       </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -579,6 +582,7 @@
       <c r="E6" t="n">
         <v>13500</v>
       </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -605,6 +609,7 @@
       <c r="E7" t="n">
         <v>13500</v>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -631,6 +636,7 @@
       <c r="E8" t="n">
         <v>13500</v>
       </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -657,6 +663,7 @@
       <c r="E9" t="n">
         <v>13500</v>
       </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -683,6 +690,7 @@
       <c r="E10" t="n">
         <v>13500</v>
       </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -709,6 +717,7 @@
       <c r="E11" t="n">
         <v>13500</v>
       </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -735,6 +744,7 @@
       <c r="E12" t="n">
         <v>13500</v>
       </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -761,6 +771,7 @@
       <c r="E13" t="n">
         <v>13500</v>
       </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -787,6 +798,7 @@
       <c r="E14" t="n">
         <v>13500</v>
       </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -813,6 +825,7 @@
       <c r="E15" t="n">
         <v>13500</v>
       </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -839,6 +852,7 @@
       <c r="E16" t="n">
         <v>13500</v>
       </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -928,6 +942,7 @@
       <c r="D2" t="n">
         <v>2408</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -936,6 +951,8 @@
       <c r="G2" t="n">
         <v>1035</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -959,6 +976,7 @@
       <c r="D3" t="n">
         <v>2408</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -967,6 +985,8 @@
       <c r="G3" t="n">
         <v>322</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -990,6 +1010,7 @@
       <c r="D4" t="n">
         <v>2408</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -998,6 +1019,8 @@
       <c r="G4" t="n">
         <v>220</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1021,6 +1044,7 @@
       <c r="D5" t="n">
         <v>2408</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1029,6 +1053,8 @@
       <c r="G5" t="n">
         <v>194.5</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1052,6 +1078,7 @@
       <c r="D6" t="n">
         <v>2408</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1060,6 +1087,8 @@
       <c r="G6" t="n">
         <v>132.5</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1083,6 +1112,7 @@
       <c r="D7" t="n">
         <v>2408</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1091,6 +1121,8 @@
       <c r="G7" t="n">
         <v>101.3</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1114,6 +1146,7 @@
       <c r="D8" t="n">
         <v>2408</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1122,6 +1155,8 @@
       <c r="G8" t="n">
         <v>87</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1145,6 +1180,7 @@
       <c r="D9" t="n">
         <v>2408</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1153,6 +1189,8 @@
       <c r="G9" t="n">
         <v>52.5</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1176,6 +1214,7 @@
       <c r="D10" t="n">
         <v>2408</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1184,6 +1223,8 @@
       <c r="G10" t="n">
         <v>36</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1207,6 +1248,7 @@
       <c r="D11" t="n">
         <v>2408</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1215,6 +1257,8 @@
       <c r="G11" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1238,6 +1282,7 @@
       <c r="D12" t="n">
         <v>2408</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1246,6 +1291,8 @@
       <c r="G12" t="n">
         <v>72</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1269,6 +1316,7 @@
       <c r="D13" t="n">
         <v>2408</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1277,6 +1325,8 @@
       <c r="G13" t="n">
         <v>72</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1300,6 +1350,7 @@
       <c r="D14" t="n">
         <v>2408</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1308,6 +1359,8 @@
       <c r="G14" t="n">
         <v>74</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1331,6 +1384,7 @@
       <c r="D15" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1339,6 +1393,8 @@
       <c r="G15" t="n">
         <v>976.7757</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1362,6 +1418,7 @@
       <c r="D16" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1370,6 +1427,8 @@
       <c r="G16" t="n">
         <v>322</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1393,6 +1452,7 @@
       <c r="D17" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1401,6 +1461,8 @@
       <c r="G17" t="n">
         <v>220</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1424,6 +1486,7 @@
       <c r="D18" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1432,6 +1495,8 @@
       <c r="G18" t="n">
         <v>194.5</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1455,6 +1520,7 @@
       <c r="D19" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -1463,6 +1529,8 @@
       <c r="G19" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1486,6 +1554,7 @@
       <c r="D20" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1494,6 +1563,8 @@
       <c r="G20" t="n">
         <v>132.5</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1517,6 +1588,7 @@
       <c r="D21" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1525,6 +1597,8 @@
       <c r="G21" t="n">
         <v>101.3</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1548,6 +1622,7 @@
       <c r="D22" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1556,6 +1631,8 @@
       <c r="G22" t="n">
         <v>87</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1579,6 +1656,7 @@
       <c r="D23" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -1587,6 +1665,8 @@
       <c r="G23" t="n">
         <v>80</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1610,6 +1690,7 @@
       <c r="D24" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1618,6 +1699,8 @@
       <c r="G24" t="n">
         <v>74</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1641,6 +1724,7 @@
       <c r="D25" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1649,6 +1733,8 @@
       <c r="G25" t="n">
         <v>72</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1672,6 +1758,7 @@
       <c r="D26" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1680,6 +1767,8 @@
       <c r="G26" t="n">
         <v>72</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1703,6 +1792,7 @@
       <c r="D27" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1711,6 +1801,8 @@
       <c r="G27" t="n">
         <v>52.5</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1734,6 +1826,7 @@
       <c r="D28" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1742,6 +1835,8 @@
       <c r="G28" t="n">
         <v>36</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1765,6 +1860,7 @@
       <c r="D29" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1773,6 +1869,8 @@
       <c r="G29" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1796,6 +1894,7 @@
       <c r="D30" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -1804,6 +1903,8 @@
       <c r="G30" t="n">
         <v>20</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1827,6 +1928,7 @@
       <c r="D31" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -1835,6 +1937,8 @@
       <c r="G31" t="n">
         <v>20</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1858,6 +1962,7 @@
       <c r="D32" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -1866,6 +1971,8 @@
       <c r="G32" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1889,6 +1996,7 @@
       <c r="D33" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1897,6 +2005,8 @@
       <c r="G33" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1920,6 +2030,7 @@
       <c r="D34" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1928,6 +2039,8 @@
       <c r="G34" t="n">
         <v>322</v>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1951,6 +2064,7 @@
       <c r="D35" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1959,6 +2073,8 @@
       <c r="G35" t="n">
         <v>242</v>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1982,6 +2098,7 @@
       <c r="D36" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1990,6 +2107,8 @@
       <c r="G36" t="n">
         <v>194.5</v>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2013,6 +2132,7 @@
       <c r="D37" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2021,6 +2141,8 @@
       <c r="G37" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2044,6 +2166,7 @@
       <c r="D38" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2052,6 +2175,8 @@
       <c r="G38" t="n">
         <v>132.5</v>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2075,6 +2200,7 @@
       <c r="D39" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2083,6 +2209,8 @@
       <c r="G39" t="n">
         <v>101.3</v>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2106,6 +2234,7 @@
       <c r="D40" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2114,6 +2243,8 @@
       <c r="G40" t="n">
         <v>87</v>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2137,6 +2268,7 @@
       <c r="D41" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2145,6 +2277,8 @@
       <c r="G41" t="n">
         <v>80</v>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2168,6 +2302,7 @@
       <c r="D42" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2176,6 +2311,8 @@
       <c r="G42" t="n">
         <v>74</v>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2199,6 +2336,7 @@
       <c r="D43" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2207,6 +2345,8 @@
       <c r="G43" t="n">
         <v>72</v>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2230,6 +2370,7 @@
       <c r="D44" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2238,6 +2379,8 @@
       <c r="G44" t="n">
         <v>72</v>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2261,6 +2404,7 @@
       <c r="D45" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2269,6 +2413,8 @@
       <c r="G45" t="n">
         <v>52.5</v>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2292,6 +2438,7 @@
       <c r="D46" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2300,6 +2447,8 @@
       <c r="G46" t="n">
         <v>36</v>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2323,6 +2472,7 @@
       <c r="D47" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2331,6 +2481,8 @@
       <c r="G47" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2354,6 +2506,7 @@
       <c r="D48" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2362,6 +2515,8 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2385,6 +2540,7 @@
       <c r="D49" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2393,6 +2549,8 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2416,6 +2574,7 @@
       <c r="D50" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2424,6 +2583,8 @@
       <c r="G50" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2447,6 +2608,7 @@
       <c r="D51" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2455,6 +2617,8 @@
       <c r="G51" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2478,6 +2642,7 @@
       <c r="D52" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2486,6 +2651,8 @@
       <c r="G52" t="n">
         <v>322</v>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2509,6 +2676,7 @@
       <c r="D53" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2517,6 +2685,8 @@
       <c r="G53" t="n">
         <v>242</v>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2540,6 +2710,7 @@
       <c r="D54" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2548,6 +2719,8 @@
       <c r="G54" t="n">
         <v>194.5</v>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2571,6 +2744,7 @@
       <c r="D55" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2579,6 +2753,8 @@
       <c r="G55" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2602,6 +2778,7 @@
       <c r="D56" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2610,6 +2787,8 @@
       <c r="G56" t="n">
         <v>132.5</v>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2633,6 +2812,7 @@
       <c r="D57" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2641,6 +2821,8 @@
       <c r="G57" t="n">
         <v>101.3</v>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2664,6 +2846,7 @@
       <c r="D58" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2672,6 +2855,8 @@
       <c r="G58" t="n">
         <v>87</v>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2695,6 +2880,7 @@
       <c r="D59" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2703,6 +2889,8 @@
       <c r="G59" t="n">
         <v>80</v>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2726,6 +2914,7 @@
       <c r="D60" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2734,6 +2923,8 @@
       <c r="G60" t="n">
         <v>74</v>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2757,6 +2948,7 @@
       <c r="D61" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2765,6 +2957,8 @@
       <c r="G61" t="n">
         <v>72</v>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2788,6 +2982,7 @@
       <c r="D62" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2796,6 +2991,8 @@
       <c r="G62" t="n">
         <v>72</v>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2819,6 +3016,7 @@
       <c r="D63" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2827,6 +3025,8 @@
       <c r="G63" t="n">
         <v>52.5</v>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2850,6 +3050,7 @@
       <c r="D64" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2858,6 +3059,8 @@
       <c r="G64" t="n">
         <v>36</v>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2881,6 +3084,7 @@
       <c r="D65" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2889,6 +3093,8 @@
       <c r="G65" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2912,6 +3118,7 @@
       <c r="D66" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2920,6 +3127,8 @@
       <c r="G66" t="n">
         <v>20</v>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2943,6 +3152,7 @@
       <c r="D67" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2951,6 +3161,8 @@
       <c r="G67" t="n">
         <v>20</v>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2974,6 +3186,7 @@
       <c r="D68" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2982,6 +3195,8 @@
       <c r="G68" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3005,6 +3220,7 @@
       <c r="D69" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3013,6 +3229,8 @@
       <c r="G69" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3036,6 +3254,7 @@
       <c r="D70" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3044,6 +3263,8 @@
       <c r="G70" t="n">
         <v>322</v>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3067,6 +3288,7 @@
       <c r="D71" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3075,6 +3297,8 @@
       <c r="G71" t="n">
         <v>242</v>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3098,6 +3322,7 @@
       <c r="D72" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3106,6 +3331,8 @@
       <c r="G72" t="n">
         <v>194.5</v>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3129,6 +3356,7 @@
       <c r="D73" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -3137,6 +3365,8 @@
       <c r="G73" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3160,6 +3390,7 @@
       <c r="D74" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -3168,6 +3399,8 @@
       <c r="G74" t="n">
         <v>132.5</v>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3191,6 +3424,7 @@
       <c r="D75" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -3199,6 +3433,8 @@
       <c r="G75" t="n">
         <v>101.3</v>
       </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3222,6 +3458,7 @@
       <c r="D76" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -3230,6 +3467,8 @@
       <c r="G76" t="n">
         <v>87</v>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3253,6 +3492,7 @@
       <c r="D77" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -3261,6 +3501,8 @@
       <c r="G77" t="n">
         <v>80</v>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3284,6 +3526,7 @@
       <c r="D78" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -3292,6 +3535,8 @@
       <c r="G78" t="n">
         <v>74</v>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3315,6 +3560,7 @@
       <c r="D79" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -3323,6 +3569,8 @@
       <c r="G79" t="n">
         <v>72</v>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3346,6 +3594,7 @@
       <c r="D80" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -3354,6 +3603,8 @@
       <c r="G80" t="n">
         <v>72</v>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3377,6 +3628,7 @@
       <c r="D81" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3385,6 +3637,8 @@
       <c r="G81" t="n">
         <v>52.5</v>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3408,6 +3662,7 @@
       <c r="D82" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3416,6 +3671,8 @@
       <c r="G82" t="n">
         <v>36</v>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3439,6 +3696,7 @@
       <c r="D83" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3447,6 +3705,8 @@
       <c r="G83" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3470,6 +3730,7 @@
       <c r="D84" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3478,6 +3739,8 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3501,6 +3764,7 @@
       <c r="D85" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3509,6 +3773,8 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3532,6 +3798,7 @@
       <c r="D86" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3540,6 +3807,8 @@
       <c r="G86" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3563,6 +3832,7 @@
       <c r="D87" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -3571,6 +3841,8 @@
       <c r="G87" t="n">
         <v>100</v>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3594,6 +3866,7 @@
       <c r="D88" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -3602,6 +3875,8 @@
       <c r="G88" t="n">
         <v>80</v>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3625,6 +3900,7 @@
       <c r="D89" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -3633,6 +3909,8 @@
       <c r="G89" t="n">
         <v>60</v>
       </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3656,6 +3934,7 @@
       <c r="D90" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -3664,6 +3943,8 @@
       <c r="G90" t="n">
         <v>50</v>
       </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3687,6 +3968,7 @@
       <c r="D91" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -3695,6 +3977,8 @@
       <c r="G91" t="n">
         <v>40</v>
       </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3718,6 +4002,7 @@
       <c r="D92" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -3726,6 +4011,8 @@
       <c r="G92" t="n">
         <v>30</v>
       </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3749,6 +4036,7 @@
       <c r="D93" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -3757,6 +4045,8 @@
       <c r="G93" t="n">
         <v>20</v>
       </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3780,6 +4070,7 @@
       <c r="D94" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -3788,6 +4079,8 @@
       <c r="G94" t="n">
         <v>20</v>
       </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3811,6 +4104,7 @@
       <c r="D95" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -3819,6 +4113,8 @@
       <c r="G95" t="n">
         <v>20</v>
       </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3842,6 +4138,7 @@
       <c r="D96" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -3850,6 +4147,8 @@
       <c r="G96" t="n">
         <v>24.3901</v>
       </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3873,6 +4172,7 @@
       <c r="D97" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3881,6 +4181,8 @@
       <c r="G97" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3904,6 +4206,7 @@
       <c r="D98" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3912,6 +4215,8 @@
       <c r="G98" t="n">
         <v>322</v>
       </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3935,6 +4240,7 @@
       <c r="D99" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3943,6 +4249,8 @@
       <c r="G99" t="n">
         <v>242</v>
       </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3966,6 +4274,7 @@
       <c r="D100" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3974,6 +4283,8 @@
       <c r="G100" t="n">
         <v>194.5</v>
       </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3997,6 +4308,7 @@
       <c r="D101" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4005,6 +4317,8 @@
       <c r="G101" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4028,6 +4342,7 @@
       <c r="D102" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4036,6 +4351,8 @@
       <c r="G102" t="n">
         <v>132.5</v>
       </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4059,6 +4376,7 @@
       <c r="D103" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4067,6 +4385,8 @@
       <c r="G103" t="n">
         <v>101.3</v>
       </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4090,6 +4410,7 @@
       <c r="D104" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4098,6 +4419,8 @@
       <c r="G104" t="n">
         <v>87</v>
       </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4121,6 +4444,7 @@
       <c r="D105" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -4129,6 +4453,8 @@
       <c r="G105" t="n">
         <v>80</v>
       </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4152,6 +4478,7 @@
       <c r="D106" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -4160,6 +4487,8 @@
       <c r="G106" t="n">
         <v>74</v>
       </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4183,6 +4512,7 @@
       <c r="D107" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -4191,6 +4521,8 @@
       <c r="G107" t="n">
         <v>72</v>
       </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4214,6 +4546,7 @@
       <c r="D108" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -4222,6 +4555,8 @@
       <c r="G108" t="n">
         <v>72</v>
       </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4245,6 +4580,7 @@
       <c r="D109" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -4253,6 +4589,8 @@
       <c r="G109" t="n">
         <v>52.5</v>
       </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4276,6 +4614,7 @@
       <c r="D110" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -4284,6 +4623,8 @@
       <c r="G110" t="n">
         <v>36</v>
       </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4307,6 +4648,7 @@
       <c r="D111" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -4315,6 +4657,8 @@
       <c r="G111" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4338,6 +4682,7 @@
       <c r="D112" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -4346,6 +4691,8 @@
       <c r="G112" t="n">
         <v>20</v>
       </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4369,6 +4716,7 @@
       <c r="D113" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -4377,6 +4725,8 @@
       <c r="G113" t="n">
         <v>20</v>
       </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4400,6 +4750,7 @@
       <c r="D114" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -4408,6 +4759,8 @@
       <c r="G114" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4431,6 +4784,7 @@
       <c r="D115" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -4439,6 +4793,8 @@
       <c r="G115" t="n">
         <v>100</v>
       </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4462,6 +4818,7 @@
       <c r="D116" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -4470,6 +4827,8 @@
       <c r="G116" t="n">
         <v>80</v>
       </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4493,6 +4852,7 @@
       <c r="D117" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -4501,6 +4861,8 @@
       <c r="G117" t="n">
         <v>60</v>
       </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4524,6 +4886,7 @@
       <c r="D118" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -4532,6 +4895,8 @@
       <c r="G118" t="n">
         <v>50</v>
       </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4555,6 +4920,7 @@
       <c r="D119" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -4563,6 +4929,8 @@
       <c r="G119" t="n">
         <v>40</v>
       </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4586,6 +4954,7 @@
       <c r="D120" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4594,6 +4963,8 @@
       <c r="G120" t="n">
         <v>30</v>
       </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4617,6 +4988,7 @@
       <c r="D121" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4625,6 +4997,8 @@
       <c r="G121" t="n">
         <v>20</v>
       </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4648,6 +5022,7 @@
       <c r="D122" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -4656,6 +5031,8 @@
       <c r="G122" t="n">
         <v>20</v>
       </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4679,6 +5056,7 @@
       <c r="D123" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -4687,6 +5065,8 @@
       <c r="G123" t="n">
         <v>20</v>
       </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4710,6 +5090,7 @@
       <c r="D124" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -4718,6 +5099,8 @@
       <c r="G124" t="n">
         <v>24.3901</v>
       </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4741,6 +5124,7 @@
       <c r="D125" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -4749,6 +5133,8 @@
       <c r="G125" t="n">
         <v>11.7886</v>
       </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4772,6 +5158,7 @@
       <c r="D126" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -4780,6 +5167,8 @@
       <c r="G126" t="n">
         <v>9236.4177</v>
       </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4803,6 +5192,7 @@
       <c r="D127" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -4811,6 +5201,8 @@
       <c r="G127" t="n">
         <v>3220</v>
       </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4834,6 +5226,7 @@
       <c r="D128" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -4842,6 +5235,8 @@
       <c r="G128" t="n">
         <v>3102</v>
       </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4865,6 +5260,7 @@
       <c r="D129" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -4873,6 +5269,8 @@
       <c r="G129" t="n">
         <v>2960</v>
       </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4896,6 +5294,7 @@
       <c r="D130" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4904,6 +5303,8 @@
       <c r="G130" t="n">
         <v>2875</v>
       </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4927,6 +5328,7 @@
       <c r="D131" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4935,6 +5337,8 @@
       <c r="G131" t="n">
         <v>2015</v>
       </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4958,6 +5362,7 @@
       <c r="D132" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4966,6 +5371,8 @@
       <c r="G132" t="n">
         <v>1542</v>
       </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4989,6 +5396,7 @@
       <c r="D133" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4997,6 +5405,8 @@
       <c r="G133" t="n">
         <v>1322</v>
       </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5020,6 +5430,7 @@
       <c r="D134" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5028,6 +5439,8 @@
       <c r="G134" t="n">
         <v>1216</v>
       </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5051,6 +5464,7 @@
       <c r="D135" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -5059,6 +5473,8 @@
       <c r="G135" t="n">
         <v>1125</v>
       </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5082,6 +5498,7 @@
       <c r="D136" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -5090,6 +5507,8 @@
       <c r="G136" t="n">
         <v>1095</v>
       </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5113,6 +5532,7 @@
       <c r="D137" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -5121,6 +5541,8 @@
       <c r="G137" t="n">
         <v>1095</v>
       </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5144,6 +5566,7 @@
       <c r="D138" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -5152,6 +5575,8 @@
       <c r="G138" t="n">
         <v>798</v>
       </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5175,6 +5600,7 @@
       <c r="D139" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -5183,6 +5609,8 @@
       <c r="G139" t="n">
         <v>547</v>
       </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5206,6 +5634,7 @@
       <c r="D140" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -5214,6 +5643,8 @@
       <c r="G140" t="n">
         <v>140</v>
       </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5237,6 +5668,7 @@
       <c r="D141" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -5245,6 +5677,8 @@
       <c r="G141" t="n">
         <v>304</v>
       </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5268,6 +5702,7 @@
       <c r="D142" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -5276,6 +5711,8 @@
       <c r="G142" t="n">
         <v>304</v>
       </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5299,6 +5736,7 @@
       <c r="D143" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -5307,6 +5745,8 @@
       <c r="G143" t="n">
         <v>407</v>
       </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5330,6 +5770,7 @@
       <c r="D144" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5338,6 +5779,8 @@
       <c r="G144" t="n">
         <v>1520</v>
       </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5361,6 +5804,7 @@
       <c r="D145" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -5369,6 +5813,8 @@
       <c r="G145" t="n">
         <v>1216</v>
       </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5392,6 +5838,7 @@
       <c r="D146" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -5400,6 +5847,8 @@
       <c r="G146" t="n">
         <v>912</v>
       </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5423,6 +5872,7 @@
       <c r="D147" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -5431,6 +5881,8 @@
       <c r="G147" t="n">
         <v>760</v>
       </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5454,6 +5906,7 @@
       <c r="D148" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -5462,6 +5915,8 @@
       <c r="G148" t="n">
         <v>608</v>
       </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5485,6 +5940,7 @@
       <c r="D149" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -5493,6 +5949,8 @@
       <c r="G149" t="n">
         <v>456</v>
       </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5516,6 +5974,7 @@
       <c r="D150" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -5524,6 +5983,8 @@
       <c r="G150" t="n">
         <v>304</v>
       </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5547,6 +6008,7 @@
       <c r="D151" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -5555,6 +6017,8 @@
       <c r="G151" t="n">
         <v>304</v>
       </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5578,6 +6042,7 @@
       <c r="D152" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -5586,6 +6051,8 @@
       <c r="G152" t="n">
         <v>304</v>
       </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5609,6 +6076,7 @@
       <c r="D153" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -5617,6 +6085,8 @@
       <c r="G153" t="n">
         <v>370.8394</v>
       </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5640,6 +6110,7 @@
       <c r="D154" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -5648,6 +6119,8 @@
       <c r="G154" t="n">
         <v>179</v>
       </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5671,6 +6144,7 @@
       <c r="D155" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -5679,6 +6153,7 @@
       <c r="G155" t="n">
         <v>803.1668</v>
       </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>25.2961</v>
       </c>
@@ -5705,6 +6180,7 @@
       <c r="D156" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -5713,6 +6189,7 @@
       <c r="G156" t="n">
         <v>280</v>
       </c>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
         <v>8.8187</v>
       </c>
@@ -5739,6 +6216,7 @@
       <c r="D157" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -5747,6 +6225,7 @@
       <c r="G157" t="n">
         <v>270</v>
       </c>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
         <v>8.5038</v>
       </c>
@@ -5773,6 +6252,7 @@
       <c r="D158" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -5781,6 +6261,7 @@
       <c r="G158" t="n">
         <v>257.4</v>
       </c>
+      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
         <v>8.1069</v>
       </c>
@@ -5807,6 +6288,7 @@
       <c r="D159" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -5815,6 +6297,7 @@
       <c r="G159" t="n">
         <v>250.0615</v>
       </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
         <v>7.8758</v>
       </c>
@@ -5841,6 +6324,7 @@
       <c r="D160" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -5849,6 +6333,7 @@
       <c r="G160" t="n">
         <v>175.1887</v>
       </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
         <v>5.5176</v>
       </c>
@@ -5875,6 +6360,7 @@
       <c r="D161" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5883,6 +6369,7 @@
       <c r="G161" t="n">
         <v>157.1815</v>
       </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
         <v>4.9505</v>
       </c>
@@ -5909,6 +6396,7 @@
       <c r="D162" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -5917,6 +6405,7 @@
       <c r="G162" t="n">
         <v>134.15</v>
       </c>
+      <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
         <v>4.2251</v>
       </c>
@@ -5943,6 +6432,7 @@
       <c r="D163" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5951,6 +6441,7 @@
       <c r="G163" t="n">
         <v>126.3621</v>
       </c>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
         <v>3.9798</v>
       </c>
@@ -5977,6 +6468,7 @@
       <c r="D164" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -5985,6 +6477,7 @@
       <c r="G164" t="n">
         <v>114.9389</v>
       </c>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>3.62</v>
       </c>
@@ -6011,6 +6504,7 @@
       <c r="D165" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -6019,6 +6513,7 @@
       <c r="G165" t="n">
         <v>69.48</v>
       </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>2.1883</v>
       </c>
@@ -6045,6 +6540,7 @@
       <c r="D166" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>潘鼎</t>
@@ -6053,6 +6549,7 @@
       <c r="G166" t="n">
         <v>63.2</v>
       </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>1.9905</v>
       </c>
@@ -6079,6 +6576,7 @@
       <c r="D167" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -6087,6 +6585,7 @@
       <c r="G167" t="n">
         <v>62.8726</v>
       </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>1.9802</v>
       </c>
@@ -6113,6 +6612,7 @@
       <c r="D168" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -6121,6 +6621,7 @@
       <c r="G168" t="n">
         <v>62.8726</v>
       </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>1.9802</v>
       </c>
@@ -6147,6 +6648,7 @@
       <c r="D169" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -6155,6 +6657,7 @@
       <c r="G169" t="n">
         <v>47.4</v>
       </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>1.4929</v>
       </c>
@@ -6181,6 +6684,7 @@
       <c r="D170" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -6189,6 +6693,7 @@
       <c r="G170" t="n">
         <v>46.1846</v>
       </c>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>1.4546</v>
       </c>
@@ -6215,6 +6720,7 @@
       <c r="D171" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -6223,6 +6729,7 @@
       <c r="G171" t="n">
         <v>40</v>
       </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>1.2598</v>
       </c>
@@ -6249,6 +6756,7 @@
       <c r="D172" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6257,6 +6765,7 @@
       <c r="G172" t="n">
         <v>39.2954</v>
       </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>1.2376</v>
       </c>
@@ -6283,6 +6792,7 @@
       <c r="D173" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>陈志华</t>
@@ -6291,6 +6801,7 @@
       <c r="G173" t="n">
         <v>30.04</v>
       </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>0.9461000000000001</v>
       </c>
@@ -6317,6 +6828,7 @@
       <c r="D174" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>耿卫东</t>
@@ -6325,6 +6837,7 @@
       <c r="G174" t="n">
         <v>30</v>
       </c>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>0.9449</v>
       </c>
@@ -6351,6 +6864,7 @@
       <c r="D175" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6359,6 +6873,7 @@
       <c r="G175" t="n">
         <v>23.5772</v>
       </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0.7426</v>
       </c>
@@ -6385,6 +6900,7 @@
       <c r="D176" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -6393,6 +6909,7 @@
       <c r="G176" t="n">
         <v>20</v>
       </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
         <v>0.6299</v>
       </c>
@@ -6419,6 +6936,7 @@
       <c r="D177" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -6427,6 +6945,7 @@
       <c r="G177" t="n">
         <v>19.4081</v>
       </c>
+      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>0.6113</v>
       </c>
@@ -6453,6 +6972,7 @@
       <c r="D178" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6461,6 +6981,7 @@
       <c r="G178" t="n">
         <v>15.7182</v>
       </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0.4951</v>
       </c>
@@ -6487,6 +7008,7 @@
       <c r="D179" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -6495,6 +7017,7 @@
       <c r="G179" t="n">
         <v>15.5625</v>
       </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>0.4901</v>
       </c>
@@ -6521,6 +7044,7 @@
       <c r="D180" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -6529,6 +7053,7 @@
       <c r="G180" t="n">
         <v>12.0034</v>
       </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>0.3781</v>
       </c>
@@ -6555,6 +7080,7 @@
       <c r="D181" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -6563,6 +7089,7 @@
       <c r="G181" t="n">
         <v>3.0041</v>
       </c>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>0.0946</v>
       </c>
@@ -6589,6 +7116,7 @@
       <c r="D182" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -6597,6 +7125,7 @@
       <c r="G182" t="n">
         <v>2.8079</v>
       </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
         <v>0.08840000000000001</v>
       </c>
@@ -6623,6 +7152,7 @@
       <c r="D183" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -6631,6 +7161,7 @@
       <c r="G183" t="n">
         <v>2.0654</v>
       </c>
+      <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
         <v>0.06510000000000001</v>
       </c>
@@ -6657,6 +7188,7 @@
       <c r="D184" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -6665,6 +7197,7 @@
       <c r="G184" t="n">
         <v>0.9699</v>
       </c>
+      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>0.0305</v>
       </c>
@@ -6691,6 +7224,7 @@
       <c r="D185" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -6699,6 +7233,7 @@
       <c r="G185" t="n">
         <v>0.1556</v>
       </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.0049</v>
       </c>
@@ -6707,5842 +7242,6 @@
           <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J144"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量15条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量184条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>字段类型+t0存在检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2408</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6158.9225</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-3446.4699</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3156.8427</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-3306.5324</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3156.8427</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6907.7652</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3168.6313</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-3739.1339</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3168.6313</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6919.5538</v>
-      </c>
-      <c r="G9" t="n">
-        <v>40237.2571</v>
-      </c>
-      <c r="H9" t="n">
-        <v>33317.7033</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>40237.2571</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F10" t="n">
-        <v>43988.1796</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3175.067</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-40813.1126</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>322</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>322</v>
-      </c>
-      <c r="G13" t="n">
-        <v>322</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H14" t="n">
-        <v>20</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="G15" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-3535.0134</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>80</v>
-      </c>
-      <c r="H16" t="n">
-        <v>80</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H17" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>20</v>
-      </c>
-      <c r="H18" t="n">
-        <v>20</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>36</v>
-      </c>
-      <c r="G19" t="n">
-        <v>36</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>87</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>87</v>
-      </c>
-      <c r="G20" t="n">
-        <v>87</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>74</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>74</v>
-      </c>
-      <c r="G21" t="n">
-        <v>74</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G23" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>72</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>72</v>
-      </c>
-      <c r="G24" t="n">
-        <v>72</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>72</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>72</v>
-      </c>
-      <c r="G26" t="n">
-        <v>72</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>220</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>220</v>
-      </c>
-      <c r="G27" t="n">
-        <v>220</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1035</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1035</v>
-      </c>
-      <c r="G28" t="n">
-        <v>976.7757</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-58.2243</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>322</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>322</v>
-      </c>
-      <c r="G31" t="n">
-        <v>322</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>20</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>20</v>
-      </c>
-      <c r="G32" t="n">
-        <v>20</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F33" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G33" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>80</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>80</v>
-      </c>
-      <c r="G34" t="n">
-        <v>80</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G35" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>20</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>20</v>
-      </c>
-      <c r="G36" t="n">
-        <v>20</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>36</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>36</v>
-      </c>
-      <c r="G37" t="n">
-        <v>36</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>87</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>87</v>
-      </c>
-      <c r="G38" t="n">
-        <v>87</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>74</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>74</v>
-      </c>
-      <c r="G39" t="n">
-        <v>74</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G40" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G41" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>72</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>72</v>
-      </c>
-      <c r="G42" t="n">
-        <v>72</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G43" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>72</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>72</v>
-      </c>
-      <c r="G44" t="n">
-        <v>72</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>220</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>220</v>
-      </c>
-      <c r="G45" t="n">
-        <v>242</v>
-      </c>
-      <c r="H45" t="n">
-        <v>22</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>976.7757</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>976.7757</v>
-      </c>
-      <c r="G46" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G47" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G48" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>322</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>322</v>
-      </c>
-      <c r="G49" t="n">
-        <v>322</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>20</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>20</v>
-      </c>
-      <c r="G50" t="n">
-        <v>20</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G51" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>80</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>80</v>
-      </c>
-      <c r="G52" t="n">
-        <v>80</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G53" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>20</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>20</v>
-      </c>
-      <c r="G54" t="n">
-        <v>20</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>36</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>36</v>
-      </c>
-      <c r="G55" t="n">
-        <v>36</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>87</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>87</v>
-      </c>
-      <c r="G56" t="n">
-        <v>87</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>74</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>74</v>
-      </c>
-      <c r="G57" t="n">
-        <v>74</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G58" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G59" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>72</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>72</v>
-      </c>
-      <c r="G60" t="n">
-        <v>72</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>72</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>72</v>
-      </c>
-      <c r="G62" t="n">
-        <v>72</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>242</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>242</v>
-      </c>
-      <c r="G63" t="n">
-        <v>242</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="G64" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>20</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>20</v>
-      </c>
-      <c r="G66" t="n">
-        <v>20</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E67" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F67" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G67" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>40</v>
-      </c>
-      <c r="H68" t="n">
-        <v>40</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>20</v>
-      </c>
-      <c r="H69" t="n">
-        <v>20</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>80</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>80</v>
-      </c>
-      <c r="G70" t="n">
-        <v>80</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>20</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>20</v>
-      </c>
-      <c r="G71" t="n">
-        <v>20</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>36</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>36</v>
-      </c>
-      <c r="G72" t="n">
-        <v>36</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>100</v>
-      </c>
-      <c r="H73" t="n">
-        <v>100</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>80</v>
-      </c>
-      <c r="H74" t="n">
-        <v>80</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>20</v>
-      </c>
-      <c r="H75" t="n">
-        <v>20</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>87</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>87</v>
-      </c>
-      <c r="G76" t="n">
-        <v>87</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>74</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>74</v>
-      </c>
-      <c r="G77" t="n">
-        <v>74</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G78" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G79" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>72</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>72</v>
-      </c>
-      <c r="G80" t="n">
-        <v>72</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G81" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>72</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>72</v>
-      </c>
-      <c r="G82" t="n">
-        <v>72</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>242</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>242</v>
-      </c>
-      <c r="G83" t="n">
-        <v>242</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>高瓴祈睿</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>60</v>
-      </c>
-      <c r="H84" t="n">
-        <v>60</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G85" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>20</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>20</v>
-      </c>
-      <c r="G86" t="n">
-        <v>20</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E87" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F87" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G87" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>40</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>40</v>
-      </c>
-      <c r="G88" t="n">
-        <v>40</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>20</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>20</v>
-      </c>
-      <c r="G89" t="n">
-        <v>20</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>80</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>80</v>
-      </c>
-      <c r="G90" t="n">
-        <v>80</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>20</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>20</v>
-      </c>
-      <c r="G91" t="n">
-        <v>20</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>36</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>36</v>
-      </c>
-      <c r="G92" t="n">
-        <v>36</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>100</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>100</v>
-      </c>
-      <c r="G93" t="n">
-        <v>100</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>80</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>80</v>
-      </c>
-      <c r="G94" t="n">
-        <v>80</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>20</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>20</v>
-      </c>
-      <c r="G95" t="n">
-        <v>20</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>87</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>87</v>
-      </c>
-      <c r="G96" t="n">
-        <v>87</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>74</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>74</v>
-      </c>
-      <c r="G97" t="n">
-        <v>74</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G98" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G99" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>72</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>72</v>
-      </c>
-      <c r="G100" t="n">
-        <v>72</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G101" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>72</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>72</v>
-      </c>
-      <c r="G102" t="n">
-        <v>72</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>242</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>242</v>
-      </c>
-      <c r="G103" t="n">
-        <v>242</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>高瓴祈睿</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>60</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>60</v>
-      </c>
-      <c r="G104" t="n">
-        <v>60</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G105" t="n">
-        <v>2015</v>
-      </c>
-      <c r="H105" t="n">
-        <v>1882.5</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>20</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>20</v>
-      </c>
-      <c r="G106" t="n">
-        <v>304</v>
-      </c>
-      <c r="H106" t="n">
-        <v>284</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E107" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F107" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G107" t="n">
-        <v>2875</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-1091.8316</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>40</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>40</v>
-      </c>
-      <c r="G108" t="n">
-        <v>608</v>
-      </c>
-      <c r="H108" t="n">
-        <v>568</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>20</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>20</v>
-      </c>
-      <c r="G109" t="n">
-        <v>304</v>
-      </c>
-      <c r="H109" t="n">
-        <v>284</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>80</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>80</v>
-      </c>
-      <c r="G110" t="n">
-        <v>1216</v>
-      </c>
-      <c r="H110" t="n">
-        <v>1136</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>20</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>20</v>
-      </c>
-      <c r="G111" t="n">
-        <v>304</v>
-      </c>
-      <c r="H111" t="n">
-        <v>284</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>36</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>36</v>
-      </c>
-      <c r="G112" t="n">
-        <v>547</v>
-      </c>
-      <c r="H112" t="n">
-        <v>511</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>100</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>100</v>
-      </c>
-      <c r="G113" t="n">
-        <v>1520</v>
-      </c>
-      <c r="H113" t="n">
-        <v>1420</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>80</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>80</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1216</v>
-      </c>
-      <c r="H114" t="n">
-        <v>1136</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>20</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>20</v>
-      </c>
-      <c r="G115" t="n">
-        <v>304</v>
-      </c>
-      <c r="H115" t="n">
-        <v>284</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>87</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>87</v>
-      </c>
-      <c r="G116" t="n">
-        <v>1322</v>
-      </c>
-      <c r="H116" t="n">
-        <v>1235</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>74</v>
-      </c>
-      <c r="E117" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" t="n">
-        <v>74</v>
-      </c>
-      <c r="G117" t="n">
-        <v>1125</v>
-      </c>
-      <c r="H117" t="n">
-        <v>1051</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G118" t="n">
-        <v>798</v>
-      </c>
-      <c r="H118" t="n">
-        <v>745.5</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G119" t="n">
-        <v>1542</v>
-      </c>
-      <c r="H119" t="n">
-        <v>1440.7</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>72</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>72</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1095</v>
-      </c>
-      <c r="H120" t="n">
-        <v>1023</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G121" t="n">
-        <v>2960</v>
-      </c>
-      <c r="H121" t="n">
-        <v>2765.5</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>72</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="n">
-        <v>72</v>
-      </c>
-      <c r="G122" t="n">
-        <v>1095</v>
-      </c>
-      <c r="H122" t="n">
-        <v>1023</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>242</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" t="n">
-        <v>242</v>
-      </c>
-      <c r="G123" t="n">
-        <v>3102</v>
-      </c>
-      <c r="H123" t="n">
-        <v>2860</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>高瓴祈睿</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>60</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>60</v>
-      </c>
-      <c r="G124" t="n">
-        <v>912</v>
-      </c>
-      <c r="H124" t="n">
-        <v>852</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>2015</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>2015</v>
-      </c>
-      <c r="G125" t="n">
-        <v>175.1887</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-1839.8113</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>304</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>304</v>
-      </c>
-      <c r="G126" t="n">
-        <v>3.0041</v>
-      </c>
-      <c r="H126" t="n">
-        <v>-300.9959</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>2875</v>
-      </c>
-      <c r="E127" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F127" t="n">
-        <v>6625.9225</v>
-      </c>
-      <c r="G127" t="n">
-        <v>250.0615</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-6375.861</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>608</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>608</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0.9699</v>
-      </c>
-      <c r="H128" t="n">
-        <v>-607.0300999999999</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>304</v>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>304</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0.1556</v>
-      </c>
-      <c r="H129" t="n">
-        <v>-303.8444</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>1216</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>1216</v>
-      </c>
-      <c r="G130" t="n">
-        <v>126.3621</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-1089.6379</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>304</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" t="n">
-        <v>304</v>
-      </c>
-      <c r="G131" t="n">
-        <v>19.4081</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-284.5919</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>547</v>
-      </c>
-      <c r="E132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" t="n">
-        <v>547</v>
-      </c>
-      <c r="G132" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H132" t="n">
-        <v>-499.6</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>1520</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>1520</v>
-      </c>
-      <c r="G133" t="n">
-        <v>157.1815</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-1362.8185</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>潘鼎</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="H134" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>304</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>304</v>
-      </c>
-      <c r="G135" t="n">
-        <v>23.5772</v>
-      </c>
-      <c r="H135" t="n">
-        <v>-280.4228</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>1322</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G136" t="n">
-        <v>114.9389</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-1207.0611</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>1125</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" t="n">
-        <v>1125</v>
-      </c>
-      <c r="G137" t="n">
-        <v>40</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-1085</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>798</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="n">
-        <v>798</v>
-      </c>
-      <c r="G138" t="n">
-        <v>69.48</v>
-      </c>
-      <c r="H138" t="n">
-        <v>-728.52</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>1542</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" t="n">
-        <v>1542</v>
-      </c>
-      <c r="G139" t="n">
-        <v>134.15</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-1407.85</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>1095</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" t="n">
-        <v>1095</v>
-      </c>
-      <c r="G140" t="n">
-        <v>2.8079</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-1092.1921</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>陈志华</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="H141" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>1095</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" t="n">
-        <v>1095</v>
-      </c>
-      <c r="G142" t="n">
-        <v>20</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-1075</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>3102</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" t="n">
-        <v>3102</v>
-      </c>
-      <c r="G143" t="n">
-        <v>270</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-2832</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>高瓴祈睿</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>912</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="n">
-        <v>912</v>
-      </c>
-      <c r="G144" t="n">
-        <v>62.8726</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-849.1274</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +475,6 @@
       <c r="E2" t="n">
         <v>13500</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -501,7 +501,6 @@
       <c r="E3" t="n">
         <v>13500</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -528,7 +527,6 @@
       <c r="E4" t="n">
         <v>13500</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -555,7 +553,6 @@
       <c r="E5" t="n">
         <v>13500</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -582,7 +579,6 @@
       <c r="E6" t="n">
         <v>13500</v>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -609,7 +605,6 @@
       <c r="E7" t="n">
         <v>13500</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -636,7 +631,6 @@
       <c r="E8" t="n">
         <v>13500</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -663,7 +657,6 @@
       <c r="E9" t="n">
         <v>13500</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -690,7 +683,6 @@
       <c r="E10" t="n">
         <v>13500</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -717,7 +709,6 @@
       <c r="E11" t="n">
         <v>13500</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -744,7 +735,6 @@
       <c r="E12" t="n">
         <v>13500</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -771,7 +761,6 @@
       <c r="E13" t="n">
         <v>13500</v>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -798,7 +787,6 @@
       <c r="E14" t="n">
         <v>13500</v>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -825,7 +813,6 @@
       <c r="E15" t="n">
         <v>13500</v>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -852,7 +839,6 @@
       <c r="E16" t="n">
         <v>13500</v>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -942,7 +928,6 @@
       <c r="D2" t="n">
         <v>2408</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -951,8 +936,6 @@
       <c r="G2" t="n">
         <v>1035</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -976,7 +959,6 @@
       <c r="D3" t="n">
         <v>2408</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -985,8 +967,6 @@
       <c r="G3" t="n">
         <v>322</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1010,7 +990,6 @@
       <c r="D4" t="n">
         <v>2408</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1019,8 +998,6 @@
       <c r="G4" t="n">
         <v>220</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1044,7 +1021,6 @@
       <c r="D5" t="n">
         <v>2408</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1053,8 +1029,6 @@
       <c r="G5" t="n">
         <v>194.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1078,7 +1052,6 @@
       <c r="D6" t="n">
         <v>2408</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1087,8 +1060,6 @@
       <c r="G6" t="n">
         <v>132.5</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1112,7 +1083,6 @@
       <c r="D7" t="n">
         <v>2408</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1121,8 +1091,6 @@
       <c r="G7" t="n">
         <v>101.3</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1146,7 +1114,6 @@
       <c r="D8" t="n">
         <v>2408</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1155,8 +1122,6 @@
       <c r="G8" t="n">
         <v>87</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1180,7 +1145,6 @@
       <c r="D9" t="n">
         <v>2408</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1189,8 +1153,6 @@
       <c r="G9" t="n">
         <v>52.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1214,7 +1176,6 @@
       <c r="D10" t="n">
         <v>2408</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1223,8 +1184,6 @@
       <c r="G10" t="n">
         <v>36</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1248,7 +1207,6 @@
       <c r="D11" t="n">
         <v>2408</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1257,8 +1215,6 @@
       <c r="G11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1282,7 +1238,6 @@
       <c r="D12" t="n">
         <v>2408</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1291,8 +1246,6 @@
       <c r="G12" t="n">
         <v>72</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1316,7 +1269,6 @@
       <c r="D13" t="n">
         <v>2408</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1325,8 +1277,6 @@
       <c r="G13" t="n">
         <v>72</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1350,7 +1300,6 @@
       <c r="D14" t="n">
         <v>2408</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1359,8 +1308,6 @@
       <c r="G14" t="n">
         <v>74</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1384,7 +1331,6 @@
       <c r="D15" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1393,8 +1339,6 @@
       <c r="G15" t="n">
         <v>976.7757</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1418,7 +1362,6 @@
       <c r="D16" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1427,8 +1370,6 @@
       <c r="G16" t="n">
         <v>322</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1452,7 +1393,6 @@
       <c r="D17" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1461,8 +1401,6 @@
       <c r="G17" t="n">
         <v>220</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1486,7 +1424,6 @@
       <c r="D18" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1495,8 +1432,6 @@
       <c r="G18" t="n">
         <v>194.5</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1520,7 +1455,6 @@
       <c r="D19" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -1529,8 +1463,6 @@
       <c r="G19" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1554,7 +1486,6 @@
       <c r="D20" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1563,8 +1494,6 @@
       <c r="G20" t="n">
         <v>132.5</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1588,7 +1517,6 @@
       <c r="D21" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1597,8 +1525,6 @@
       <c r="G21" t="n">
         <v>101.3</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1622,7 +1548,6 @@
       <c r="D22" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1631,8 +1556,6 @@
       <c r="G22" t="n">
         <v>87</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1656,7 +1579,6 @@
       <c r="D23" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -1665,8 +1587,6 @@
       <c r="G23" t="n">
         <v>80</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1690,7 +1610,6 @@
       <c r="D24" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1699,8 +1618,6 @@
       <c r="G24" t="n">
         <v>74</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1724,7 +1641,6 @@
       <c r="D25" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1733,8 +1649,6 @@
       <c r="G25" t="n">
         <v>72</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1758,7 +1672,6 @@
       <c r="D26" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1767,8 +1680,6 @@
       <c r="G26" t="n">
         <v>72</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1792,7 +1703,6 @@
       <c r="D27" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1801,8 +1711,6 @@
       <c r="G27" t="n">
         <v>52.5</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1826,7 +1734,6 @@
       <c r="D28" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1835,8 +1742,6 @@
       <c r="G28" t="n">
         <v>36</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1860,7 +1765,6 @@
       <c r="D29" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1869,8 +1773,6 @@
       <c r="G29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1894,7 +1796,6 @@
       <c r="D30" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -1903,8 +1804,6 @@
       <c r="G30" t="n">
         <v>20</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1928,7 +1827,6 @@
       <c r="D31" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -1937,8 +1835,6 @@
       <c r="G31" t="n">
         <v>20</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1962,7 +1858,6 @@
       <c r="D32" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -1971,8 +1866,6 @@
       <c r="G32" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1996,7 +1889,6 @@
       <c r="D33" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2005,8 +1897,6 @@
       <c r="G33" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2030,7 +1920,6 @@
       <c r="D34" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2039,8 +1928,6 @@
       <c r="G34" t="n">
         <v>322</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2064,7 +1951,6 @@
       <c r="D35" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2073,8 +1959,6 @@
       <c r="G35" t="n">
         <v>242</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2098,7 +1982,6 @@
       <c r="D36" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2107,8 +1990,6 @@
       <c r="G36" t="n">
         <v>194.5</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2132,7 +2013,6 @@
       <c r="D37" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2141,8 +2021,6 @@
       <c r="G37" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2166,7 +2044,6 @@
       <c r="D38" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2175,8 +2052,6 @@
       <c r="G38" t="n">
         <v>132.5</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2200,7 +2075,6 @@
       <c r="D39" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2209,8 +2083,6 @@
       <c r="G39" t="n">
         <v>101.3</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2234,7 +2106,6 @@
       <c r="D40" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2243,8 +2114,6 @@
       <c r="G40" t="n">
         <v>87</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2268,7 +2137,6 @@
       <c r="D41" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2277,8 +2145,6 @@
       <c r="G41" t="n">
         <v>80</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2302,7 +2168,6 @@
       <c r="D42" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2311,8 +2176,6 @@
       <c r="G42" t="n">
         <v>74</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2336,7 +2199,6 @@
       <c r="D43" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2345,8 +2207,6 @@
       <c r="G43" t="n">
         <v>72</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2370,7 +2230,6 @@
       <c r="D44" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2379,8 +2238,6 @@
       <c r="G44" t="n">
         <v>72</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2404,7 +2261,6 @@
       <c r="D45" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2413,8 +2269,6 @@
       <c r="G45" t="n">
         <v>52.5</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2438,7 +2292,6 @@
       <c r="D46" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2447,8 +2300,6 @@
       <c r="G46" t="n">
         <v>36</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2472,7 +2323,6 @@
       <c r="D47" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2481,8 +2331,6 @@
       <c r="G47" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2506,7 +2354,6 @@
       <c r="D48" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2515,8 +2362,6 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2540,7 +2385,6 @@
       <c r="D49" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2549,8 +2393,6 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2574,7 +2416,6 @@
       <c r="D50" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2583,8 +2424,6 @@
       <c r="G50" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2608,7 +2447,6 @@
       <c r="D51" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2617,8 +2455,6 @@
       <c r="G51" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2642,7 +2478,6 @@
       <c r="D52" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2651,8 +2486,6 @@
       <c r="G52" t="n">
         <v>322</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2676,7 +2509,6 @@
       <c r="D53" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2685,8 +2517,6 @@
       <c r="G53" t="n">
         <v>242</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2710,7 +2540,6 @@
       <c r="D54" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2719,8 +2548,6 @@
       <c r="G54" t="n">
         <v>194.5</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2744,7 +2571,6 @@
       <c r="D55" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2753,8 +2579,6 @@
       <c r="G55" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2778,7 +2602,6 @@
       <c r="D56" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2787,8 +2610,6 @@
       <c r="G56" t="n">
         <v>132.5</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2812,7 +2633,6 @@
       <c r="D57" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2821,8 +2641,6 @@
       <c r="G57" t="n">
         <v>101.3</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2846,7 +2664,6 @@
       <c r="D58" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2855,8 +2672,6 @@
       <c r="G58" t="n">
         <v>87</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2880,7 +2695,6 @@
       <c r="D59" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2889,8 +2703,6 @@
       <c r="G59" t="n">
         <v>80</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2914,7 +2726,6 @@
       <c r="D60" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2923,8 +2734,6 @@
       <c r="G60" t="n">
         <v>74</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2948,7 +2757,6 @@
       <c r="D61" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2957,8 +2765,6 @@
       <c r="G61" t="n">
         <v>72</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2982,7 +2788,6 @@
       <c r="D62" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2991,8 +2796,6 @@
       <c r="G62" t="n">
         <v>72</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3016,7 +2819,6 @@
       <c r="D63" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3025,8 +2827,6 @@
       <c r="G63" t="n">
         <v>52.5</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3050,7 +2850,6 @@
       <c r="D64" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3059,8 +2858,6 @@
       <c r="G64" t="n">
         <v>36</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3084,7 +2881,6 @@
       <c r="D65" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3093,8 +2889,6 @@
       <c r="G65" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3118,7 +2912,6 @@
       <c r="D66" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3127,8 +2920,6 @@
       <c r="G66" t="n">
         <v>20</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3152,7 +2943,6 @@
       <c r="D67" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3161,8 +2951,6 @@
       <c r="G67" t="n">
         <v>20</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3186,7 +2974,6 @@
       <c r="D68" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3195,8 +2982,6 @@
       <c r="G68" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3220,7 +3005,6 @@
       <c r="D69" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3229,8 +3013,6 @@
       <c r="G69" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3254,7 +3036,6 @@
       <c r="D70" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3263,8 +3044,6 @@
       <c r="G70" t="n">
         <v>322</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3288,7 +3067,6 @@
       <c r="D71" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3297,8 +3075,6 @@
       <c r="G71" t="n">
         <v>242</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3322,7 +3098,6 @@
       <c r="D72" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3331,8 +3106,6 @@
       <c r="G72" t="n">
         <v>194.5</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3356,7 +3129,6 @@
       <c r="D73" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -3365,8 +3137,6 @@
       <c r="G73" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3390,7 +3160,6 @@
       <c r="D74" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -3399,8 +3168,6 @@
       <c r="G74" t="n">
         <v>132.5</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3424,7 +3191,6 @@
       <c r="D75" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -3433,8 +3199,6 @@
       <c r="G75" t="n">
         <v>101.3</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3458,7 +3222,6 @@
       <c r="D76" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -3467,8 +3230,6 @@
       <c r="G76" t="n">
         <v>87</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3492,7 +3253,6 @@
       <c r="D77" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -3501,8 +3261,6 @@
       <c r="G77" t="n">
         <v>80</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3526,7 +3284,6 @@
       <c r="D78" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -3535,8 +3292,6 @@
       <c r="G78" t="n">
         <v>74</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3560,7 +3315,6 @@
       <c r="D79" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -3569,8 +3323,6 @@
       <c r="G79" t="n">
         <v>72</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3594,7 +3346,6 @@
       <c r="D80" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -3603,8 +3354,6 @@
       <c r="G80" t="n">
         <v>72</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3628,7 +3377,6 @@
       <c r="D81" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3637,8 +3385,6 @@
       <c r="G81" t="n">
         <v>52.5</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3662,7 +3408,6 @@
       <c r="D82" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3671,8 +3416,6 @@
       <c r="G82" t="n">
         <v>36</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3696,7 +3439,6 @@
       <c r="D83" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3705,8 +3447,6 @@
       <c r="G83" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3730,7 +3470,6 @@
       <c r="D84" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3739,8 +3478,6 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3764,7 +3501,6 @@
       <c r="D85" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3773,8 +3509,6 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3798,7 +3532,6 @@
       <c r="D86" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3807,8 +3540,6 @@
       <c r="G86" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3832,7 +3563,6 @@
       <c r="D87" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -3841,8 +3571,6 @@
       <c r="G87" t="n">
         <v>100</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3866,7 +3594,6 @@
       <c r="D88" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -3875,8 +3602,6 @@
       <c r="G88" t="n">
         <v>80</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3900,7 +3625,6 @@
       <c r="D89" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -3909,8 +3633,6 @@
       <c r="G89" t="n">
         <v>60</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3934,7 +3656,6 @@
       <c r="D90" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -3943,8 +3664,6 @@
       <c r="G90" t="n">
         <v>50</v>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3968,7 +3687,6 @@
       <c r="D91" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -3977,8 +3695,6 @@
       <c r="G91" t="n">
         <v>40</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4002,7 +3718,6 @@
       <c r="D92" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4011,8 +3726,6 @@
       <c r="G92" t="n">
         <v>30</v>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4036,7 +3749,6 @@
       <c r="D93" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4045,8 +3757,6 @@
       <c r="G93" t="n">
         <v>20</v>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4070,7 +3780,6 @@
       <c r="D94" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -4079,8 +3788,6 @@
       <c r="G94" t="n">
         <v>20</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4104,7 +3811,6 @@
       <c r="D95" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -4113,8 +3819,6 @@
       <c r="G95" t="n">
         <v>20</v>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4138,7 +3842,6 @@
       <c r="D96" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -4147,8 +3850,6 @@
       <c r="G96" t="n">
         <v>24.3901</v>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4172,7 +3873,6 @@
       <c r="D97" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -4181,8 +3881,6 @@
       <c r="G97" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4206,7 +3904,6 @@
       <c r="D98" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -4215,8 +3912,6 @@
       <c r="G98" t="n">
         <v>322</v>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4240,7 +3935,6 @@
       <c r="D99" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -4249,8 +3943,6 @@
       <c r="G99" t="n">
         <v>242</v>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4274,7 +3966,6 @@
       <c r="D100" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -4283,8 +3974,6 @@
       <c r="G100" t="n">
         <v>194.5</v>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4308,7 +3997,6 @@
       <c r="D101" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4317,8 +4005,6 @@
       <c r="G101" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4342,7 +4028,6 @@
       <c r="D102" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4351,8 +4036,6 @@
       <c r="G102" t="n">
         <v>132.5</v>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4376,7 +4059,6 @@
       <c r="D103" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4385,8 +4067,6 @@
       <c r="G103" t="n">
         <v>101.3</v>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4410,7 +4090,6 @@
       <c r="D104" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4419,8 +4098,6 @@
       <c r="G104" t="n">
         <v>87</v>
       </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4444,7 +4121,6 @@
       <c r="D105" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -4453,8 +4129,6 @@
       <c r="G105" t="n">
         <v>80</v>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4478,7 +4152,6 @@
       <c r="D106" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -4487,8 +4160,6 @@
       <c r="G106" t="n">
         <v>74</v>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4512,7 +4183,6 @@
       <c r="D107" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -4521,8 +4191,6 @@
       <c r="G107" t="n">
         <v>72</v>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4546,7 +4214,6 @@
       <c r="D108" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -4555,8 +4222,6 @@
       <c r="G108" t="n">
         <v>72</v>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4580,7 +4245,6 @@
       <c r="D109" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -4589,8 +4253,6 @@
       <c r="G109" t="n">
         <v>52.5</v>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4614,7 +4276,6 @@
       <c r="D110" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -4623,8 +4284,6 @@
       <c r="G110" t="n">
         <v>36</v>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4648,7 +4307,6 @@
       <c r="D111" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -4657,8 +4315,6 @@
       <c r="G111" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4682,7 +4338,6 @@
       <c r="D112" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -4691,8 +4346,6 @@
       <c r="G112" t="n">
         <v>20</v>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4716,7 +4369,6 @@
       <c r="D113" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -4725,8 +4377,6 @@
       <c r="G113" t="n">
         <v>20</v>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4750,7 +4400,6 @@
       <c r="D114" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -4759,8 +4408,6 @@
       <c r="G114" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4784,7 +4431,6 @@
       <c r="D115" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -4793,8 +4439,6 @@
       <c r="G115" t="n">
         <v>100</v>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4818,7 +4462,6 @@
       <c r="D116" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -4827,8 +4470,6 @@
       <c r="G116" t="n">
         <v>80</v>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4852,7 +4493,6 @@
       <c r="D117" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -4861,8 +4501,6 @@
       <c r="G117" t="n">
         <v>60</v>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4886,7 +4524,6 @@
       <c r="D118" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -4895,8 +4532,6 @@
       <c r="G118" t="n">
         <v>50</v>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4920,7 +4555,6 @@
       <c r="D119" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -4929,8 +4563,6 @@
       <c r="G119" t="n">
         <v>40</v>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4954,7 +4586,6 @@
       <c r="D120" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4963,8 +4594,6 @@
       <c r="G120" t="n">
         <v>30</v>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4988,7 +4617,6 @@
       <c r="D121" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4997,8 +4625,6 @@
       <c r="G121" t="n">
         <v>20</v>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5022,7 +4648,6 @@
       <c r="D122" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -5031,8 +4656,6 @@
       <c r="G122" t="n">
         <v>20</v>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5056,7 +4679,6 @@
       <c r="D123" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -5065,8 +4687,6 @@
       <c r="G123" t="n">
         <v>20</v>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5090,7 +4710,6 @@
       <c r="D124" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -5099,8 +4718,6 @@
       <c r="G124" t="n">
         <v>24.3901</v>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5124,7 +4741,6 @@
       <c r="D125" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -5133,8 +4749,6 @@
       <c r="G125" t="n">
         <v>11.7886</v>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5158,7 +4772,6 @@
       <c r="D126" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -5167,8 +4780,6 @@
       <c r="G126" t="n">
         <v>9236.4177</v>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5192,7 +4803,6 @@
       <c r="D127" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -5201,8 +4811,6 @@
       <c r="G127" t="n">
         <v>3220</v>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5226,7 +4834,6 @@
       <c r="D128" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -5235,8 +4842,6 @@
       <c r="G128" t="n">
         <v>3102</v>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5260,7 +4865,6 @@
       <c r="D129" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -5269,8 +4873,6 @@
       <c r="G129" t="n">
         <v>2960</v>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5294,7 +4896,6 @@
       <c r="D130" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -5303,8 +4904,6 @@
       <c r="G130" t="n">
         <v>2875</v>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5328,7 +4927,6 @@
       <c r="D131" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -5337,8 +4935,6 @@
       <c r="G131" t="n">
         <v>2015</v>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5362,7 +4958,6 @@
       <c r="D132" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -5371,8 +4966,6 @@
       <c r="G132" t="n">
         <v>1542</v>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5396,7 +4989,6 @@
       <c r="D133" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -5405,8 +4997,6 @@
       <c r="G133" t="n">
         <v>1322</v>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5430,7 +5020,6 @@
       <c r="D134" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5439,8 +5028,6 @@
       <c r="G134" t="n">
         <v>1216</v>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5464,7 +5051,6 @@
       <c r="D135" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -5473,8 +5059,6 @@
       <c r="G135" t="n">
         <v>1125</v>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5498,7 +5082,6 @@
       <c r="D136" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -5507,8 +5090,6 @@
       <c r="G136" t="n">
         <v>1095</v>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5532,7 +5113,6 @@
       <c r="D137" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -5541,8 +5121,6 @@
       <c r="G137" t="n">
         <v>1095</v>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5566,7 +5144,6 @@
       <c r="D138" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -5575,8 +5152,6 @@
       <c r="G138" t="n">
         <v>798</v>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5600,7 +5175,6 @@
       <c r="D139" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -5609,8 +5183,6 @@
       <c r="G139" t="n">
         <v>547</v>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5634,7 +5206,6 @@
       <c r="D140" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -5643,8 +5214,6 @@
       <c r="G140" t="n">
         <v>140</v>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5668,7 +5237,6 @@
       <c r="D141" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -5677,8 +5245,6 @@
       <c r="G141" t="n">
         <v>304</v>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5702,7 +5268,6 @@
       <c r="D142" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -5711,8 +5276,6 @@
       <c r="G142" t="n">
         <v>304</v>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5736,7 +5299,6 @@
       <c r="D143" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -5745,8 +5307,6 @@
       <c r="G143" t="n">
         <v>407</v>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5770,7 +5330,6 @@
       <c r="D144" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5779,8 +5338,6 @@
       <c r="G144" t="n">
         <v>1520</v>
       </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5804,7 +5361,6 @@
       <c r="D145" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -5813,8 +5369,6 @@
       <c r="G145" t="n">
         <v>1216</v>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5838,7 +5392,6 @@
       <c r="D146" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -5847,8 +5400,6 @@
       <c r="G146" t="n">
         <v>912</v>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5872,7 +5423,6 @@
       <c r="D147" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -5881,8 +5431,6 @@
       <c r="G147" t="n">
         <v>760</v>
       </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5906,7 +5454,6 @@
       <c r="D148" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -5915,8 +5462,6 @@
       <c r="G148" t="n">
         <v>608</v>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5940,7 +5485,6 @@
       <c r="D149" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -5949,8 +5493,6 @@
       <c r="G149" t="n">
         <v>456</v>
       </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5974,7 +5516,6 @@
       <c r="D150" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -5983,8 +5524,6 @@
       <c r="G150" t="n">
         <v>304</v>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6008,7 +5547,6 @@
       <c r="D151" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6017,8 +5555,6 @@
       <c r="G151" t="n">
         <v>304</v>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6042,7 +5578,6 @@
       <c r="D152" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6051,8 +5586,6 @@
       <c r="G152" t="n">
         <v>304</v>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6076,7 +5609,6 @@
       <c r="D153" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6085,8 +5617,6 @@
       <c r="G153" t="n">
         <v>370.8394</v>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6110,7 +5640,6 @@
       <c r="D154" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -6119,8 +5648,6 @@
       <c r="G154" t="n">
         <v>179</v>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6144,7 +5671,6 @@
       <c r="D155" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -6153,7 +5679,6 @@
       <c r="G155" t="n">
         <v>803.1668</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>25.2961</v>
       </c>
@@ -6180,7 +5705,6 @@
       <c r="D156" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -6189,7 +5713,6 @@
       <c r="G156" t="n">
         <v>280</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
         <v>8.8187</v>
       </c>
@@ -6216,7 +5739,6 @@
       <c r="D157" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -6225,7 +5747,6 @@
       <c r="G157" t="n">
         <v>270</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
         <v>8.5038</v>
       </c>
@@ -6252,7 +5773,6 @@
       <c r="D158" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -6261,7 +5781,6 @@
       <c r="G158" t="n">
         <v>257.4</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
         <v>8.1069</v>
       </c>
@@ -6288,7 +5807,6 @@
       <c r="D159" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -6297,7 +5815,6 @@
       <c r="G159" t="n">
         <v>250.0615</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
         <v>7.8758</v>
       </c>
@@ -6324,7 +5841,6 @@
       <c r="D160" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -6333,7 +5849,6 @@
       <c r="G160" t="n">
         <v>175.1887</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
         <v>5.5176</v>
       </c>
@@ -6360,7 +5875,6 @@
       <c r="D161" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -6369,7 +5883,6 @@
       <c r="G161" t="n">
         <v>157.1815</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
         <v>4.9505</v>
       </c>
@@ -6396,7 +5909,6 @@
       <c r="D162" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -6405,7 +5917,6 @@
       <c r="G162" t="n">
         <v>134.15</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
         <v>4.2251</v>
       </c>
@@ -6432,7 +5943,6 @@
       <c r="D163" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -6441,7 +5951,6 @@
       <c r="G163" t="n">
         <v>126.3621</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
         <v>3.9798</v>
       </c>
@@ -6468,7 +5977,6 @@
       <c r="D164" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -6477,7 +5985,6 @@
       <c r="G164" t="n">
         <v>114.9389</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>3.62</v>
       </c>
@@ -6504,7 +6011,6 @@
       <c r="D165" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -6513,7 +6019,6 @@
       <c r="G165" t="n">
         <v>69.48</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>2.1883</v>
       </c>
@@ -6540,7 +6045,6 @@
       <c r="D166" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>潘鼎</t>
@@ -6549,7 +6053,6 @@
       <c r="G166" t="n">
         <v>63.2</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>1.9905</v>
       </c>
@@ -6576,7 +6079,6 @@
       <c r="D167" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -6585,7 +6087,6 @@
       <c r="G167" t="n">
         <v>62.8726</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>1.9802</v>
       </c>
@@ -6612,7 +6113,6 @@
       <c r="D168" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -6621,7 +6121,6 @@
       <c r="G168" t="n">
         <v>62.8726</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>1.9802</v>
       </c>
@@ -6648,7 +6147,6 @@
       <c r="D169" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -6657,7 +6155,6 @@
       <c r="G169" t="n">
         <v>47.4</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>1.4929</v>
       </c>
@@ -6684,7 +6181,6 @@
       <c r="D170" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -6693,7 +6189,6 @@
       <c r="G170" t="n">
         <v>46.1846</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>1.4546</v>
       </c>
@@ -6720,7 +6215,6 @@
       <c r="D171" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -6729,7 +6223,6 @@
       <c r="G171" t="n">
         <v>40</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>1.2598</v>
       </c>
@@ -6756,7 +6249,6 @@
       <c r="D172" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6765,7 +6257,6 @@
       <c r="G172" t="n">
         <v>39.2954</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>1.2376</v>
       </c>
@@ -6792,7 +6283,6 @@
       <c r="D173" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>陈志华</t>
@@ -6801,7 +6291,6 @@
       <c r="G173" t="n">
         <v>30.04</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>0.9461000000000001</v>
       </c>
@@ -6828,7 +6317,6 @@
       <c r="D174" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>耿卫东</t>
@@ -6837,7 +6325,6 @@
       <c r="G174" t="n">
         <v>30</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>0.9449</v>
       </c>
@@ -6864,7 +6351,6 @@
       <c r="D175" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6873,7 +6359,6 @@
       <c r="G175" t="n">
         <v>23.5772</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0.7426</v>
       </c>
@@ -6900,7 +6385,6 @@
       <c r="D176" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -6909,7 +6393,6 @@
       <c r="G176" t="n">
         <v>20</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
         <v>0.6299</v>
       </c>
@@ -6936,7 +6419,6 @@
       <c r="D177" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -6945,7 +6427,6 @@
       <c r="G177" t="n">
         <v>19.4081</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>0.6113</v>
       </c>
@@ -6972,7 +6453,6 @@
       <c r="D178" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6981,7 +6461,6 @@
       <c r="G178" t="n">
         <v>15.7182</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0.4951</v>
       </c>
@@ -7008,7 +6487,6 @@
       <c r="D179" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -7017,7 +6495,6 @@
       <c r="G179" t="n">
         <v>15.5625</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>0.4901</v>
       </c>
@@ -7044,7 +6521,6 @@
       <c r="D180" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -7053,7 +6529,6 @@
       <c r="G180" t="n">
         <v>12.0034</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>0.3781</v>
       </c>
@@ -7080,7 +6555,6 @@
       <c r="D181" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -7089,7 +6563,6 @@
       <c r="G181" t="n">
         <v>3.0041</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>0.0946</v>
       </c>
@@ -7116,7 +6589,6 @@
       <c r="D182" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -7125,7 +6597,6 @@
       <c r="G182" t="n">
         <v>2.8079</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
         <v>0.08840000000000001</v>
       </c>
@@ -7152,7 +6623,6 @@
       <c r="D183" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -7161,7 +6631,6 @@
       <c r="G183" t="n">
         <v>2.0654</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
         <v>0.06510000000000001</v>
       </c>
@@ -7188,7 +6657,6 @@
       <c r="D184" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -7197,7 +6665,6 @@
       <c r="G184" t="n">
         <v>0.9699</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>0.0305</v>
       </c>
@@ -7224,7 +6691,6 @@
       <c r="D185" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -7233,7 +6699,6 @@
       <c r="G185" t="n">
         <v>0.1556</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.0049</v>
       </c>
@@ -7242,6 +6707,6314 @@
           <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J164"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴15条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量184条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2408</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6158.9225</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-3446.4699</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>322</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>322</v>
+      </c>
+      <c r="G7" t="n">
+        <v>322</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="G9" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-3535.0134</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>80</v>
+      </c>
+      <c r="H10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H11" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>36</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>87</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>87</v>
+      </c>
+      <c r="G14" t="n">
+        <v>87</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>74</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>74</v>
+      </c>
+      <c r="G15" t="n">
+        <v>74</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>72</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>72</v>
+      </c>
+      <c r="G18" t="n">
+        <v>72</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>72</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>72</v>
+      </c>
+      <c r="G20" t="n">
+        <v>72</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>220</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>220</v>
+      </c>
+      <c r="G21" t="n">
+        <v>220</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1035</v>
+      </c>
+      <c r="G22" t="n">
+        <v>976.7757</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-58.2243</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>322</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>322</v>
+      </c>
+      <c r="G26" t="n">
+        <v>322</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G28" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>80</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>80</v>
+      </c>
+      <c r="G29" t="n">
+        <v>80</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G30" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>20</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>36</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36</v>
+      </c>
+      <c r="G32" t="n">
+        <v>36</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>87</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>87</v>
+      </c>
+      <c r="G33" t="n">
+        <v>87</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>74</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>74</v>
+      </c>
+      <c r="G34" t="n">
+        <v>74</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>72</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>72</v>
+      </c>
+      <c r="G37" t="n">
+        <v>72</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>72</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>72</v>
+      </c>
+      <c r="G39" t="n">
+        <v>72</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>220</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>220</v>
+      </c>
+      <c r="G40" t="n">
+        <v>242</v>
+      </c>
+      <c r="H40" t="n">
+        <v>22</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>976.7757</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>976.7757</v>
+      </c>
+      <c r="G41" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>322</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>322</v>
+      </c>
+      <c r="G45" t="n">
+        <v>322</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G47" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>80</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>80</v>
+      </c>
+      <c r="G48" t="n">
+        <v>80</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G49" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" t="n">
+        <v>20</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>36</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>36</v>
+      </c>
+      <c r="G51" t="n">
+        <v>36</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>87</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>87</v>
+      </c>
+      <c r="G52" t="n">
+        <v>87</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>74</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>74</v>
+      </c>
+      <c r="G53" t="n">
+        <v>74</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>72</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>72</v>
+      </c>
+      <c r="G56" t="n">
+        <v>72</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>72</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>72</v>
+      </c>
+      <c r="G58" t="n">
+        <v>72</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>242</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>242</v>
+      </c>
+      <c r="G59" t="n">
+        <v>242</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="G60" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3156.8427</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-3306.5324</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G63" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="H64" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>322</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>322</v>
+      </c>
+      <c r="G65" t="n">
+        <v>322</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>20</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>20</v>
+      </c>
+      <c r="G66" t="n">
+        <v>20</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G67" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>50</v>
+      </c>
+      <c r="H68" t="n">
+        <v>50</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>30</v>
+      </c>
+      <c r="H69" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>40</v>
+      </c>
+      <c r="H70" t="n">
+        <v>40</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>20</v>
+      </c>
+      <c r="H71" t="n">
+        <v>20</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>80</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>80</v>
+      </c>
+      <c r="G72" t="n">
+        <v>80</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>20</v>
+      </c>
+      <c r="H73" t="n">
+        <v>20</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G74" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>20</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>36</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>36</v>
+      </c>
+      <c r="G76" t="n">
+        <v>36</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>100</v>
+      </c>
+      <c r="H77" t="n">
+        <v>100</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>80</v>
+      </c>
+      <c r="H78" t="n">
+        <v>80</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>20</v>
+      </c>
+      <c r="H79" t="n">
+        <v>20</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>87</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>87</v>
+      </c>
+      <c r="G80" t="n">
+        <v>87</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>74</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>74</v>
+      </c>
+      <c r="G81" t="n">
+        <v>74</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G83" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>72</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>72</v>
+      </c>
+      <c r="G84" t="n">
+        <v>72</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>72</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>72</v>
+      </c>
+      <c r="G86" t="n">
+        <v>72</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3156.8427</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F87" t="n">
+        <v>6907.7652</v>
+      </c>
+      <c r="G87" t="n">
+        <v>3168.6313</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-3739.1339</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G89" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="G90" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>322</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>322</v>
+      </c>
+      <c r="G91" t="n">
+        <v>322</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>20</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>20</v>
+      </c>
+      <c r="G92" t="n">
+        <v>20</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G93" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>50</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>50</v>
+      </c>
+      <c r="G94" t="n">
+        <v>50</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>30</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>30</v>
+      </c>
+      <c r="G95" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>40</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>40</v>
+      </c>
+      <c r="G96" t="n">
+        <v>40</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>20</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>20</v>
+      </c>
+      <c r="G97" t="n">
+        <v>20</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>80</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>80</v>
+      </c>
+      <c r="G98" t="n">
+        <v>80</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>20</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>20</v>
+      </c>
+      <c r="G99" t="n">
+        <v>20</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G100" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>20</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>20</v>
+      </c>
+      <c r="G101" t="n">
+        <v>20</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>36</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>36</v>
+      </c>
+      <c r="G102" t="n">
+        <v>36</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>100</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>100</v>
+      </c>
+      <c r="G103" t="n">
+        <v>100</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>80</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>80</v>
+      </c>
+      <c r="G104" t="n">
+        <v>80</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>20</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>20</v>
+      </c>
+      <c r="G105" t="n">
+        <v>20</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="H106" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>87</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>87</v>
+      </c>
+      <c r="G107" t="n">
+        <v>87</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>74</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>74</v>
+      </c>
+      <c r="G108" t="n">
+        <v>74</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G109" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G110" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>72</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>72</v>
+      </c>
+      <c r="G111" t="n">
+        <v>72</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3168.6313</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F113" t="n">
+        <v>6919.5538</v>
+      </c>
+      <c r="G113" t="n">
+        <v>40237.2571</v>
+      </c>
+      <c r="H113" t="n">
+        <v>33317.7033</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1882.5</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G115" t="n">
+        <v>140</v>
+      </c>
+      <c r="H115" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="G116" t="n">
+        <v>370.8394</v>
+      </c>
+      <c r="H116" t="n">
+        <v>346.4493</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>322</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>322</v>
+      </c>
+      <c r="G117" t="n">
+        <v>3220</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2898</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>20</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>20</v>
+      </c>
+      <c r="G118" t="n">
+        <v>304</v>
+      </c>
+      <c r="H118" t="n">
+        <v>284</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F119" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2875</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-1091.8316</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>50</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>50</v>
+      </c>
+      <c r="G120" t="n">
+        <v>760</v>
+      </c>
+      <c r="H120" t="n">
+        <v>710</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>30</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>30</v>
+      </c>
+      <c r="G121" t="n">
+        <v>456</v>
+      </c>
+      <c r="H121" t="n">
+        <v>426</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>40</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>40</v>
+      </c>
+      <c r="G122" t="n">
+        <v>608</v>
+      </c>
+      <c r="H122" t="n">
+        <v>568</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>20</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>20</v>
+      </c>
+      <c r="G123" t="n">
+        <v>304</v>
+      </c>
+      <c r="H123" t="n">
+        <v>284</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>80</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>80</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1136</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>20</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>20</v>
+      </c>
+      <c r="G125" t="n">
+        <v>304</v>
+      </c>
+      <c r="H125" t="n">
+        <v>284</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G126" t="n">
+        <v>407</v>
+      </c>
+      <c r="H126" t="n">
+        <v>380.2322</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>20</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>20</v>
+      </c>
+      <c r="G127" t="n">
+        <v>304</v>
+      </c>
+      <c r="H127" t="n">
+        <v>284</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>36</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>36</v>
+      </c>
+      <c r="G128" t="n">
+        <v>547</v>
+      </c>
+      <c r="H128" t="n">
+        <v>511</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>100</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>100</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1520</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>80</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>80</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1136</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>20</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>20</v>
+      </c>
+      <c r="G131" t="n">
+        <v>304</v>
+      </c>
+      <c r="H131" t="n">
+        <v>284</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="G132" t="n">
+        <v>179</v>
+      </c>
+      <c r="H132" t="n">
+        <v>167.2114</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>87</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>87</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1322</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1235</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>74</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>74</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1125</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1051</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>798</v>
+      </c>
+      <c r="H135" t="n">
+        <v>745.5</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1542</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1440.7</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>72</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>72</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1023</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2960</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2765.5</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>40237.2571</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F139" t="n">
+        <v>43988.1796</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-40813.1126</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G140" t="n">
+        <v>175.1887</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-1839.8113</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>140</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>140</v>
+      </c>
+      <c r="G141" t="n">
+        <v>12.0034</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-127.9966</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>370.8394</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>370.8394</v>
+      </c>
+      <c r="G142" t="n">
+        <v>15.7182</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-355.1212</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>3220</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3220</v>
+      </c>
+      <c r="G143" t="n">
+        <v>280</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-2940</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>304</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>304</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3.0041</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-300.9959</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>2875</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F145" t="n">
+        <v>6625.9225</v>
+      </c>
+      <c r="G145" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-6375.861</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>760</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>760</v>
+      </c>
+      <c r="G146" t="n">
+        <v>46.1846</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-713.8154</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>456</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>456</v>
+      </c>
+      <c r="G147" t="n">
+        <v>15.5625</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-440.4375</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>608</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>608</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-607.0300999999999</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>304</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>304</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-303.8444</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1216</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1216</v>
+      </c>
+      <c r="G150" t="n">
+        <v>126.3621</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-1089.6379</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>304</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>304</v>
+      </c>
+      <c r="G151" t="n">
+        <v>39.2954</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-264.7046</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>407</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>407</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2.0654</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-404.9346</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>304</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>304</v>
+      </c>
+      <c r="G153" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="H153" t="n">
+        <v>-284.5919</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>547</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>547</v>
+      </c>
+      <c r="G154" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H154" t="n">
+        <v>-499.6</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1520</v>
+      </c>
+      <c r="G155" t="n">
+        <v>157.1815</v>
+      </c>
+      <c r="H155" t="n">
+        <v>-1362.8185</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>潘鼎</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="H156" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1216</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1216</v>
+      </c>
+      <c r="G157" t="n">
+        <v>62.8726</v>
+      </c>
+      <c r="H157" t="n">
+        <v>-1153.1274</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>304</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>304</v>
+      </c>
+      <c r="G158" t="n">
+        <v>23.5772</v>
+      </c>
+      <c r="H158" t="n">
+        <v>-280.4228</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>耿卫东</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>30</v>
+      </c>
+      <c r="H159" t="n">
+        <v>30</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>179</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>179</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>-179</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1322</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1322</v>
+      </c>
+      <c r="G161" t="n">
+        <v>114.9389</v>
+      </c>
+      <c r="H161" t="n">
+        <v>-1207.0611</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1125</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1125</v>
+      </c>
+      <c r="G162" t="n">
+        <v>40</v>
+      </c>
+      <c r="H162" t="n">
+        <v>-1085</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>798</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="n">
+        <v>798</v>
+      </c>
+      <c r="G163" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="H163" t="n">
+        <v>-728.52</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1542</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1542</v>
+      </c>
+      <c r="G164" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="H164" t="n">
+        <v>-1407.85</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,6 +474,7 @@
       <c r="E2" t="n">
         <v>13500</v>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -501,6 +501,7 @@
       <c r="E3" t="n">
         <v>13500</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -527,6 +528,7 @@
       <c r="E4" t="n">
         <v>13500</v>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -553,6 +555,7 @@
       <c r="E5" t="n">
         <v>13500</v>
       </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -579,6 +582,7 @@
       <c r="E6" t="n">
         <v>13500</v>
       </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -605,6 +609,7 @@
       <c r="E7" t="n">
         <v>13500</v>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -631,6 +636,7 @@
       <c r="E8" t="n">
         <v>13500</v>
       </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -657,6 +663,7 @@
       <c r="E9" t="n">
         <v>13500</v>
       </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -683,6 +690,7 @@
       <c r="E10" t="n">
         <v>13500</v>
       </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -709,6 +717,7 @@
       <c r="E11" t="n">
         <v>13500</v>
       </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -735,6 +744,7 @@
       <c r="E12" t="n">
         <v>13500</v>
       </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -761,6 +771,7 @@
       <c r="E13" t="n">
         <v>13500</v>
       </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -787,6 +798,7 @@
       <c r="E14" t="n">
         <v>13500</v>
       </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -813,6 +825,7 @@
       <c r="E15" t="n">
         <v>13500</v>
       </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -839,6 +852,7 @@
       <c r="E16" t="n">
         <v>13500</v>
       </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -928,6 +942,7 @@
       <c r="D2" t="n">
         <v>2408</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -936,6 +951,8 @@
       <c r="G2" t="n">
         <v>1035</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -959,6 +976,7 @@
       <c r="D3" t="n">
         <v>2408</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -967,6 +985,8 @@
       <c r="G3" t="n">
         <v>322</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -990,6 +1010,7 @@
       <c r="D4" t="n">
         <v>2408</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -998,6 +1019,8 @@
       <c r="G4" t="n">
         <v>220</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1021,6 +1044,7 @@
       <c r="D5" t="n">
         <v>2408</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1029,6 +1053,8 @@
       <c r="G5" t="n">
         <v>194.5</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1052,6 +1078,7 @@
       <c r="D6" t="n">
         <v>2408</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1060,6 +1087,8 @@
       <c r="G6" t="n">
         <v>132.5</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1083,6 +1112,7 @@
       <c r="D7" t="n">
         <v>2408</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1091,6 +1121,8 @@
       <c r="G7" t="n">
         <v>101.3</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1114,6 +1146,7 @@
       <c r="D8" t="n">
         <v>2408</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1122,6 +1155,8 @@
       <c r="G8" t="n">
         <v>87</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1145,6 +1180,7 @@
       <c r="D9" t="n">
         <v>2408</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1153,6 +1189,8 @@
       <c r="G9" t="n">
         <v>52.5</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1176,6 +1214,7 @@
       <c r="D10" t="n">
         <v>2408</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1184,6 +1223,8 @@
       <c r="G10" t="n">
         <v>36</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1207,6 +1248,7 @@
       <c r="D11" t="n">
         <v>2408</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1215,6 +1257,8 @@
       <c r="G11" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1238,6 +1282,7 @@
       <c r="D12" t="n">
         <v>2408</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1246,6 +1291,8 @@
       <c r="G12" t="n">
         <v>72</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1269,6 +1316,7 @@
       <c r="D13" t="n">
         <v>2408</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1277,6 +1325,8 @@
       <c r="G13" t="n">
         <v>72</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1300,6 +1350,7 @@
       <c r="D14" t="n">
         <v>2408</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1308,6 +1359,8 @@
       <c r="G14" t="n">
         <v>74</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1331,6 +1384,7 @@
       <c r="D15" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1339,6 +1393,8 @@
       <c r="G15" t="n">
         <v>976.7757</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1362,6 +1418,7 @@
       <c r="D16" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1370,6 +1427,8 @@
       <c r="G16" t="n">
         <v>322</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1393,6 +1452,7 @@
       <c r="D17" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1401,6 +1461,8 @@
       <c r="G17" t="n">
         <v>220</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1424,6 +1486,7 @@
       <c r="D18" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1432,6 +1495,8 @@
       <c r="G18" t="n">
         <v>194.5</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1455,6 +1520,7 @@
       <c r="D19" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -1463,6 +1529,8 @@
       <c r="G19" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1486,6 +1554,7 @@
       <c r="D20" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1494,6 +1563,8 @@
       <c r="G20" t="n">
         <v>132.5</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1517,6 +1588,7 @@
       <c r="D21" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1525,6 +1597,8 @@
       <c r="G21" t="n">
         <v>101.3</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1548,6 +1622,7 @@
       <c r="D22" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1556,6 +1631,8 @@
       <c r="G22" t="n">
         <v>87</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1579,6 +1656,7 @@
       <c r="D23" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -1587,6 +1665,8 @@
       <c r="G23" t="n">
         <v>80</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1610,6 +1690,7 @@
       <c r="D24" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1618,6 +1699,8 @@
       <c r="G24" t="n">
         <v>74</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1641,6 +1724,7 @@
       <c r="D25" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1649,6 +1733,8 @@
       <c r="G25" t="n">
         <v>72</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1672,6 +1758,7 @@
       <c r="D26" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1680,6 +1767,8 @@
       <c r="G26" t="n">
         <v>72</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1703,6 +1792,7 @@
       <c r="D27" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1711,6 +1801,8 @@
       <c r="G27" t="n">
         <v>52.5</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1734,6 +1826,7 @@
       <c r="D28" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1742,6 +1835,8 @@
       <c r="G28" t="n">
         <v>36</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1765,6 +1860,7 @@
       <c r="D29" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1773,6 +1869,8 @@
       <c r="G29" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1796,6 +1894,7 @@
       <c r="D30" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -1804,6 +1903,8 @@
       <c r="G30" t="n">
         <v>20</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1827,6 +1928,7 @@
       <c r="D31" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -1835,6 +1937,8 @@
       <c r="G31" t="n">
         <v>20</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1858,6 +1962,7 @@
       <c r="D32" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -1866,6 +1971,8 @@
       <c r="G32" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1889,6 +1996,7 @@
       <c r="D33" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1897,6 +2005,8 @@
       <c r="G33" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1920,6 +2030,7 @@
       <c r="D34" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1928,6 +2039,8 @@
       <c r="G34" t="n">
         <v>322</v>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1951,6 +2064,7 @@
       <c r="D35" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1959,6 +2073,8 @@
       <c r="G35" t="n">
         <v>242</v>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1982,6 +2098,7 @@
       <c r="D36" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1990,6 +2107,8 @@
       <c r="G36" t="n">
         <v>194.5</v>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2013,6 +2132,7 @@
       <c r="D37" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2021,6 +2141,8 @@
       <c r="G37" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2044,6 +2166,7 @@
       <c r="D38" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2052,6 +2175,8 @@
       <c r="G38" t="n">
         <v>132.5</v>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2075,6 +2200,7 @@
       <c r="D39" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2083,6 +2209,8 @@
       <c r="G39" t="n">
         <v>101.3</v>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2106,6 +2234,7 @@
       <c r="D40" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2114,6 +2243,8 @@
       <c r="G40" t="n">
         <v>87</v>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2137,6 +2268,7 @@
       <c r="D41" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2145,6 +2277,8 @@
       <c r="G41" t="n">
         <v>80</v>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2168,6 +2302,7 @@
       <c r="D42" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2176,6 +2311,8 @@
       <c r="G42" t="n">
         <v>74</v>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2199,6 +2336,7 @@
       <c r="D43" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2207,6 +2345,8 @@
       <c r="G43" t="n">
         <v>72</v>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2230,6 +2370,7 @@
       <c r="D44" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2238,6 +2379,8 @@
       <c r="G44" t="n">
         <v>72</v>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2261,6 +2404,7 @@
       <c r="D45" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2269,6 +2413,8 @@
       <c r="G45" t="n">
         <v>52.5</v>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2292,6 +2438,7 @@
       <c r="D46" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2300,6 +2447,8 @@
       <c r="G46" t="n">
         <v>36</v>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2323,6 +2472,7 @@
       <c r="D47" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2331,6 +2481,8 @@
       <c r="G47" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2354,6 +2506,7 @@
       <c r="D48" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2362,6 +2515,8 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2385,6 +2540,7 @@
       <c r="D49" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2393,6 +2549,8 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2416,6 +2574,7 @@
       <c r="D50" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2424,6 +2583,8 @@
       <c r="G50" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2447,6 +2608,7 @@
       <c r="D51" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2455,6 +2617,8 @@
       <c r="G51" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2478,6 +2642,7 @@
       <c r="D52" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2486,6 +2651,8 @@
       <c r="G52" t="n">
         <v>322</v>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2509,6 +2676,7 @@
       <c r="D53" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2517,6 +2685,8 @@
       <c r="G53" t="n">
         <v>242</v>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2540,6 +2710,7 @@
       <c r="D54" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2548,6 +2719,8 @@
       <c r="G54" t="n">
         <v>194.5</v>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2571,6 +2744,7 @@
       <c r="D55" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2579,6 +2753,8 @@
       <c r="G55" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2602,6 +2778,7 @@
       <c r="D56" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2610,6 +2787,8 @@
       <c r="G56" t="n">
         <v>132.5</v>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2633,6 +2812,7 @@
       <c r="D57" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2641,6 +2821,8 @@
       <c r="G57" t="n">
         <v>101.3</v>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2664,6 +2846,7 @@
       <c r="D58" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2672,6 +2855,8 @@
       <c r="G58" t="n">
         <v>87</v>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2695,6 +2880,7 @@
       <c r="D59" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2703,6 +2889,8 @@
       <c r="G59" t="n">
         <v>80</v>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2726,6 +2914,7 @@
       <c r="D60" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2734,6 +2923,8 @@
       <c r="G60" t="n">
         <v>74</v>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2757,6 +2948,7 @@
       <c r="D61" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2765,6 +2957,8 @@
       <c r="G61" t="n">
         <v>72</v>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2788,6 +2982,7 @@
       <c r="D62" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2796,6 +2991,8 @@
       <c r="G62" t="n">
         <v>72</v>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2819,6 +3016,7 @@
       <c r="D63" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2827,6 +3025,8 @@
       <c r="G63" t="n">
         <v>52.5</v>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2850,6 +3050,7 @@
       <c r="D64" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2858,6 +3059,8 @@
       <c r="G64" t="n">
         <v>36</v>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2881,6 +3084,7 @@
       <c r="D65" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2889,6 +3093,8 @@
       <c r="G65" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2912,6 +3118,7 @@
       <c r="D66" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2920,6 +3127,8 @@
       <c r="G66" t="n">
         <v>20</v>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2943,6 +3152,7 @@
       <c r="D67" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2951,6 +3161,8 @@
       <c r="G67" t="n">
         <v>20</v>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2974,6 +3186,7 @@
       <c r="D68" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2982,6 +3195,8 @@
       <c r="G68" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3005,6 +3220,7 @@
       <c r="D69" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3013,6 +3229,8 @@
       <c r="G69" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3036,6 +3254,7 @@
       <c r="D70" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3044,6 +3263,8 @@
       <c r="G70" t="n">
         <v>322</v>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3067,6 +3288,7 @@
       <c r="D71" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3075,6 +3297,8 @@
       <c r="G71" t="n">
         <v>242</v>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3098,6 +3322,7 @@
       <c r="D72" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3106,6 +3331,8 @@
       <c r="G72" t="n">
         <v>194.5</v>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3129,6 +3356,7 @@
       <c r="D73" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -3137,6 +3365,8 @@
       <c r="G73" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3160,6 +3390,7 @@
       <c r="D74" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -3168,6 +3399,8 @@
       <c r="G74" t="n">
         <v>132.5</v>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3191,6 +3424,7 @@
       <c r="D75" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -3199,6 +3433,8 @@
       <c r="G75" t="n">
         <v>101.3</v>
       </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3222,6 +3458,7 @@
       <c r="D76" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -3230,6 +3467,8 @@
       <c r="G76" t="n">
         <v>87</v>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3253,6 +3492,7 @@
       <c r="D77" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -3261,6 +3501,8 @@
       <c r="G77" t="n">
         <v>80</v>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3284,6 +3526,7 @@
       <c r="D78" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -3292,6 +3535,8 @@
       <c r="G78" t="n">
         <v>74</v>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3315,6 +3560,7 @@
       <c r="D79" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -3323,6 +3569,8 @@
       <c r="G79" t="n">
         <v>72</v>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3346,6 +3594,7 @@
       <c r="D80" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -3354,6 +3603,8 @@
       <c r="G80" t="n">
         <v>72</v>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3377,6 +3628,7 @@
       <c r="D81" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3385,6 +3637,8 @@
       <c r="G81" t="n">
         <v>52.5</v>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3408,6 +3662,7 @@
       <c r="D82" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3416,6 +3671,8 @@
       <c r="G82" t="n">
         <v>36</v>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3439,6 +3696,7 @@
       <c r="D83" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3447,6 +3705,8 @@
       <c r="G83" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3470,6 +3730,7 @@
       <c r="D84" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3478,6 +3739,8 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3501,6 +3764,7 @@
       <c r="D85" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3509,6 +3773,8 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3532,6 +3798,7 @@
       <c r="D86" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3540,6 +3807,8 @@
       <c r="G86" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3563,6 +3832,7 @@
       <c r="D87" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -3571,6 +3841,8 @@
       <c r="G87" t="n">
         <v>100</v>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3594,6 +3866,7 @@
       <c r="D88" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -3602,6 +3875,8 @@
       <c r="G88" t="n">
         <v>80</v>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3625,6 +3900,7 @@
       <c r="D89" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -3633,6 +3909,8 @@
       <c r="G89" t="n">
         <v>60</v>
       </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3656,6 +3934,7 @@
       <c r="D90" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -3664,6 +3943,8 @@
       <c r="G90" t="n">
         <v>50</v>
       </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3687,6 +3968,7 @@
       <c r="D91" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -3695,6 +3977,8 @@
       <c r="G91" t="n">
         <v>40</v>
       </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3718,6 +4002,7 @@
       <c r="D92" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -3726,6 +4011,8 @@
       <c r="G92" t="n">
         <v>30</v>
       </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3749,6 +4036,7 @@
       <c r="D93" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -3757,6 +4045,8 @@
       <c r="G93" t="n">
         <v>20</v>
       </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3780,6 +4070,7 @@
       <c r="D94" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -3788,6 +4079,8 @@
       <c r="G94" t="n">
         <v>20</v>
       </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3811,6 +4104,7 @@
       <c r="D95" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -3819,6 +4113,8 @@
       <c r="G95" t="n">
         <v>20</v>
       </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3842,6 +4138,7 @@
       <c r="D96" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -3850,6 +4147,8 @@
       <c r="G96" t="n">
         <v>24.3901</v>
       </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3873,6 +4172,7 @@
       <c r="D97" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3881,6 +4181,8 @@
       <c r="G97" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3904,6 +4206,7 @@
       <c r="D98" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3912,6 +4215,8 @@
       <c r="G98" t="n">
         <v>322</v>
       </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3935,6 +4240,7 @@
       <c r="D99" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3943,6 +4249,8 @@
       <c r="G99" t="n">
         <v>242</v>
       </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3966,6 +4274,7 @@
       <c r="D100" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3974,6 +4283,8 @@
       <c r="G100" t="n">
         <v>194.5</v>
       </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3997,6 +4308,7 @@
       <c r="D101" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4005,6 +4317,8 @@
       <c r="G101" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4028,6 +4342,7 @@
       <c r="D102" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4036,6 +4351,8 @@
       <c r="G102" t="n">
         <v>132.5</v>
       </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4059,6 +4376,7 @@
       <c r="D103" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4067,6 +4385,8 @@
       <c r="G103" t="n">
         <v>101.3</v>
       </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4090,6 +4410,7 @@
       <c r="D104" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4098,6 +4419,8 @@
       <c r="G104" t="n">
         <v>87</v>
       </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4121,6 +4444,7 @@
       <c r="D105" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -4129,6 +4453,8 @@
       <c r="G105" t="n">
         <v>80</v>
       </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4152,6 +4478,7 @@
       <c r="D106" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -4160,6 +4487,8 @@
       <c r="G106" t="n">
         <v>74</v>
       </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4183,6 +4512,7 @@
       <c r="D107" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -4191,6 +4521,8 @@
       <c r="G107" t="n">
         <v>72</v>
       </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4214,6 +4546,7 @@
       <c r="D108" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -4222,6 +4555,8 @@
       <c r="G108" t="n">
         <v>72</v>
       </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4245,6 +4580,7 @@
       <c r="D109" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -4253,6 +4589,8 @@
       <c r="G109" t="n">
         <v>52.5</v>
       </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4276,6 +4614,7 @@
       <c r="D110" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -4284,6 +4623,8 @@
       <c r="G110" t="n">
         <v>36</v>
       </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4307,6 +4648,7 @@
       <c r="D111" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -4315,6 +4657,8 @@
       <c r="G111" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4338,6 +4682,7 @@
       <c r="D112" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -4346,6 +4691,8 @@
       <c r="G112" t="n">
         <v>20</v>
       </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4369,6 +4716,7 @@
       <c r="D113" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -4377,6 +4725,8 @@
       <c r="G113" t="n">
         <v>20</v>
       </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4400,6 +4750,7 @@
       <c r="D114" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -4408,6 +4759,8 @@
       <c r="G114" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4431,6 +4784,7 @@
       <c r="D115" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -4439,6 +4793,8 @@
       <c r="G115" t="n">
         <v>100</v>
       </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4462,6 +4818,7 @@
       <c r="D116" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -4470,6 +4827,8 @@
       <c r="G116" t="n">
         <v>80</v>
       </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4493,6 +4852,7 @@
       <c r="D117" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -4501,6 +4861,8 @@
       <c r="G117" t="n">
         <v>60</v>
       </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4524,6 +4886,7 @@
       <c r="D118" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -4532,6 +4895,8 @@
       <c r="G118" t="n">
         <v>50</v>
       </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4555,6 +4920,7 @@
       <c r="D119" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -4563,6 +4929,8 @@
       <c r="G119" t="n">
         <v>40</v>
       </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4586,6 +4954,7 @@
       <c r="D120" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4594,6 +4963,8 @@
       <c r="G120" t="n">
         <v>30</v>
       </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4617,6 +4988,7 @@
       <c r="D121" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4625,6 +4997,8 @@
       <c r="G121" t="n">
         <v>20</v>
       </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4648,6 +5022,7 @@
       <c r="D122" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -4656,6 +5031,8 @@
       <c r="G122" t="n">
         <v>20</v>
       </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4679,6 +5056,7 @@
       <c r="D123" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -4687,6 +5065,8 @@
       <c r="G123" t="n">
         <v>20</v>
       </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4710,6 +5090,7 @@
       <c r="D124" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -4718,6 +5099,8 @@
       <c r="G124" t="n">
         <v>24.3901</v>
       </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4741,6 +5124,7 @@
       <c r="D125" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -4749,6 +5133,8 @@
       <c r="G125" t="n">
         <v>11.7886</v>
       </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4772,6 +5158,7 @@
       <c r="D126" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -4780,6 +5167,8 @@
       <c r="G126" t="n">
         <v>9236.4177</v>
       </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4803,6 +5192,7 @@
       <c r="D127" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -4811,6 +5201,8 @@
       <c r="G127" t="n">
         <v>3220</v>
       </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4834,6 +5226,7 @@
       <c r="D128" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -4842,6 +5235,8 @@
       <c r="G128" t="n">
         <v>3102</v>
       </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4865,6 +5260,7 @@
       <c r="D129" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -4873,6 +5269,8 @@
       <c r="G129" t="n">
         <v>2960</v>
       </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4896,6 +5294,7 @@
       <c r="D130" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4904,6 +5303,8 @@
       <c r="G130" t="n">
         <v>2875</v>
       </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4927,6 +5328,7 @@
       <c r="D131" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4935,6 +5337,8 @@
       <c r="G131" t="n">
         <v>2015</v>
       </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4958,6 +5362,7 @@
       <c r="D132" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4966,6 +5371,8 @@
       <c r="G132" t="n">
         <v>1542</v>
       </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4989,6 +5396,7 @@
       <c r="D133" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4997,6 +5405,8 @@
       <c r="G133" t="n">
         <v>1322</v>
       </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5020,6 +5430,7 @@
       <c r="D134" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5028,6 +5439,8 @@
       <c r="G134" t="n">
         <v>1216</v>
       </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5051,6 +5464,7 @@
       <c r="D135" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -5059,6 +5473,8 @@
       <c r="G135" t="n">
         <v>1125</v>
       </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5082,6 +5498,7 @@
       <c r="D136" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -5090,6 +5507,8 @@
       <c r="G136" t="n">
         <v>1095</v>
       </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5113,6 +5532,7 @@
       <c r="D137" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -5121,6 +5541,8 @@
       <c r="G137" t="n">
         <v>1095</v>
       </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5144,6 +5566,7 @@
       <c r="D138" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -5152,6 +5575,8 @@
       <c r="G138" t="n">
         <v>798</v>
       </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5175,6 +5600,7 @@
       <c r="D139" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -5183,6 +5609,8 @@
       <c r="G139" t="n">
         <v>547</v>
       </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5206,6 +5634,7 @@
       <c r="D140" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -5214,6 +5643,8 @@
       <c r="G140" t="n">
         <v>140</v>
       </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5237,6 +5668,7 @@
       <c r="D141" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -5245,6 +5677,8 @@
       <c r="G141" t="n">
         <v>304</v>
       </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5268,6 +5702,7 @@
       <c r="D142" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -5276,6 +5711,8 @@
       <c r="G142" t="n">
         <v>304</v>
       </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5299,6 +5736,7 @@
       <c r="D143" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -5307,6 +5745,8 @@
       <c r="G143" t="n">
         <v>407</v>
       </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5330,6 +5770,7 @@
       <c r="D144" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5338,6 +5779,8 @@
       <c r="G144" t="n">
         <v>1520</v>
       </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5361,6 +5804,7 @@
       <c r="D145" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -5369,6 +5813,8 @@
       <c r="G145" t="n">
         <v>1216</v>
       </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5392,6 +5838,7 @@
       <c r="D146" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -5400,6 +5847,8 @@
       <c r="G146" t="n">
         <v>912</v>
       </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5423,6 +5872,7 @@
       <c r="D147" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -5431,6 +5881,8 @@
       <c r="G147" t="n">
         <v>760</v>
       </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5454,6 +5906,7 @@
       <c r="D148" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -5462,6 +5915,8 @@
       <c r="G148" t="n">
         <v>608</v>
       </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5485,6 +5940,7 @@
       <c r="D149" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -5493,6 +5949,8 @@
       <c r="G149" t="n">
         <v>456</v>
       </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5516,6 +5974,7 @@
       <c r="D150" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -5524,6 +5983,8 @@
       <c r="G150" t="n">
         <v>304</v>
       </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5547,6 +6008,7 @@
       <c r="D151" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -5555,6 +6017,8 @@
       <c r="G151" t="n">
         <v>304</v>
       </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5578,6 +6042,7 @@
       <c r="D152" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -5586,6 +6051,8 @@
       <c r="G152" t="n">
         <v>304</v>
       </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5609,6 +6076,7 @@
       <c r="D153" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -5617,6 +6085,8 @@
       <c r="G153" t="n">
         <v>370.8394</v>
       </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5640,6 +6110,7 @@
       <c r="D154" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -5648,6 +6119,8 @@
       <c r="G154" t="n">
         <v>179</v>
       </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5671,6 +6144,7 @@
       <c r="D155" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -5679,6 +6153,7 @@
       <c r="G155" t="n">
         <v>803.1668</v>
       </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>25.2961</v>
       </c>
@@ -5705,6 +6180,7 @@
       <c r="D156" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -5713,6 +6189,7 @@
       <c r="G156" t="n">
         <v>280</v>
       </c>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
         <v>8.8187</v>
       </c>
@@ -5739,6 +6216,7 @@
       <c r="D157" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -5747,6 +6225,7 @@
       <c r="G157" t="n">
         <v>270</v>
       </c>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
         <v>8.5038</v>
       </c>
@@ -5773,6 +6252,7 @@
       <c r="D158" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -5781,6 +6261,7 @@
       <c r="G158" t="n">
         <v>257.4</v>
       </c>
+      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
         <v>8.1069</v>
       </c>
@@ -5807,6 +6288,7 @@
       <c r="D159" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -5815,6 +6297,7 @@
       <c r="G159" t="n">
         <v>250.0615</v>
       </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
         <v>7.8758</v>
       </c>
@@ -5841,6 +6324,7 @@
       <c r="D160" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -5849,6 +6333,7 @@
       <c r="G160" t="n">
         <v>175.1887</v>
       </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
         <v>5.5176</v>
       </c>
@@ -5875,6 +6360,7 @@
       <c r="D161" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5883,6 +6369,7 @@
       <c r="G161" t="n">
         <v>157.1815</v>
       </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
         <v>4.9505</v>
       </c>
@@ -5909,6 +6396,7 @@
       <c r="D162" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -5917,6 +6405,7 @@
       <c r="G162" t="n">
         <v>134.15</v>
       </c>
+      <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
         <v>4.2251</v>
       </c>
@@ -5943,6 +6432,7 @@
       <c r="D163" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5951,6 +6441,7 @@
       <c r="G163" t="n">
         <v>126.3621</v>
       </c>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
         <v>3.9798</v>
       </c>
@@ -5977,6 +6468,7 @@
       <c r="D164" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -5985,6 +6477,7 @@
       <c r="G164" t="n">
         <v>114.9389</v>
       </c>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>3.62</v>
       </c>
@@ -6011,6 +6504,7 @@
       <c r="D165" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -6019,6 +6513,7 @@
       <c r="G165" t="n">
         <v>69.48</v>
       </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>2.1883</v>
       </c>
@@ -6045,6 +6540,7 @@
       <c r="D166" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>潘鼎</t>
@@ -6053,6 +6549,7 @@
       <c r="G166" t="n">
         <v>63.2</v>
       </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>1.9905</v>
       </c>
@@ -6079,6 +6576,7 @@
       <c r="D167" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -6087,6 +6585,7 @@
       <c r="G167" t="n">
         <v>62.8726</v>
       </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>1.9802</v>
       </c>
@@ -6113,6 +6612,7 @@
       <c r="D168" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -6121,6 +6621,7 @@
       <c r="G168" t="n">
         <v>62.8726</v>
       </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>1.9802</v>
       </c>
@@ -6147,6 +6648,7 @@
       <c r="D169" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -6155,6 +6657,7 @@
       <c r="G169" t="n">
         <v>47.4</v>
       </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>1.4929</v>
       </c>
@@ -6181,6 +6684,7 @@
       <c r="D170" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -6189,6 +6693,7 @@
       <c r="G170" t="n">
         <v>46.1846</v>
       </c>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>1.4546</v>
       </c>
@@ -6215,6 +6720,7 @@
       <c r="D171" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -6223,6 +6729,7 @@
       <c r="G171" t="n">
         <v>40</v>
       </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>1.2598</v>
       </c>
@@ -6249,6 +6756,7 @@
       <c r="D172" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6257,6 +6765,7 @@
       <c r="G172" t="n">
         <v>39.2954</v>
       </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>1.2376</v>
       </c>
@@ -6283,6 +6792,7 @@
       <c r="D173" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>陈志华</t>
@@ -6291,6 +6801,7 @@
       <c r="G173" t="n">
         <v>30.04</v>
       </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>0.9461000000000001</v>
       </c>
@@ -6317,6 +6828,7 @@
       <c r="D174" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>耿卫东</t>
@@ -6325,6 +6837,7 @@
       <c r="G174" t="n">
         <v>30</v>
       </c>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>0.9449</v>
       </c>
@@ -6351,6 +6864,7 @@
       <c r="D175" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6359,6 +6873,7 @@
       <c r="G175" t="n">
         <v>23.5772</v>
       </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0.7426</v>
       </c>
@@ -6385,6 +6900,7 @@
       <c r="D176" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -6393,6 +6909,7 @@
       <c r="G176" t="n">
         <v>20</v>
       </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
         <v>0.6299</v>
       </c>
@@ -6419,6 +6936,7 @@
       <c r="D177" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -6427,6 +6945,7 @@
       <c r="G177" t="n">
         <v>19.4081</v>
       </c>
+      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>0.6113</v>
       </c>
@@ -6453,6 +6972,7 @@
       <c r="D178" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6461,6 +6981,7 @@
       <c r="G178" t="n">
         <v>15.7182</v>
       </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0.4951</v>
       </c>
@@ -6487,6 +7008,7 @@
       <c r="D179" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -6495,6 +7017,7 @@
       <c r="G179" t="n">
         <v>15.5625</v>
       </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>0.4901</v>
       </c>
@@ -6521,6 +7044,7 @@
       <c r="D180" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -6529,6 +7053,7 @@
       <c r="G180" t="n">
         <v>12.0034</v>
       </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>0.3781</v>
       </c>
@@ -6555,6 +7080,7 @@
       <c r="D181" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -6563,6 +7089,7 @@
       <c r="G181" t="n">
         <v>3.0041</v>
       </c>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>0.0946</v>
       </c>
@@ -6589,6 +7116,7 @@
       <c r="D182" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -6597,6 +7125,7 @@
       <c r="G182" t="n">
         <v>2.8079</v>
       </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
         <v>0.08840000000000001</v>
       </c>
@@ -6623,6 +7152,7 @@
       <c r="D183" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -6631,6 +7161,7 @@
       <c r="G183" t="n">
         <v>2.0654</v>
       </c>
+      <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
         <v>0.06510000000000001</v>
       </c>
@@ -6657,6 +7188,7 @@
       <c r="D184" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -6665,6 +7197,7 @@
       <c r="G184" t="n">
         <v>0.9699</v>
       </c>
+      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>0.0305</v>
       </c>
@@ -6691,6 +7224,7 @@
       <c r="D185" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -6699,6 +7233,7 @@
       <c r="G185" t="n">
         <v>0.1556</v>
       </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.0049</v>
       </c>
@@ -6707,6314 +7242,6 @@
           <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J164"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴15条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量184条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2408</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6158.9225</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-3446.4699</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>322</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>322</v>
-      </c>
-      <c r="G7" t="n">
-        <v>322</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="G9" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-3535.0134</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>80</v>
-      </c>
-      <c r="H10" t="n">
-        <v>80</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H11" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>36</v>
-      </c>
-      <c r="G13" t="n">
-        <v>36</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>87</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>87</v>
-      </c>
-      <c r="G14" t="n">
-        <v>87</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>74</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>74</v>
-      </c>
-      <c r="G15" t="n">
-        <v>74</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>72</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>72</v>
-      </c>
-      <c r="G18" t="n">
-        <v>72</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>72</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>72</v>
-      </c>
-      <c r="G20" t="n">
-        <v>72</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>220</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>220</v>
-      </c>
-      <c r="G21" t="n">
-        <v>220</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1035</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1035</v>
-      </c>
-      <c r="G22" t="n">
-        <v>976.7757</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-58.2243</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>322</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>322</v>
-      </c>
-      <c r="G26" t="n">
-        <v>322</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>20</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>20</v>
-      </c>
-      <c r="G27" t="n">
-        <v>20</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F28" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G28" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>80</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>80</v>
-      </c>
-      <c r="G29" t="n">
-        <v>80</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G30" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>20</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>20</v>
-      </c>
-      <c r="G31" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>36</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>36</v>
-      </c>
-      <c r="G32" t="n">
-        <v>36</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>87</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>87</v>
-      </c>
-      <c r="G33" t="n">
-        <v>87</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>74</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>74</v>
-      </c>
-      <c r="G34" t="n">
-        <v>74</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>72</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>72</v>
-      </c>
-      <c r="G37" t="n">
-        <v>72</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>72</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>72</v>
-      </c>
-      <c r="G39" t="n">
-        <v>72</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>220</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>220</v>
-      </c>
-      <c r="G40" t="n">
-        <v>242</v>
-      </c>
-      <c r="H40" t="n">
-        <v>22</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>976.7757</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>976.7757</v>
-      </c>
-      <c r="G41" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="E42" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F42" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G43" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G44" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>322</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>322</v>
-      </c>
-      <c r="G45" t="n">
-        <v>322</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>20</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>20</v>
-      </c>
-      <c r="G46" t="n">
-        <v>20</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E47" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F47" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G47" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>80</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>80</v>
-      </c>
-      <c r="G48" t="n">
-        <v>80</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G49" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>20</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>20</v>
-      </c>
-      <c r="G50" t="n">
-        <v>20</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>36</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>36</v>
-      </c>
-      <c r="G51" t="n">
-        <v>36</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>87</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>87</v>
-      </c>
-      <c r="G52" t="n">
-        <v>87</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>74</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>74</v>
-      </c>
-      <c r="G53" t="n">
-        <v>74</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G54" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G55" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>72</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>72</v>
-      </c>
-      <c r="G56" t="n">
-        <v>72</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G57" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>72</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>72</v>
-      </c>
-      <c r="G58" t="n">
-        <v>72</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>242</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>242</v>
-      </c>
-      <c r="G59" t="n">
-        <v>242</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="G60" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="E61" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F61" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="G61" t="n">
-        <v>3156.8427</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-3306.5324</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G62" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G63" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="H64" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>322</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>322</v>
-      </c>
-      <c r="G65" t="n">
-        <v>322</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>20</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>20</v>
-      </c>
-      <c r="G66" t="n">
-        <v>20</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E67" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F67" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G67" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>50</v>
-      </c>
-      <c r="H68" t="n">
-        <v>50</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>30</v>
-      </c>
-      <c r="H69" t="n">
-        <v>30</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>40</v>
-      </c>
-      <c r="H70" t="n">
-        <v>40</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>20</v>
-      </c>
-      <c r="H71" t="n">
-        <v>20</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>80</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>80</v>
-      </c>
-      <c r="G72" t="n">
-        <v>80</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>20</v>
-      </c>
-      <c r="H73" t="n">
-        <v>20</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G74" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>20</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>20</v>
-      </c>
-      <c r="G75" t="n">
-        <v>20</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>36</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>36</v>
-      </c>
-      <c r="G76" t="n">
-        <v>36</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>100</v>
-      </c>
-      <c r="H77" t="n">
-        <v>100</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>80</v>
-      </c>
-      <c r="H78" t="n">
-        <v>80</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="n">
-        <v>20</v>
-      </c>
-      <c r="H79" t="n">
-        <v>20</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>87</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>87</v>
-      </c>
-      <c r="G80" t="n">
-        <v>87</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>74</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>74</v>
-      </c>
-      <c r="G81" t="n">
-        <v>74</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G82" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G83" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>72</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>72</v>
-      </c>
-      <c r="G84" t="n">
-        <v>72</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G85" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>72</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>72</v>
-      </c>
-      <c r="G86" t="n">
-        <v>72</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>3156.8427</v>
-      </c>
-      <c r="E87" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F87" t="n">
-        <v>6907.7652</v>
-      </c>
-      <c r="G87" t="n">
-        <v>3168.6313</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-3739.1339</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G88" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G89" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="G90" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>322</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>322</v>
-      </c>
-      <c r="G91" t="n">
-        <v>322</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>20</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>20</v>
-      </c>
-      <c r="G92" t="n">
-        <v>20</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E93" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F93" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G93" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>50</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>50</v>
-      </c>
-      <c r="G94" t="n">
-        <v>50</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>30</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>30</v>
-      </c>
-      <c r="G95" t="n">
-        <v>30</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>40</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>40</v>
-      </c>
-      <c r="G96" t="n">
-        <v>40</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>20</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>20</v>
-      </c>
-      <c r="G97" t="n">
-        <v>20</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>80</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>80</v>
-      </c>
-      <c r="G98" t="n">
-        <v>80</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>20</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>20</v>
-      </c>
-      <c r="G99" t="n">
-        <v>20</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G100" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>20</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>20</v>
-      </c>
-      <c r="G101" t="n">
-        <v>20</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>36</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>36</v>
-      </c>
-      <c r="G102" t="n">
-        <v>36</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>100</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>100</v>
-      </c>
-      <c r="G103" t="n">
-        <v>100</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>80</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>80</v>
-      </c>
-      <c r="G104" t="n">
-        <v>80</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>20</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>20</v>
-      </c>
-      <c r="G105" t="n">
-        <v>20</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>聚贝投资</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>11.7886</v>
-      </c>
-      <c r="H106" t="n">
-        <v>11.7886</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>87</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>87</v>
-      </c>
-      <c r="G107" t="n">
-        <v>87</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>74</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>74</v>
-      </c>
-      <c r="G108" t="n">
-        <v>74</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G109" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G110" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>72</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>72</v>
-      </c>
-      <c r="G111" t="n">
-        <v>72</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G112" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>3168.6313</v>
-      </c>
-      <c r="E113" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F113" t="n">
-        <v>6919.5538</v>
-      </c>
-      <c r="G113" t="n">
-        <v>40237.2571</v>
-      </c>
-      <c r="H113" t="n">
-        <v>33317.7033</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G114" t="n">
-        <v>2015</v>
-      </c>
-      <c r="H114" t="n">
-        <v>1882.5</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G115" t="n">
-        <v>140</v>
-      </c>
-      <c r="H115" t="n">
-        <v>130.8</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="G116" t="n">
-        <v>370.8394</v>
-      </c>
-      <c r="H116" t="n">
-        <v>346.4493</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>322</v>
-      </c>
-      <c r="E117" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" t="n">
-        <v>322</v>
-      </c>
-      <c r="G117" t="n">
-        <v>3220</v>
-      </c>
-      <c r="H117" t="n">
-        <v>2898</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>20</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>20</v>
-      </c>
-      <c r="G118" t="n">
-        <v>304</v>
-      </c>
-      <c r="H118" t="n">
-        <v>284</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E119" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F119" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G119" t="n">
-        <v>2875</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-1091.8316</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>50</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>50</v>
-      </c>
-      <c r="G120" t="n">
-        <v>760</v>
-      </c>
-      <c r="H120" t="n">
-        <v>710</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>30</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>30</v>
-      </c>
-      <c r="G121" t="n">
-        <v>456</v>
-      </c>
-      <c r="H121" t="n">
-        <v>426</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>40</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="n">
-        <v>40</v>
-      </c>
-      <c r="G122" t="n">
-        <v>608</v>
-      </c>
-      <c r="H122" t="n">
-        <v>568</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>20</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" t="n">
-        <v>20</v>
-      </c>
-      <c r="G123" t="n">
-        <v>304</v>
-      </c>
-      <c r="H123" t="n">
-        <v>284</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>80</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>80</v>
-      </c>
-      <c r="G124" t="n">
-        <v>1216</v>
-      </c>
-      <c r="H124" t="n">
-        <v>1136</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>20</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>20</v>
-      </c>
-      <c r="G125" t="n">
-        <v>304</v>
-      </c>
-      <c r="H125" t="n">
-        <v>284</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G126" t="n">
-        <v>407</v>
-      </c>
-      <c r="H126" t="n">
-        <v>380.2322</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>20</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" t="n">
-        <v>20</v>
-      </c>
-      <c r="G127" t="n">
-        <v>304</v>
-      </c>
-      <c r="H127" t="n">
-        <v>284</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>36</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>36</v>
-      </c>
-      <c r="G128" t="n">
-        <v>547</v>
-      </c>
-      <c r="H128" t="n">
-        <v>511</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>100</v>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>100</v>
-      </c>
-      <c r="G129" t="n">
-        <v>1520</v>
-      </c>
-      <c r="H129" t="n">
-        <v>1420</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>80</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>80</v>
-      </c>
-      <c r="G130" t="n">
-        <v>1216</v>
-      </c>
-      <c r="H130" t="n">
-        <v>1136</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>20</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" t="n">
-        <v>20</v>
-      </c>
-      <c r="G131" t="n">
-        <v>304</v>
-      </c>
-      <c r="H131" t="n">
-        <v>284</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>聚贝投资</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.7886</v>
-      </c>
-      <c r="E132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" t="n">
-        <v>11.7886</v>
-      </c>
-      <c r="G132" t="n">
-        <v>179</v>
-      </c>
-      <c r="H132" t="n">
-        <v>167.2114</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>87</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>87</v>
-      </c>
-      <c r="G133" t="n">
-        <v>1322</v>
-      </c>
-      <c r="H133" t="n">
-        <v>1235</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>74</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="n">
-        <v>74</v>
-      </c>
-      <c r="G134" t="n">
-        <v>1125</v>
-      </c>
-      <c r="H134" t="n">
-        <v>1051</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G135" t="n">
-        <v>798</v>
-      </c>
-      <c r="H135" t="n">
-        <v>745.5</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G136" t="n">
-        <v>1542</v>
-      </c>
-      <c r="H136" t="n">
-        <v>1440.7</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>72</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" t="n">
-        <v>72</v>
-      </c>
-      <c r="G137" t="n">
-        <v>1095</v>
-      </c>
-      <c r="H137" t="n">
-        <v>1023</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G138" t="n">
-        <v>2960</v>
-      </c>
-      <c r="H138" t="n">
-        <v>2765.5</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>40237.2571</v>
-      </c>
-      <c r="E139" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F139" t="n">
-        <v>43988.1796</v>
-      </c>
-      <c r="G139" t="n">
-        <v>3175.067</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-40813.1126</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>2015</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" t="n">
-        <v>2015</v>
-      </c>
-      <c r="G140" t="n">
-        <v>175.1887</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-1839.8113</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>140</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" t="n">
-        <v>140</v>
-      </c>
-      <c r="G141" t="n">
-        <v>12.0034</v>
-      </c>
-      <c r="H141" t="n">
-        <v>-127.9966</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>370.8394</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" t="n">
-        <v>370.8394</v>
-      </c>
-      <c r="G142" t="n">
-        <v>15.7182</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-355.1212</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>3220</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" t="n">
-        <v>3220</v>
-      </c>
-      <c r="G143" t="n">
-        <v>280</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-2940</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>304</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="n">
-        <v>304</v>
-      </c>
-      <c r="G144" t="n">
-        <v>3.0041</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-300.9959</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>2875</v>
-      </c>
-      <c r="E145" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F145" t="n">
-        <v>6625.9225</v>
-      </c>
-      <c r="G145" t="n">
-        <v>250.0615</v>
-      </c>
-      <c r="H145" t="n">
-        <v>-6375.861</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>760</v>
-      </c>
-      <c r="E146" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" t="n">
-        <v>760</v>
-      </c>
-      <c r="G146" t="n">
-        <v>46.1846</v>
-      </c>
-      <c r="H146" t="n">
-        <v>-713.8154</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>456</v>
-      </c>
-      <c r="E147" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" t="n">
-        <v>456</v>
-      </c>
-      <c r="G147" t="n">
-        <v>15.5625</v>
-      </c>
-      <c r="H147" t="n">
-        <v>-440.4375</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>608</v>
-      </c>
-      <c r="E148" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" t="n">
-        <v>608</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0.9699</v>
-      </c>
-      <c r="H148" t="n">
-        <v>-607.0300999999999</v>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>304</v>
-      </c>
-      <c r="E149" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" t="n">
-        <v>304</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0.1556</v>
-      </c>
-      <c r="H149" t="n">
-        <v>-303.8444</v>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>1216</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" t="n">
-        <v>1216</v>
-      </c>
-      <c r="G150" t="n">
-        <v>126.3621</v>
-      </c>
-      <c r="H150" t="n">
-        <v>-1089.6379</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>304</v>
-      </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" t="n">
-        <v>304</v>
-      </c>
-      <c r="G151" t="n">
-        <v>39.2954</v>
-      </c>
-      <c r="H151" t="n">
-        <v>-264.7046</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>407</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" t="n">
-        <v>407</v>
-      </c>
-      <c r="G152" t="n">
-        <v>2.0654</v>
-      </c>
-      <c r="H152" t="n">
-        <v>-404.9346</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>304</v>
-      </c>
-      <c r="E153" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" t="n">
-        <v>304</v>
-      </c>
-      <c r="G153" t="n">
-        <v>19.4081</v>
-      </c>
-      <c r="H153" t="n">
-        <v>-284.5919</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>547</v>
-      </c>
-      <c r="E154" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" t="n">
-        <v>547</v>
-      </c>
-      <c r="G154" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H154" t="n">
-        <v>-499.6</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>1520</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" t="n">
-        <v>1520</v>
-      </c>
-      <c r="G155" t="n">
-        <v>157.1815</v>
-      </c>
-      <c r="H155" t="n">
-        <v>-1362.8185</v>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>潘鼎</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>0</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="H156" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>1216</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="n">
-        <v>1216</v>
-      </c>
-      <c r="G157" t="n">
-        <v>62.8726</v>
-      </c>
-      <c r="H157" t="n">
-        <v>-1153.1274</v>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>304</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" t="n">
-        <v>304</v>
-      </c>
-      <c r="G158" t="n">
-        <v>23.5772</v>
-      </c>
-      <c r="H158" t="n">
-        <v>-280.4228</v>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>耿卫东</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="n">
-        <v>30</v>
-      </c>
-      <c r="H159" t="n">
-        <v>30</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>聚贝投资</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>179</v>
-      </c>
-      <c r="E160" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" t="n">
-        <v>179</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" t="n">
-        <v>-179</v>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>1322</v>
-      </c>
-      <c r="E161" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G161" t="n">
-        <v>114.9389</v>
-      </c>
-      <c r="H161" t="n">
-        <v>-1207.0611</v>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>1125</v>
-      </c>
-      <c r="E162" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" t="n">
-        <v>1125</v>
-      </c>
-      <c r="G162" t="n">
-        <v>40</v>
-      </c>
-      <c r="H162" t="n">
-        <v>-1085</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>798</v>
-      </c>
-      <c r="E163" t="n">
-        <v>0</v>
-      </c>
-      <c r="F163" t="n">
-        <v>798</v>
-      </c>
-      <c r="G163" t="n">
-        <v>69.48</v>
-      </c>
-      <c r="H163" t="n">
-        <v>-728.52</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>1542</v>
-      </c>
-      <c r="E164" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" t="n">
-        <v>1542</v>
-      </c>
-      <c r="G164" t="n">
-        <v>134.15</v>
-      </c>
-      <c r="H164" t="n">
-        <v>-1407.85</v>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +475,6 @@
       <c r="E2" t="n">
         <v>13500</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -501,7 +501,6 @@
       <c r="E3" t="n">
         <v>13500</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -528,7 +527,6 @@
       <c r="E4" t="n">
         <v>13500</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -555,7 +553,6 @@
       <c r="E5" t="n">
         <v>13500</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -582,7 +579,6 @@
       <c r="E6" t="n">
         <v>13500</v>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -609,7 +605,6 @@
       <c r="E7" t="n">
         <v>13500</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -636,7 +631,6 @@
       <c r="E8" t="n">
         <v>13500</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -663,7 +657,6 @@
       <c r="E9" t="n">
         <v>13500</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -690,7 +683,6 @@
       <c r="E10" t="n">
         <v>13500</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -717,7 +709,6 @@
       <c r="E11" t="n">
         <v>13500</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -744,7 +735,6 @@
       <c r="E12" t="n">
         <v>13500</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -771,7 +761,6 @@
       <c r="E13" t="n">
         <v>13500</v>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -798,7 +787,6 @@
       <c r="E14" t="n">
         <v>13500</v>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -825,7 +813,6 @@
       <c r="E15" t="n">
         <v>13500</v>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -852,7 +839,6 @@
       <c r="E16" t="n">
         <v>13500</v>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -942,7 +928,6 @@
       <c r="D2" t="n">
         <v>2408</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -951,8 +936,6 @@
       <c r="G2" t="n">
         <v>1035</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -976,7 +959,6 @@
       <c r="D3" t="n">
         <v>2408</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -985,8 +967,6 @@
       <c r="G3" t="n">
         <v>322</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1010,7 +990,6 @@
       <c r="D4" t="n">
         <v>2408</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1019,8 +998,6 @@
       <c r="G4" t="n">
         <v>220</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1044,7 +1021,6 @@
       <c r="D5" t="n">
         <v>2408</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1053,8 +1029,6 @@
       <c r="G5" t="n">
         <v>194.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1078,7 +1052,6 @@
       <c r="D6" t="n">
         <v>2408</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1087,8 +1060,6 @@
       <c r="G6" t="n">
         <v>132.5</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1112,7 +1083,6 @@
       <c r="D7" t="n">
         <v>2408</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1121,8 +1091,6 @@
       <c r="G7" t="n">
         <v>101.3</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1146,7 +1114,6 @@
       <c r="D8" t="n">
         <v>2408</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1155,8 +1122,6 @@
       <c r="G8" t="n">
         <v>87</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1180,7 +1145,6 @@
       <c r="D9" t="n">
         <v>2408</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1189,8 +1153,6 @@
       <c r="G9" t="n">
         <v>52.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1214,7 +1176,6 @@
       <c r="D10" t="n">
         <v>2408</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1223,8 +1184,6 @@
       <c r="G10" t="n">
         <v>36</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1248,7 +1207,6 @@
       <c r="D11" t="n">
         <v>2408</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1257,8 +1215,6 @@
       <c r="G11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1282,7 +1238,6 @@
       <c r="D12" t="n">
         <v>2408</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1291,8 +1246,6 @@
       <c r="G12" t="n">
         <v>72</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1316,7 +1269,6 @@
       <c r="D13" t="n">
         <v>2408</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1325,8 +1277,6 @@
       <c r="G13" t="n">
         <v>72</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1350,7 +1300,6 @@
       <c r="D14" t="n">
         <v>2408</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1359,8 +1308,6 @@
       <c r="G14" t="n">
         <v>74</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1384,7 +1331,6 @@
       <c r="D15" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1393,8 +1339,6 @@
       <c r="G15" t="n">
         <v>976.7757</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1418,7 +1362,6 @@
       <c r="D16" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1427,8 +1370,6 @@
       <c r="G16" t="n">
         <v>322</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1452,7 +1393,6 @@
       <c r="D17" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1461,8 +1401,6 @@
       <c r="G17" t="n">
         <v>220</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1486,7 +1424,6 @@
       <c r="D18" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1495,8 +1432,6 @@
       <c r="G18" t="n">
         <v>194.5</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1520,7 +1455,6 @@
       <c r="D19" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -1529,8 +1463,6 @@
       <c r="G19" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1554,7 +1486,6 @@
       <c r="D20" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1563,8 +1494,6 @@
       <c r="G20" t="n">
         <v>132.5</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1588,7 +1517,6 @@
       <c r="D21" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1597,8 +1525,6 @@
       <c r="G21" t="n">
         <v>101.3</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1622,7 +1548,6 @@
       <c r="D22" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1631,8 +1556,6 @@
       <c r="G22" t="n">
         <v>87</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1656,7 +1579,6 @@
       <c r="D23" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -1665,8 +1587,6 @@
       <c r="G23" t="n">
         <v>80</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1690,7 +1610,6 @@
       <c r="D24" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1699,8 +1618,6 @@
       <c r="G24" t="n">
         <v>74</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1724,7 +1641,6 @@
       <c r="D25" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1733,8 +1649,6 @@
       <c r="G25" t="n">
         <v>72</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1758,7 +1672,6 @@
       <c r="D26" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1767,8 +1680,6 @@
       <c r="G26" t="n">
         <v>72</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1792,7 +1703,6 @@
       <c r="D27" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1801,8 +1711,6 @@
       <c r="G27" t="n">
         <v>52.5</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1826,7 +1734,6 @@
       <c r="D28" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1835,8 +1742,6 @@
       <c r="G28" t="n">
         <v>36</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1860,7 +1765,6 @@
       <c r="D29" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1869,8 +1773,6 @@
       <c r="G29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1894,7 +1796,6 @@
       <c r="D30" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -1903,8 +1804,6 @@
       <c r="G30" t="n">
         <v>20</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1928,7 +1827,6 @@
       <c r="D31" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -1937,8 +1835,6 @@
       <c r="G31" t="n">
         <v>20</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1962,7 +1858,6 @@
       <c r="D32" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -1971,8 +1866,6 @@
       <c r="G32" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1996,7 +1889,6 @@
       <c r="D33" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2005,8 +1897,6 @@
       <c r="G33" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2030,7 +1920,6 @@
       <c r="D34" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2039,8 +1928,6 @@
       <c r="G34" t="n">
         <v>322</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2064,7 +1951,6 @@
       <c r="D35" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2073,8 +1959,6 @@
       <c r="G35" t="n">
         <v>242</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2098,7 +1982,6 @@
       <c r="D36" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2107,8 +1990,6 @@
       <c r="G36" t="n">
         <v>194.5</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2132,7 +2013,6 @@
       <c r="D37" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2141,8 +2021,6 @@
       <c r="G37" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2166,7 +2044,6 @@
       <c r="D38" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2175,8 +2052,6 @@
       <c r="G38" t="n">
         <v>132.5</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2200,7 +2075,6 @@
       <c r="D39" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2209,8 +2083,6 @@
       <c r="G39" t="n">
         <v>101.3</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2234,7 +2106,6 @@
       <c r="D40" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2243,8 +2114,6 @@
       <c r="G40" t="n">
         <v>87</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2268,7 +2137,6 @@
       <c r="D41" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2277,8 +2145,6 @@
       <c r="G41" t="n">
         <v>80</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2302,7 +2168,6 @@
       <c r="D42" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2311,8 +2176,6 @@
       <c r="G42" t="n">
         <v>74</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2336,7 +2199,6 @@
       <c r="D43" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2345,8 +2207,6 @@
       <c r="G43" t="n">
         <v>72</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2370,7 +2230,6 @@
       <c r="D44" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2379,8 +2238,6 @@
       <c r="G44" t="n">
         <v>72</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2404,7 +2261,6 @@
       <c r="D45" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2413,8 +2269,6 @@
       <c r="G45" t="n">
         <v>52.5</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2438,7 +2292,6 @@
       <c r="D46" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2447,8 +2300,6 @@
       <c r="G46" t="n">
         <v>36</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2472,7 +2323,6 @@
       <c r="D47" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2481,8 +2331,6 @@
       <c r="G47" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2506,7 +2354,6 @@
       <c r="D48" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2515,8 +2362,6 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2540,7 +2385,6 @@
       <c r="D49" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2549,8 +2393,6 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2574,7 +2416,6 @@
       <c r="D50" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2583,8 +2424,6 @@
       <c r="G50" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2608,7 +2447,6 @@
       <c r="D51" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2617,8 +2455,6 @@
       <c r="G51" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2642,7 +2478,6 @@
       <c r="D52" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2651,8 +2486,6 @@
       <c r="G52" t="n">
         <v>322</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2676,7 +2509,6 @@
       <c r="D53" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2685,8 +2517,6 @@
       <c r="G53" t="n">
         <v>242</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2710,7 +2540,6 @@
       <c r="D54" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2719,8 +2548,6 @@
       <c r="G54" t="n">
         <v>194.5</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2744,7 +2571,6 @@
       <c r="D55" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2753,8 +2579,6 @@
       <c r="G55" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2778,7 +2602,6 @@
       <c r="D56" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2787,8 +2610,6 @@
       <c r="G56" t="n">
         <v>132.5</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2812,7 +2633,6 @@
       <c r="D57" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2821,8 +2641,6 @@
       <c r="G57" t="n">
         <v>101.3</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2846,7 +2664,6 @@
       <c r="D58" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2855,8 +2672,6 @@
       <c r="G58" t="n">
         <v>87</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2880,7 +2695,6 @@
       <c r="D59" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2889,8 +2703,6 @@
       <c r="G59" t="n">
         <v>80</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2914,7 +2726,6 @@
       <c r="D60" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2923,8 +2734,6 @@
       <c r="G60" t="n">
         <v>74</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2948,7 +2757,6 @@
       <c r="D61" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2957,8 +2765,6 @@
       <c r="G61" t="n">
         <v>72</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2982,7 +2788,6 @@
       <c r="D62" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2991,8 +2796,6 @@
       <c r="G62" t="n">
         <v>72</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3016,7 +2819,6 @@
       <c r="D63" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3025,8 +2827,6 @@
       <c r="G63" t="n">
         <v>52.5</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3050,7 +2850,6 @@
       <c r="D64" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3059,8 +2858,6 @@
       <c r="G64" t="n">
         <v>36</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3084,7 +2881,6 @@
       <c r="D65" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3093,8 +2889,6 @@
       <c r="G65" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3118,7 +2912,6 @@
       <c r="D66" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3127,8 +2920,6 @@
       <c r="G66" t="n">
         <v>20</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3152,7 +2943,6 @@
       <c r="D67" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3161,8 +2951,6 @@
       <c r="G67" t="n">
         <v>20</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3186,7 +2974,6 @@
       <c r="D68" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3195,8 +2982,6 @@
       <c r="G68" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3220,7 +3005,6 @@
       <c r="D69" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3229,8 +3013,6 @@
       <c r="G69" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3254,7 +3036,6 @@
       <c r="D70" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3263,8 +3044,6 @@
       <c r="G70" t="n">
         <v>322</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3288,7 +3067,6 @@
       <c r="D71" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3297,8 +3075,6 @@
       <c r="G71" t="n">
         <v>242</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3322,7 +3098,6 @@
       <c r="D72" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3331,8 +3106,6 @@
       <c r="G72" t="n">
         <v>194.5</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3356,7 +3129,6 @@
       <c r="D73" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -3365,8 +3137,6 @@
       <c r="G73" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3390,7 +3160,6 @@
       <c r="D74" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -3399,8 +3168,6 @@
       <c r="G74" t="n">
         <v>132.5</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3424,7 +3191,6 @@
       <c r="D75" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -3433,8 +3199,6 @@
       <c r="G75" t="n">
         <v>101.3</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3458,7 +3222,6 @@
       <c r="D76" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -3467,8 +3230,6 @@
       <c r="G76" t="n">
         <v>87</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3492,7 +3253,6 @@
       <c r="D77" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -3501,8 +3261,6 @@
       <c r="G77" t="n">
         <v>80</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3526,7 +3284,6 @@
       <c r="D78" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -3535,8 +3292,6 @@
       <c r="G78" t="n">
         <v>74</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3560,7 +3315,6 @@
       <c r="D79" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -3569,8 +3323,6 @@
       <c r="G79" t="n">
         <v>72</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3594,7 +3346,6 @@
       <c r="D80" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -3603,8 +3354,6 @@
       <c r="G80" t="n">
         <v>72</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3628,7 +3377,6 @@
       <c r="D81" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3637,8 +3385,6 @@
       <c r="G81" t="n">
         <v>52.5</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3662,7 +3408,6 @@
       <c r="D82" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3671,8 +3416,6 @@
       <c r="G82" t="n">
         <v>36</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3696,7 +3439,6 @@
       <c r="D83" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3705,8 +3447,6 @@
       <c r="G83" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3730,7 +3470,6 @@
       <c r="D84" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3739,8 +3478,6 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3764,7 +3501,6 @@
       <c r="D85" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3773,8 +3509,6 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3798,7 +3532,6 @@
       <c r="D86" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3807,8 +3540,6 @@
       <c r="G86" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3832,7 +3563,6 @@
       <c r="D87" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -3841,8 +3571,6 @@
       <c r="G87" t="n">
         <v>100</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3866,7 +3594,6 @@
       <c r="D88" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -3875,8 +3602,6 @@
       <c r="G88" t="n">
         <v>80</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3900,7 +3625,6 @@
       <c r="D89" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -3909,8 +3633,6 @@
       <c r="G89" t="n">
         <v>60</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3934,7 +3656,6 @@
       <c r="D90" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -3943,8 +3664,6 @@
       <c r="G90" t="n">
         <v>50</v>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3968,7 +3687,6 @@
       <c r="D91" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -3977,8 +3695,6 @@
       <c r="G91" t="n">
         <v>40</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4002,7 +3718,6 @@
       <c r="D92" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4011,8 +3726,6 @@
       <c r="G92" t="n">
         <v>30</v>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4036,7 +3749,6 @@
       <c r="D93" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4045,8 +3757,6 @@
       <c r="G93" t="n">
         <v>20</v>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4070,7 +3780,6 @@
       <c r="D94" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -4079,8 +3788,6 @@
       <c r="G94" t="n">
         <v>20</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4104,7 +3811,6 @@
       <c r="D95" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -4113,8 +3819,6 @@
       <c r="G95" t="n">
         <v>20</v>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4138,7 +3842,6 @@
       <c r="D96" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -4147,8 +3850,6 @@
       <c r="G96" t="n">
         <v>24.3901</v>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4172,7 +3873,6 @@
       <c r="D97" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -4181,8 +3881,6 @@
       <c r="G97" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4206,7 +3904,6 @@
       <c r="D98" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -4215,8 +3912,6 @@
       <c r="G98" t="n">
         <v>322</v>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4240,7 +3935,6 @@
       <c r="D99" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -4249,8 +3943,6 @@
       <c r="G99" t="n">
         <v>242</v>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4274,7 +3966,6 @@
       <c r="D100" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -4283,8 +3974,6 @@
       <c r="G100" t="n">
         <v>194.5</v>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4308,7 +3997,6 @@
       <c r="D101" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4317,8 +4005,6 @@
       <c r="G101" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4342,7 +4028,6 @@
       <c r="D102" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4351,8 +4036,6 @@
       <c r="G102" t="n">
         <v>132.5</v>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4376,7 +4059,6 @@
       <c r="D103" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4385,8 +4067,6 @@
       <c r="G103" t="n">
         <v>101.3</v>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4410,7 +4090,6 @@
       <c r="D104" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4419,8 +4098,6 @@
       <c r="G104" t="n">
         <v>87</v>
       </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4444,7 +4121,6 @@
       <c r="D105" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -4453,8 +4129,6 @@
       <c r="G105" t="n">
         <v>80</v>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4478,7 +4152,6 @@
       <c r="D106" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -4487,8 +4160,6 @@
       <c r="G106" t="n">
         <v>74</v>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4512,7 +4183,6 @@
       <c r="D107" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -4521,8 +4191,6 @@
       <c r="G107" t="n">
         <v>72</v>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4546,7 +4214,6 @@
       <c r="D108" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -4555,8 +4222,6 @@
       <c r="G108" t="n">
         <v>72</v>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4580,7 +4245,6 @@
       <c r="D109" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -4589,8 +4253,6 @@
       <c r="G109" t="n">
         <v>52.5</v>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4614,7 +4276,6 @@
       <c r="D110" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -4623,8 +4284,6 @@
       <c r="G110" t="n">
         <v>36</v>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4648,7 +4307,6 @@
       <c r="D111" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -4657,8 +4315,6 @@
       <c r="G111" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4682,7 +4338,6 @@
       <c r="D112" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -4691,8 +4346,6 @@
       <c r="G112" t="n">
         <v>20</v>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4716,7 +4369,6 @@
       <c r="D113" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -4725,8 +4377,6 @@
       <c r="G113" t="n">
         <v>20</v>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4750,7 +4400,6 @@
       <c r="D114" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -4759,8 +4408,6 @@
       <c r="G114" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4784,7 +4431,6 @@
       <c r="D115" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -4793,8 +4439,6 @@
       <c r="G115" t="n">
         <v>100</v>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4818,7 +4462,6 @@
       <c r="D116" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -4827,8 +4470,6 @@
       <c r="G116" t="n">
         <v>80</v>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4852,7 +4493,6 @@
       <c r="D117" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -4861,8 +4501,6 @@
       <c r="G117" t="n">
         <v>60</v>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4886,7 +4524,6 @@
       <c r="D118" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -4895,8 +4532,6 @@
       <c r="G118" t="n">
         <v>50</v>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4920,7 +4555,6 @@
       <c r="D119" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -4929,8 +4563,6 @@
       <c r="G119" t="n">
         <v>40</v>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4954,7 +4586,6 @@
       <c r="D120" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4963,8 +4594,6 @@
       <c r="G120" t="n">
         <v>30</v>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4988,7 +4617,6 @@
       <c r="D121" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4997,8 +4625,6 @@
       <c r="G121" t="n">
         <v>20</v>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5022,7 +4648,6 @@
       <c r="D122" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -5031,8 +4656,6 @@
       <c r="G122" t="n">
         <v>20</v>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5056,7 +4679,6 @@
       <c r="D123" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -5065,8 +4687,6 @@
       <c r="G123" t="n">
         <v>20</v>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5090,7 +4710,6 @@
       <c r="D124" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -5099,8 +4718,6 @@
       <c r="G124" t="n">
         <v>24.3901</v>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5124,7 +4741,6 @@
       <c r="D125" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -5133,8 +4749,6 @@
       <c r="G125" t="n">
         <v>11.7886</v>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5158,7 +4772,6 @@
       <c r="D126" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -5167,8 +4780,6 @@
       <c r="G126" t="n">
         <v>9236.4177</v>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5192,7 +4803,6 @@
       <c r="D127" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -5201,8 +4811,6 @@
       <c r="G127" t="n">
         <v>3220</v>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5226,7 +4834,6 @@
       <c r="D128" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -5235,8 +4842,6 @@
       <c r="G128" t="n">
         <v>3102</v>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5260,7 +4865,6 @@
       <c r="D129" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -5269,8 +4873,6 @@
       <c r="G129" t="n">
         <v>2960</v>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5294,7 +4896,6 @@
       <c r="D130" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -5303,8 +4904,6 @@
       <c r="G130" t="n">
         <v>2875</v>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5328,7 +4927,6 @@
       <c r="D131" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -5337,8 +4935,6 @@
       <c r="G131" t="n">
         <v>2015</v>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5362,7 +4958,6 @@
       <c r="D132" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -5371,8 +4966,6 @@
       <c r="G132" t="n">
         <v>1542</v>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5396,7 +4989,6 @@
       <c r="D133" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -5405,8 +4997,6 @@
       <c r="G133" t="n">
         <v>1322</v>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5430,7 +5020,6 @@
       <c r="D134" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5439,8 +5028,6 @@
       <c r="G134" t="n">
         <v>1216</v>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5464,7 +5051,6 @@
       <c r="D135" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -5473,8 +5059,6 @@
       <c r="G135" t="n">
         <v>1125</v>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5498,7 +5082,6 @@
       <c r="D136" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -5507,8 +5090,6 @@
       <c r="G136" t="n">
         <v>1095</v>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5532,7 +5113,6 @@
       <c r="D137" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -5541,8 +5121,6 @@
       <c r="G137" t="n">
         <v>1095</v>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5566,7 +5144,6 @@
       <c r="D138" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -5575,8 +5152,6 @@
       <c r="G138" t="n">
         <v>798</v>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5600,7 +5175,6 @@
       <c r="D139" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -5609,8 +5183,6 @@
       <c r="G139" t="n">
         <v>547</v>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5634,7 +5206,6 @@
       <c r="D140" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -5643,8 +5214,6 @@
       <c r="G140" t="n">
         <v>140</v>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5668,7 +5237,6 @@
       <c r="D141" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -5677,8 +5245,6 @@
       <c r="G141" t="n">
         <v>304</v>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5702,7 +5268,6 @@
       <c r="D142" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -5711,8 +5276,6 @@
       <c r="G142" t="n">
         <v>304</v>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5736,7 +5299,6 @@
       <c r="D143" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -5745,8 +5307,6 @@
       <c r="G143" t="n">
         <v>407</v>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5770,7 +5330,6 @@
       <c r="D144" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5779,8 +5338,6 @@
       <c r="G144" t="n">
         <v>1520</v>
       </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5804,7 +5361,6 @@
       <c r="D145" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -5813,8 +5369,6 @@
       <c r="G145" t="n">
         <v>1216</v>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5838,7 +5392,6 @@
       <c r="D146" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -5847,8 +5400,6 @@
       <c r="G146" t="n">
         <v>912</v>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5872,7 +5423,6 @@
       <c r="D147" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -5881,8 +5431,6 @@
       <c r="G147" t="n">
         <v>760</v>
       </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5906,7 +5454,6 @@
       <c r="D148" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -5915,8 +5462,6 @@
       <c r="G148" t="n">
         <v>608</v>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5940,7 +5485,6 @@
       <c r="D149" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -5949,8 +5493,6 @@
       <c r="G149" t="n">
         <v>456</v>
       </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5974,7 +5516,6 @@
       <c r="D150" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -5983,8 +5524,6 @@
       <c r="G150" t="n">
         <v>304</v>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6008,7 +5547,6 @@
       <c r="D151" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6017,8 +5555,6 @@
       <c r="G151" t="n">
         <v>304</v>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6042,7 +5578,6 @@
       <c r="D152" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6051,8 +5586,6 @@
       <c r="G152" t="n">
         <v>304</v>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6076,7 +5609,6 @@
       <c r="D153" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6085,8 +5617,6 @@
       <c r="G153" t="n">
         <v>370.8394</v>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6110,7 +5640,6 @@
       <c r="D154" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -6119,8 +5648,6 @@
       <c r="G154" t="n">
         <v>179</v>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6144,7 +5671,6 @@
       <c r="D155" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -6153,7 +5679,6 @@
       <c r="G155" t="n">
         <v>803.1668</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>25.2961</v>
       </c>
@@ -6180,7 +5705,6 @@
       <c r="D156" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -6189,7 +5713,6 @@
       <c r="G156" t="n">
         <v>280</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
         <v>8.8187</v>
       </c>
@@ -6216,7 +5739,6 @@
       <c r="D157" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -6225,7 +5747,6 @@
       <c r="G157" t="n">
         <v>270</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
         <v>8.5038</v>
       </c>
@@ -6252,7 +5773,6 @@
       <c r="D158" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -6261,7 +5781,6 @@
       <c r="G158" t="n">
         <v>257.4</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
         <v>8.1069</v>
       </c>
@@ -6288,7 +5807,6 @@
       <c r="D159" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -6297,7 +5815,6 @@
       <c r="G159" t="n">
         <v>250.0615</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
         <v>7.8758</v>
       </c>
@@ -6324,7 +5841,6 @@
       <c r="D160" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -6333,7 +5849,6 @@
       <c r="G160" t="n">
         <v>175.1887</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
         <v>5.5176</v>
       </c>
@@ -6360,7 +5875,6 @@
       <c r="D161" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -6369,7 +5883,6 @@
       <c r="G161" t="n">
         <v>157.1815</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
         <v>4.9505</v>
       </c>
@@ -6396,7 +5909,6 @@
       <c r="D162" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -6405,7 +5917,6 @@
       <c r="G162" t="n">
         <v>134.15</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
         <v>4.2251</v>
       </c>
@@ -6432,7 +5943,6 @@
       <c r="D163" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -6441,7 +5951,6 @@
       <c r="G163" t="n">
         <v>126.3621</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
         <v>3.9798</v>
       </c>
@@ -6468,7 +5977,6 @@
       <c r="D164" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -6477,7 +5985,6 @@
       <c r="G164" t="n">
         <v>114.9389</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>3.62</v>
       </c>
@@ -6504,7 +6011,6 @@
       <c r="D165" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -6513,7 +6019,6 @@
       <c r="G165" t="n">
         <v>69.48</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>2.1883</v>
       </c>
@@ -6540,7 +6045,6 @@
       <c r="D166" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>潘鼎</t>
@@ -6549,7 +6053,6 @@
       <c r="G166" t="n">
         <v>63.2</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>1.9905</v>
       </c>
@@ -6576,7 +6079,6 @@
       <c r="D167" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -6585,7 +6087,6 @@
       <c r="G167" t="n">
         <v>62.8726</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>1.9802</v>
       </c>
@@ -6612,7 +6113,6 @@
       <c r="D168" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -6621,7 +6121,6 @@
       <c r="G168" t="n">
         <v>62.8726</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>1.9802</v>
       </c>
@@ -6648,7 +6147,6 @@
       <c r="D169" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -6657,7 +6155,6 @@
       <c r="G169" t="n">
         <v>47.4</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>1.4929</v>
       </c>
@@ -6684,7 +6181,6 @@
       <c r="D170" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -6693,7 +6189,6 @@
       <c r="G170" t="n">
         <v>46.1846</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>1.4546</v>
       </c>
@@ -6720,7 +6215,6 @@
       <c r="D171" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -6729,7 +6223,6 @@
       <c r="G171" t="n">
         <v>40</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>1.2598</v>
       </c>
@@ -6756,7 +6249,6 @@
       <c r="D172" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6765,7 +6257,6 @@
       <c r="G172" t="n">
         <v>39.2954</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>1.2376</v>
       </c>
@@ -6792,7 +6283,6 @@
       <c r="D173" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>陈志华</t>
@@ -6801,7 +6291,6 @@
       <c r="G173" t="n">
         <v>30.04</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>0.9461000000000001</v>
       </c>
@@ -6828,7 +6317,6 @@
       <c r="D174" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>耿卫东</t>
@@ -6837,7 +6325,6 @@
       <c r="G174" t="n">
         <v>30</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>0.9449</v>
       </c>
@@ -6864,7 +6351,6 @@
       <c r="D175" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6873,7 +6359,6 @@
       <c r="G175" t="n">
         <v>23.5772</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0.7426</v>
       </c>
@@ -6900,7 +6385,6 @@
       <c r="D176" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -6909,7 +6393,6 @@
       <c r="G176" t="n">
         <v>20</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
         <v>0.6299</v>
       </c>
@@ -6936,7 +6419,6 @@
       <c r="D177" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -6945,7 +6427,6 @@
       <c r="G177" t="n">
         <v>19.4081</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>0.6113</v>
       </c>
@@ -6972,7 +6453,6 @@
       <c r="D178" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6981,7 +6461,6 @@
       <c r="G178" t="n">
         <v>15.7182</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0.4951</v>
       </c>
@@ -7008,7 +6487,6 @@
       <c r="D179" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -7017,7 +6495,6 @@
       <c r="G179" t="n">
         <v>15.5625</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>0.4901</v>
       </c>
@@ -7044,7 +6521,6 @@
       <c r="D180" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -7053,7 +6529,6 @@
       <c r="G180" t="n">
         <v>12.0034</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>0.3781</v>
       </c>
@@ -7080,7 +6555,6 @@
       <c r="D181" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -7089,7 +6563,6 @@
       <c r="G181" t="n">
         <v>3.0041</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>0.0946</v>
       </c>
@@ -7116,7 +6589,6 @@
       <c r="D182" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -7125,7 +6597,6 @@
       <c r="G182" t="n">
         <v>2.8079</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
         <v>0.08840000000000001</v>
       </c>
@@ -7152,7 +6623,6 @@
       <c r="D183" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -7161,7 +6631,6 @@
       <c r="G183" t="n">
         <v>2.0654</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
         <v>0.06510000000000001</v>
       </c>
@@ -7188,7 +6657,6 @@
       <c r="D184" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -7197,7 +6665,6 @@
       <c r="G184" t="n">
         <v>0.9699</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>0.0305</v>
       </c>
@@ -7224,7 +6691,6 @@
       <c r="D185" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -7233,7 +6699,6 @@
       <c r="G185" t="n">
         <v>0.1556</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.0049</v>
       </c>
@@ -7242,6 +6707,428 @@
           <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴15条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量184条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>2408</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6158.9225</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-3446.4699</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-3750.9225</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-3750.9225</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3156.8427</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-3306.5324</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>3156.8427</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6907.7652</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3168.6313</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-3739.1339</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>3168.6313</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6919.5538</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40237.2571</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33317.7033</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>40237.2571</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="H10" t="n">
+        <v>43988.1796</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-40813.1126</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>31股东</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>比例合计100.00%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>3175.07</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,6 +474,7 @@
       <c r="E2" t="n">
         <v>13500</v>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -501,6 +501,7 @@
       <c r="E3" t="n">
         <v>13500</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -527,6 +528,7 @@
       <c r="E4" t="n">
         <v>13500</v>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -553,6 +555,7 @@
       <c r="E5" t="n">
         <v>13500</v>
       </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -579,6 +582,7 @@
       <c r="E6" t="n">
         <v>13500</v>
       </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -605,6 +609,7 @@
       <c r="E7" t="n">
         <v>13500</v>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -631,6 +636,7 @@
       <c r="E8" t="n">
         <v>13500</v>
       </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -657,6 +663,7 @@
       <c r="E9" t="n">
         <v>13500</v>
       </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -683,6 +690,7 @@
       <c r="E10" t="n">
         <v>13500</v>
       </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -709,6 +717,7 @@
       <c r="E11" t="n">
         <v>13500</v>
       </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -735,6 +744,7 @@
       <c r="E12" t="n">
         <v>13500</v>
       </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -761,6 +771,7 @@
       <c r="E13" t="n">
         <v>13500</v>
       </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -787,6 +798,7 @@
       <c r="E14" t="n">
         <v>13500</v>
       </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -813,6 +825,7 @@
       <c r="E15" t="n">
         <v>13500</v>
       </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -839,6 +852,7 @@
       <c r="E16" t="n">
         <v>13500</v>
       </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -928,6 +942,7 @@
       <c r="D2" t="n">
         <v>2408</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -936,6 +951,8 @@
       <c r="G2" t="n">
         <v>1035</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -959,6 +976,7 @@
       <c r="D3" t="n">
         <v>2408</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -967,6 +985,8 @@
       <c r="G3" t="n">
         <v>322</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -990,6 +1010,7 @@
       <c r="D4" t="n">
         <v>2408</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -998,6 +1019,8 @@
       <c r="G4" t="n">
         <v>220</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1021,6 +1044,7 @@
       <c r="D5" t="n">
         <v>2408</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1029,6 +1053,8 @@
       <c r="G5" t="n">
         <v>194.5</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1052,6 +1078,7 @@
       <c r="D6" t="n">
         <v>2408</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1060,6 +1087,8 @@
       <c r="G6" t="n">
         <v>132.5</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1083,6 +1112,7 @@
       <c r="D7" t="n">
         <v>2408</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1091,6 +1121,8 @@
       <c r="G7" t="n">
         <v>101.3</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1114,6 +1146,7 @@
       <c r="D8" t="n">
         <v>2408</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1122,6 +1155,8 @@
       <c r="G8" t="n">
         <v>87</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1145,6 +1180,7 @@
       <c r="D9" t="n">
         <v>2408</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1153,6 +1189,8 @@
       <c r="G9" t="n">
         <v>52.5</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1176,6 +1214,7 @@
       <c r="D10" t="n">
         <v>2408</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1184,6 +1223,8 @@
       <c r="G10" t="n">
         <v>36</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1207,6 +1248,7 @@
       <c r="D11" t="n">
         <v>2408</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1215,6 +1257,8 @@
       <c r="G11" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1238,6 +1282,7 @@
       <c r="D12" t="n">
         <v>2408</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1246,6 +1291,8 @@
       <c r="G12" t="n">
         <v>72</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1269,6 +1316,7 @@
       <c r="D13" t="n">
         <v>2408</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1277,6 +1325,8 @@
       <c r="G13" t="n">
         <v>72</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1300,6 +1350,7 @@
       <c r="D14" t="n">
         <v>2408</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1308,6 +1359,8 @@
       <c r="G14" t="n">
         <v>74</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1331,6 +1384,7 @@
       <c r="D15" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1339,6 +1393,8 @@
       <c r="G15" t="n">
         <v>976.7757</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1362,6 +1418,7 @@
       <c r="D16" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1370,6 +1427,8 @@
       <c r="G16" t="n">
         <v>322</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1393,6 +1452,7 @@
       <c r="D17" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1401,6 +1461,8 @@
       <c r="G17" t="n">
         <v>220</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1424,6 +1486,7 @@
       <c r="D18" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1432,6 +1495,8 @@
       <c r="G18" t="n">
         <v>194.5</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1455,6 +1520,7 @@
       <c r="D19" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -1463,6 +1529,8 @@
       <c r="G19" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1486,6 +1554,7 @@
       <c r="D20" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1494,6 +1563,8 @@
       <c r="G20" t="n">
         <v>132.5</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1517,6 +1588,7 @@
       <c r="D21" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1525,6 +1597,8 @@
       <c r="G21" t="n">
         <v>101.3</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1548,6 +1622,7 @@
       <c r="D22" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1556,6 +1631,8 @@
       <c r="G22" t="n">
         <v>87</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1579,6 +1656,7 @@
       <c r="D23" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -1587,6 +1665,8 @@
       <c r="G23" t="n">
         <v>80</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1610,6 +1690,7 @@
       <c r="D24" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1618,6 +1699,8 @@
       <c r="G24" t="n">
         <v>74</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1641,6 +1724,7 @@
       <c r="D25" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1649,6 +1733,8 @@
       <c r="G25" t="n">
         <v>72</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1672,6 +1758,7 @@
       <c r="D26" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1680,6 +1767,8 @@
       <c r="G26" t="n">
         <v>72</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1703,6 +1792,7 @@
       <c r="D27" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1711,6 +1801,8 @@
       <c r="G27" t="n">
         <v>52.5</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1734,6 +1826,7 @@
       <c r="D28" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1742,6 +1835,8 @@
       <c r="G28" t="n">
         <v>36</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1765,6 +1860,7 @@
       <c r="D29" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1773,6 +1869,8 @@
       <c r="G29" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1796,6 +1894,7 @@
       <c r="D30" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -1804,6 +1903,8 @@
       <c r="G30" t="n">
         <v>20</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1827,6 +1928,7 @@
       <c r="D31" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -1835,6 +1937,8 @@
       <c r="G31" t="n">
         <v>20</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1858,6 +1962,7 @@
       <c r="D32" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -1866,6 +1971,8 @@
       <c r="G32" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1889,6 +1996,7 @@
       <c r="D33" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1897,6 +2005,8 @@
       <c r="G33" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1920,6 +2030,7 @@
       <c r="D34" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1928,6 +2039,8 @@
       <c r="G34" t="n">
         <v>322</v>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1951,6 +2064,7 @@
       <c r="D35" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1959,6 +2073,8 @@
       <c r="G35" t="n">
         <v>242</v>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1982,6 +2098,7 @@
       <c r="D36" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1990,6 +2107,8 @@
       <c r="G36" t="n">
         <v>194.5</v>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2013,6 +2132,7 @@
       <c r="D37" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2021,6 +2141,8 @@
       <c r="G37" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2044,6 +2166,7 @@
       <c r="D38" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2052,6 +2175,8 @@
       <c r="G38" t="n">
         <v>132.5</v>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2075,6 +2200,7 @@
       <c r="D39" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2083,6 +2209,8 @@
       <c r="G39" t="n">
         <v>101.3</v>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2106,6 +2234,7 @@
       <c r="D40" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2114,6 +2243,8 @@
       <c r="G40" t="n">
         <v>87</v>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2137,6 +2268,7 @@
       <c r="D41" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2145,6 +2277,8 @@
       <c r="G41" t="n">
         <v>80</v>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2168,6 +2302,7 @@
       <c r="D42" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2176,6 +2311,8 @@
       <c r="G42" t="n">
         <v>74</v>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2199,6 +2336,7 @@
       <c r="D43" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2207,6 +2345,8 @@
       <c r="G43" t="n">
         <v>72</v>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2230,6 +2370,7 @@
       <c r="D44" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2238,6 +2379,8 @@
       <c r="G44" t="n">
         <v>72</v>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2261,6 +2404,7 @@
       <c r="D45" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2269,6 +2413,8 @@
       <c r="G45" t="n">
         <v>52.5</v>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2292,6 +2438,7 @@
       <c r="D46" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2300,6 +2447,8 @@
       <c r="G46" t="n">
         <v>36</v>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2323,6 +2472,7 @@
       <c r="D47" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2331,6 +2481,8 @@
       <c r="G47" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2354,6 +2506,7 @@
       <c r="D48" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2362,6 +2515,8 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2385,6 +2540,7 @@
       <c r="D49" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2393,6 +2549,8 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2416,6 +2574,7 @@
       <c r="D50" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2424,6 +2583,8 @@
       <c r="G50" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2447,6 +2608,7 @@
       <c r="D51" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2455,6 +2617,8 @@
       <c r="G51" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2478,6 +2642,7 @@
       <c r="D52" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2486,6 +2651,8 @@
       <c r="G52" t="n">
         <v>322</v>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2509,6 +2676,7 @@
       <c r="D53" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2517,6 +2685,8 @@
       <c r="G53" t="n">
         <v>242</v>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2540,6 +2710,7 @@
       <c r="D54" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2548,6 +2719,8 @@
       <c r="G54" t="n">
         <v>194.5</v>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2571,6 +2744,7 @@
       <c r="D55" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2579,6 +2753,8 @@
       <c r="G55" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2602,6 +2778,7 @@
       <c r="D56" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2610,6 +2787,8 @@
       <c r="G56" t="n">
         <v>132.5</v>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2633,6 +2812,7 @@
       <c r="D57" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2641,6 +2821,8 @@
       <c r="G57" t="n">
         <v>101.3</v>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2664,6 +2846,7 @@
       <c r="D58" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2672,6 +2855,8 @@
       <c r="G58" t="n">
         <v>87</v>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2695,6 +2880,7 @@
       <c r="D59" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2703,6 +2889,8 @@
       <c r="G59" t="n">
         <v>80</v>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2726,6 +2914,7 @@
       <c r="D60" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2734,6 +2923,8 @@
       <c r="G60" t="n">
         <v>74</v>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2757,6 +2948,7 @@
       <c r="D61" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2765,6 +2957,8 @@
       <c r="G61" t="n">
         <v>72</v>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2788,6 +2982,7 @@
       <c r="D62" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2796,6 +2991,8 @@
       <c r="G62" t="n">
         <v>72</v>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2819,6 +3016,7 @@
       <c r="D63" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2827,6 +3025,8 @@
       <c r="G63" t="n">
         <v>52.5</v>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2850,6 +3050,7 @@
       <c r="D64" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2858,6 +3059,8 @@
       <c r="G64" t="n">
         <v>36</v>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2881,6 +3084,7 @@
       <c r="D65" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2889,6 +3093,8 @@
       <c r="G65" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2912,6 +3118,7 @@
       <c r="D66" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2920,6 +3127,8 @@
       <c r="G66" t="n">
         <v>20</v>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2943,6 +3152,7 @@
       <c r="D67" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2951,6 +3161,8 @@
       <c r="G67" t="n">
         <v>20</v>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2974,6 +3186,7 @@
       <c r="D68" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2982,6 +3195,8 @@
       <c r="G68" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3005,6 +3220,7 @@
       <c r="D69" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3013,6 +3229,8 @@
       <c r="G69" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3036,6 +3254,7 @@
       <c r="D70" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3044,6 +3263,8 @@
       <c r="G70" t="n">
         <v>322</v>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3067,6 +3288,7 @@
       <c r="D71" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3075,6 +3297,8 @@
       <c r="G71" t="n">
         <v>242</v>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3098,6 +3322,7 @@
       <c r="D72" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3106,6 +3331,8 @@
       <c r="G72" t="n">
         <v>194.5</v>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3129,6 +3356,7 @@
       <c r="D73" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -3137,6 +3365,8 @@
       <c r="G73" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3160,6 +3390,7 @@
       <c r="D74" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -3168,6 +3399,8 @@
       <c r="G74" t="n">
         <v>132.5</v>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3191,6 +3424,7 @@
       <c r="D75" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -3199,6 +3433,8 @@
       <c r="G75" t="n">
         <v>101.3</v>
       </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3222,6 +3458,7 @@
       <c r="D76" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -3230,6 +3467,8 @@
       <c r="G76" t="n">
         <v>87</v>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3253,6 +3492,7 @@
       <c r="D77" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -3261,6 +3501,8 @@
       <c r="G77" t="n">
         <v>80</v>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3284,6 +3526,7 @@
       <c r="D78" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -3292,6 +3535,8 @@
       <c r="G78" t="n">
         <v>74</v>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3315,6 +3560,7 @@
       <c r="D79" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -3323,6 +3569,8 @@
       <c r="G79" t="n">
         <v>72</v>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3346,6 +3594,7 @@
       <c r="D80" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -3354,6 +3603,8 @@
       <c r="G80" t="n">
         <v>72</v>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3377,6 +3628,7 @@
       <c r="D81" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3385,6 +3637,8 @@
       <c r="G81" t="n">
         <v>52.5</v>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3408,6 +3662,7 @@
       <c r="D82" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3416,6 +3671,8 @@
       <c r="G82" t="n">
         <v>36</v>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3439,6 +3696,7 @@
       <c r="D83" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3447,6 +3705,8 @@
       <c r="G83" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3470,6 +3730,7 @@
       <c r="D84" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3478,6 +3739,8 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3501,6 +3764,7 @@
       <c r="D85" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3509,6 +3773,8 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3532,6 +3798,7 @@
       <c r="D86" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3540,6 +3807,8 @@
       <c r="G86" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3563,6 +3832,7 @@
       <c r="D87" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -3571,6 +3841,8 @@
       <c r="G87" t="n">
         <v>100</v>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3594,6 +3866,7 @@
       <c r="D88" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -3602,6 +3875,8 @@
       <c r="G88" t="n">
         <v>80</v>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3625,6 +3900,7 @@
       <c r="D89" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -3633,6 +3909,8 @@
       <c r="G89" t="n">
         <v>60</v>
       </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3656,6 +3934,7 @@
       <c r="D90" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -3664,6 +3943,8 @@
       <c r="G90" t="n">
         <v>50</v>
       </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3687,6 +3968,7 @@
       <c r="D91" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -3695,6 +3977,8 @@
       <c r="G91" t="n">
         <v>40</v>
       </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3718,6 +4002,7 @@
       <c r="D92" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -3726,6 +4011,8 @@
       <c r="G92" t="n">
         <v>30</v>
       </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3749,6 +4036,7 @@
       <c r="D93" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -3757,6 +4045,8 @@
       <c r="G93" t="n">
         <v>20</v>
       </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3780,6 +4070,7 @@
       <c r="D94" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -3788,6 +4079,8 @@
       <c r="G94" t="n">
         <v>20</v>
       </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3811,6 +4104,7 @@
       <c r="D95" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -3819,6 +4113,8 @@
       <c r="G95" t="n">
         <v>20</v>
       </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3842,6 +4138,7 @@
       <c r="D96" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -3850,6 +4147,8 @@
       <c r="G96" t="n">
         <v>24.3901</v>
       </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3873,6 +4172,7 @@
       <c r="D97" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3881,6 +4181,8 @@
       <c r="G97" t="n">
         <v>954.7757</v>
       </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3904,6 +4206,7 @@
       <c r="D98" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3912,6 +4215,8 @@
       <c r="G98" t="n">
         <v>322</v>
       </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3935,6 +4240,7 @@
       <c r="D99" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3943,6 +4249,8 @@
       <c r="G99" t="n">
         <v>242</v>
       </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3966,6 +4274,7 @@
       <c r="D100" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3974,6 +4283,8 @@
       <c r="G100" t="n">
         <v>194.5</v>
       </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3997,6 +4308,7 @@
       <c r="D101" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4005,6 +4317,8 @@
       <c r="G101" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4028,6 +4342,7 @@
       <c r="D102" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4036,6 +4351,8 @@
       <c r="G102" t="n">
         <v>132.5</v>
       </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4059,6 +4376,7 @@
       <c r="D103" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4067,6 +4385,8 @@
       <c r="G103" t="n">
         <v>101.3</v>
       </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4090,6 +4410,7 @@
       <c r="D104" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4098,6 +4419,8 @@
       <c r="G104" t="n">
         <v>87</v>
       </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4121,6 +4444,7 @@
       <c r="D105" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -4129,6 +4453,8 @@
       <c r="G105" t="n">
         <v>80</v>
       </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4152,6 +4478,7 @@
       <c r="D106" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -4160,6 +4487,8 @@
       <c r="G106" t="n">
         <v>74</v>
       </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4183,6 +4512,7 @@
       <c r="D107" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -4191,6 +4521,8 @@
       <c r="G107" t="n">
         <v>72</v>
       </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4214,6 +4546,7 @@
       <c r="D108" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -4222,6 +4555,8 @@
       <c r="G108" t="n">
         <v>72</v>
       </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4245,6 +4580,7 @@
       <c r="D109" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -4253,6 +4589,8 @@
       <c r="G109" t="n">
         <v>52.5</v>
       </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4276,6 +4614,7 @@
       <c r="D110" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -4284,6 +4623,8 @@
       <c r="G110" t="n">
         <v>36</v>
       </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4307,6 +4648,7 @@
       <c r="D111" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -4315,6 +4657,8 @@
       <c r="G111" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4338,6 +4682,7 @@
       <c r="D112" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -4346,6 +4691,8 @@
       <c r="G112" t="n">
         <v>20</v>
       </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4369,6 +4716,7 @@
       <c r="D113" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -4377,6 +4725,8 @@
       <c r="G113" t="n">
         <v>20</v>
       </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4400,6 +4750,7 @@
       <c r="D114" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -4408,6 +4759,8 @@
       <c r="G114" t="n">
         <v>26.7678</v>
       </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4431,6 +4784,7 @@
       <c r="D115" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -4439,6 +4793,8 @@
       <c r="G115" t="n">
         <v>100</v>
       </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4462,6 +4818,7 @@
       <c r="D116" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -4470,6 +4827,8 @@
       <c r="G116" t="n">
         <v>80</v>
       </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4493,6 +4852,7 @@
       <c r="D117" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -4501,6 +4861,8 @@
       <c r="G117" t="n">
         <v>60</v>
       </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4524,6 +4886,7 @@
       <c r="D118" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -4532,6 +4895,8 @@
       <c r="G118" t="n">
         <v>50</v>
       </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4555,6 +4920,7 @@
       <c r="D119" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -4563,6 +4929,8 @@
       <c r="G119" t="n">
         <v>40</v>
       </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4586,6 +4954,7 @@
       <c r="D120" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4594,6 +4963,8 @@
       <c r="G120" t="n">
         <v>30</v>
       </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4617,6 +4988,7 @@
       <c r="D121" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4625,6 +4997,8 @@
       <c r="G121" t="n">
         <v>20</v>
       </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4648,6 +5022,7 @@
       <c r="D122" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -4656,6 +5031,8 @@
       <c r="G122" t="n">
         <v>20</v>
       </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4679,6 +5056,7 @@
       <c r="D123" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -4687,6 +5065,8 @@
       <c r="G123" t="n">
         <v>20</v>
       </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4710,6 +5090,7 @@
       <c r="D124" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -4718,6 +5099,8 @@
       <c r="G124" t="n">
         <v>24.3901</v>
       </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4741,6 +5124,7 @@
       <c r="D125" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -4749,6 +5133,8 @@
       <c r="G125" t="n">
         <v>11.7886</v>
       </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4772,6 +5158,7 @@
       <c r="D126" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -4780,6 +5167,8 @@
       <c r="G126" t="n">
         <v>9236.4177</v>
       </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4803,6 +5192,7 @@
       <c r="D127" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -4811,6 +5201,8 @@
       <c r="G127" t="n">
         <v>3220</v>
       </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4834,6 +5226,7 @@
       <c r="D128" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -4842,6 +5235,8 @@
       <c r="G128" t="n">
         <v>3102</v>
       </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4865,6 +5260,7 @@
       <c r="D129" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -4873,6 +5269,8 @@
       <c r="G129" t="n">
         <v>2960</v>
       </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4896,6 +5294,7 @@
       <c r="D130" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4904,6 +5303,8 @@
       <c r="G130" t="n">
         <v>2875</v>
       </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4927,6 +5328,7 @@
       <c r="D131" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4935,6 +5337,8 @@
       <c r="G131" t="n">
         <v>2015</v>
       </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4958,6 +5362,7 @@
       <c r="D132" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4966,6 +5371,8 @@
       <c r="G132" t="n">
         <v>1542</v>
       </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4989,6 +5396,7 @@
       <c r="D133" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4997,6 +5405,8 @@
       <c r="G133" t="n">
         <v>1322</v>
       </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5020,6 +5430,7 @@
       <c r="D134" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5028,6 +5439,8 @@
       <c r="G134" t="n">
         <v>1216</v>
       </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5051,6 +5464,7 @@
       <c r="D135" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -5059,6 +5473,8 @@
       <c r="G135" t="n">
         <v>1125</v>
       </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5082,6 +5498,7 @@
       <c r="D136" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -5090,6 +5507,8 @@
       <c r="G136" t="n">
         <v>1095</v>
       </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5113,6 +5532,7 @@
       <c r="D137" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -5121,6 +5541,8 @@
       <c r="G137" t="n">
         <v>1095</v>
       </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5144,6 +5566,7 @@
       <c r="D138" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -5152,6 +5575,8 @@
       <c r="G138" t="n">
         <v>798</v>
       </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5175,6 +5600,7 @@
       <c r="D139" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -5183,6 +5609,8 @@
       <c r="G139" t="n">
         <v>547</v>
       </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5206,6 +5634,7 @@
       <c r="D140" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -5214,6 +5643,8 @@
       <c r="G140" t="n">
         <v>140</v>
       </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5237,6 +5668,7 @@
       <c r="D141" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -5245,6 +5677,8 @@
       <c r="G141" t="n">
         <v>304</v>
       </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5268,6 +5702,7 @@
       <c r="D142" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -5276,6 +5711,8 @@
       <c r="G142" t="n">
         <v>304</v>
       </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5299,6 +5736,7 @@
       <c r="D143" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -5307,6 +5745,8 @@
       <c r="G143" t="n">
         <v>407</v>
       </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5330,6 +5770,7 @@
       <c r="D144" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5338,6 +5779,8 @@
       <c r="G144" t="n">
         <v>1520</v>
       </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5361,6 +5804,7 @@
       <c r="D145" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -5369,6 +5813,8 @@
       <c r="G145" t="n">
         <v>1216</v>
       </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5392,6 +5838,7 @@
       <c r="D146" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -5400,6 +5847,8 @@
       <c r="G146" t="n">
         <v>912</v>
       </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5423,6 +5872,7 @@
       <c r="D147" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -5431,6 +5881,8 @@
       <c r="G147" t="n">
         <v>760</v>
       </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5454,6 +5906,7 @@
       <c r="D148" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -5462,6 +5915,8 @@
       <c r="G148" t="n">
         <v>608</v>
       </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5485,6 +5940,7 @@
       <c r="D149" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -5493,6 +5949,8 @@
       <c r="G149" t="n">
         <v>456</v>
       </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5516,6 +5974,7 @@
       <c r="D150" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -5524,6 +5983,8 @@
       <c r="G150" t="n">
         <v>304</v>
       </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5547,6 +6008,7 @@
       <c r="D151" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -5555,6 +6017,8 @@
       <c r="G151" t="n">
         <v>304</v>
       </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5578,6 +6042,7 @@
       <c r="D152" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -5586,6 +6051,8 @@
       <c r="G152" t="n">
         <v>304</v>
       </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5609,6 +6076,7 @@
       <c r="D153" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -5617,6 +6085,8 @@
       <c r="G153" t="n">
         <v>370.8394</v>
       </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5640,6 +6110,7 @@
       <c r="D154" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -5648,6 +6119,8 @@
       <c r="G154" t="n">
         <v>179</v>
       </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5671,6 +6144,7 @@
       <c r="D155" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -5679,6 +6153,7 @@
       <c r="G155" t="n">
         <v>803.1668</v>
       </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>25.2961</v>
       </c>
@@ -5705,6 +6180,7 @@
       <c r="D156" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -5713,6 +6189,7 @@
       <c r="G156" t="n">
         <v>280</v>
       </c>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
         <v>8.8187</v>
       </c>
@@ -5739,6 +6216,7 @@
       <c r="D157" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -5747,6 +6225,7 @@
       <c r="G157" t="n">
         <v>270</v>
       </c>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
         <v>8.5038</v>
       </c>
@@ -5773,6 +6252,7 @@
       <c r="D158" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -5781,6 +6261,7 @@
       <c r="G158" t="n">
         <v>257.4</v>
       </c>
+      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
         <v>8.1069</v>
       </c>
@@ -5807,6 +6288,7 @@
       <c r="D159" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -5815,6 +6297,7 @@
       <c r="G159" t="n">
         <v>250.0615</v>
       </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
         <v>7.8758</v>
       </c>
@@ -5841,6 +6324,7 @@
       <c r="D160" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -5849,6 +6333,7 @@
       <c r="G160" t="n">
         <v>175.1887</v>
       </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
         <v>5.5176</v>
       </c>
@@ -5875,6 +6360,7 @@
       <c r="D161" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5883,6 +6369,7 @@
       <c r="G161" t="n">
         <v>157.1815</v>
       </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
         <v>4.9505</v>
       </c>
@@ -5909,6 +6396,7 @@
       <c r="D162" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -5917,6 +6405,7 @@
       <c r="G162" t="n">
         <v>134.15</v>
       </c>
+      <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
         <v>4.2251</v>
       </c>
@@ -5943,6 +6432,7 @@
       <c r="D163" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5951,6 +6441,7 @@
       <c r="G163" t="n">
         <v>126.3621</v>
       </c>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
         <v>3.9798</v>
       </c>
@@ -5977,6 +6468,7 @@
       <c r="D164" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -5985,6 +6477,7 @@
       <c r="G164" t="n">
         <v>114.9389</v>
       </c>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>3.62</v>
       </c>
@@ -6011,6 +6504,7 @@
       <c r="D165" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -6019,6 +6513,7 @@
       <c r="G165" t="n">
         <v>69.48</v>
       </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>2.1883</v>
       </c>
@@ -6045,6 +6540,7 @@
       <c r="D166" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>潘鼎</t>
@@ -6053,6 +6549,7 @@
       <c r="G166" t="n">
         <v>63.2</v>
       </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>1.9905</v>
       </c>
@@ -6079,6 +6576,7 @@
       <c r="D167" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -6087,6 +6585,7 @@
       <c r="G167" t="n">
         <v>62.8726</v>
       </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>1.9802</v>
       </c>
@@ -6113,6 +6612,7 @@
       <c r="D168" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -6121,6 +6621,7 @@
       <c r="G168" t="n">
         <v>62.8726</v>
       </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>1.9802</v>
       </c>
@@ -6147,6 +6648,7 @@
       <c r="D169" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -6155,6 +6657,7 @@
       <c r="G169" t="n">
         <v>47.4</v>
       </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>1.4929</v>
       </c>
@@ -6181,6 +6684,7 @@
       <c r="D170" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -6189,6 +6693,7 @@
       <c r="G170" t="n">
         <v>46.1846</v>
       </c>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>1.4546</v>
       </c>
@@ -6215,6 +6720,7 @@
       <c r="D171" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -6223,6 +6729,7 @@
       <c r="G171" t="n">
         <v>40</v>
       </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>1.2598</v>
       </c>
@@ -6249,6 +6756,7 @@
       <c r="D172" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6257,6 +6765,7 @@
       <c r="G172" t="n">
         <v>39.2954</v>
       </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>1.2376</v>
       </c>
@@ -6283,6 +6792,7 @@
       <c r="D173" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>陈志华</t>
@@ -6291,6 +6801,7 @@
       <c r="G173" t="n">
         <v>30.04</v>
       </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>0.9461000000000001</v>
       </c>
@@ -6317,6 +6828,7 @@
       <c r="D174" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>耿卫东</t>
@@ -6325,6 +6837,7 @@
       <c r="G174" t="n">
         <v>30</v>
       </c>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>0.9449</v>
       </c>
@@ -6351,6 +6864,7 @@
       <c r="D175" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6359,6 +6873,7 @@
       <c r="G175" t="n">
         <v>23.5772</v>
       </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0.7426</v>
       </c>
@@ -6385,6 +6900,7 @@
       <c r="D176" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -6393,6 +6909,7 @@
       <c r="G176" t="n">
         <v>20</v>
       </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
         <v>0.6299</v>
       </c>
@@ -6419,6 +6936,7 @@
       <c r="D177" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -6427,6 +6945,7 @@
       <c r="G177" t="n">
         <v>19.4081</v>
       </c>
+      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>0.6113</v>
       </c>
@@ -6453,6 +6972,7 @@
       <c r="D178" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6461,6 +6981,7 @@
       <c r="G178" t="n">
         <v>15.7182</v>
       </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0.4951</v>
       </c>
@@ -6487,6 +7008,7 @@
       <c r="D179" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -6495,6 +7017,7 @@
       <c r="G179" t="n">
         <v>15.5625</v>
       </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>0.4901</v>
       </c>
@@ -6521,6 +7044,7 @@
       <c r="D180" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -6529,6 +7053,7 @@
       <c r="G180" t="n">
         <v>12.0034</v>
       </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>0.3781</v>
       </c>
@@ -6555,6 +7080,7 @@
       <c r="D181" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -6563,6 +7089,7 @@
       <c r="G181" t="n">
         <v>3.0041</v>
       </c>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>0.0946</v>
       </c>
@@ -6589,6 +7116,7 @@
       <c r="D182" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -6597,6 +7125,7 @@
       <c r="G182" t="n">
         <v>2.8079</v>
       </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
         <v>0.08840000000000001</v>
       </c>
@@ -6623,6 +7152,7 @@
       <c r="D183" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -6631,6 +7161,7 @@
       <c r="G183" t="n">
         <v>2.0654</v>
       </c>
+      <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
         <v>0.06510000000000001</v>
       </c>
@@ -6657,6 +7188,7 @@
       <c r="D184" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -6665,6 +7197,7 @@
       <c r="G184" t="n">
         <v>0.9699</v>
       </c>
+      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>0.0305</v>
       </c>
@@ -6691,6 +7224,7 @@
       <c r="D185" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -6699,6 +7233,7 @@
       <c r="G185" t="n">
         <v>0.1556</v>
       </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.0049</v>
       </c>
@@ -6707,428 +7242,6 @@
           <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴15条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量184条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>2408</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6158.9225</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-3446.4699</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-3750.9225</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-3750.9225</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3156.8427</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-3306.5324</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>3156.8427</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6907.7652</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3168.6313</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-3739.1339</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>3168.6313</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6919.5538</v>
-      </c>
-      <c r="I9" t="n">
-        <v>40237.2571</v>
-      </c>
-      <c r="J9" t="n">
-        <v>33317.7033</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>40237.2571</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="H10" t="n">
-        <v>43988.1796</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3175.067</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-40813.1126</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>31股东</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>比例合计100.00%</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>3175.07</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +475,6 @@
       <c r="E2" t="n">
         <v>13500</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -501,7 +501,6 @@
       <c r="E3" t="n">
         <v>13500</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -528,7 +527,6 @@
       <c r="E4" t="n">
         <v>13500</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -555,7 +553,6 @@
       <c r="E5" t="n">
         <v>13500</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -582,7 +579,6 @@
       <c r="E6" t="n">
         <v>13500</v>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -609,7 +605,6 @@
       <c r="E7" t="n">
         <v>13500</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -636,7 +631,6 @@
       <c r="E8" t="n">
         <v>13500</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -663,7 +657,6 @@
       <c r="E9" t="n">
         <v>13500</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -690,7 +683,6 @@
       <c r="E10" t="n">
         <v>13500</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -717,7 +709,6 @@
       <c r="E11" t="n">
         <v>13500</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -744,7 +735,6 @@
       <c r="E12" t="n">
         <v>13500</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -771,7 +761,6 @@
       <c r="E13" t="n">
         <v>13500</v>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -798,7 +787,6 @@
       <c r="E14" t="n">
         <v>13500</v>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -825,7 +813,6 @@
       <c r="E15" t="n">
         <v>13500</v>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -852,7 +839,6 @@
       <c r="E16" t="n">
         <v>13500</v>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -942,7 +928,6 @@
       <c r="D2" t="n">
         <v>2408</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -951,8 +936,6 @@
       <c r="G2" t="n">
         <v>1035</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -976,7 +959,6 @@
       <c r="D3" t="n">
         <v>2408</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -985,8 +967,6 @@
       <c r="G3" t="n">
         <v>322</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1010,7 +990,6 @@
       <c r="D4" t="n">
         <v>2408</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1019,8 +998,6 @@
       <c r="G4" t="n">
         <v>220</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1044,7 +1021,6 @@
       <c r="D5" t="n">
         <v>2408</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1053,8 +1029,6 @@
       <c r="G5" t="n">
         <v>194.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1078,7 +1052,6 @@
       <c r="D6" t="n">
         <v>2408</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1087,8 +1060,6 @@
       <c r="G6" t="n">
         <v>132.5</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1112,7 +1083,6 @@
       <c r="D7" t="n">
         <v>2408</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1121,8 +1091,6 @@
       <c r="G7" t="n">
         <v>101.3</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1146,7 +1114,6 @@
       <c r="D8" t="n">
         <v>2408</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1155,8 +1122,6 @@
       <c r="G8" t="n">
         <v>87</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1180,7 +1145,6 @@
       <c r="D9" t="n">
         <v>2408</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1189,8 +1153,6 @@
       <c r="G9" t="n">
         <v>52.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1214,7 +1176,6 @@
       <c r="D10" t="n">
         <v>2408</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1223,8 +1184,6 @@
       <c r="G10" t="n">
         <v>36</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1248,7 +1207,6 @@
       <c r="D11" t="n">
         <v>2408</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1257,8 +1215,6 @@
       <c r="G11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1282,7 +1238,6 @@
       <c r="D12" t="n">
         <v>2408</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1291,8 +1246,6 @@
       <c r="G12" t="n">
         <v>72</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1316,7 +1269,6 @@
       <c r="D13" t="n">
         <v>2408</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1325,8 +1277,6 @@
       <c r="G13" t="n">
         <v>72</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1350,7 +1300,6 @@
       <c r="D14" t="n">
         <v>2408</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1359,8 +1308,6 @@
       <c r="G14" t="n">
         <v>74</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>报告期初，公司注册资本 2,408.00万元，其股权结构如下：</t>
@@ -1384,7 +1331,6 @@
       <c r="D15" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1393,8 +1339,6 @@
       <c r="G15" t="n">
         <v>976.7757</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1418,7 +1362,6 @@
       <c r="D16" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1427,8 +1370,6 @@
       <c r="G16" t="n">
         <v>322</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1452,7 +1393,6 @@
       <c r="D17" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1461,8 +1401,6 @@
       <c r="G17" t="n">
         <v>220</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1486,7 +1424,6 @@
       <c r="D18" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1495,8 +1432,6 @@
       <c r="G18" t="n">
         <v>194.5</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1520,7 +1455,6 @@
       <c r="D19" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -1529,8 +1463,6 @@
       <c r="G19" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1554,7 +1486,6 @@
       <c r="D20" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1563,8 +1494,6 @@
       <c r="G20" t="n">
         <v>132.5</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1588,7 +1517,6 @@
       <c r="D21" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1597,8 +1525,6 @@
       <c r="G21" t="n">
         <v>101.3</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1622,7 +1548,6 @@
       <c r="D22" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1631,8 +1556,6 @@
       <c r="G22" t="n">
         <v>87</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1656,7 +1579,6 @@
       <c r="D23" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -1665,8 +1587,6 @@
       <c r="G23" t="n">
         <v>80</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1690,7 +1610,6 @@
       <c r="D24" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1699,8 +1618,6 @@
       <c r="G24" t="n">
         <v>74</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1724,7 +1641,6 @@
       <c r="D25" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1733,8 +1649,6 @@
       <c r="G25" t="n">
         <v>72</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1758,7 +1672,6 @@
       <c r="D26" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1767,8 +1680,6 @@
       <c r="G26" t="n">
         <v>72</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1792,7 +1703,6 @@
       <c r="D27" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1801,8 +1711,6 @@
       <c r="G27" t="n">
         <v>52.5</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1826,7 +1734,6 @@
       <c r="D28" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1835,8 +1742,6 @@
       <c r="G28" t="n">
         <v>36</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1860,7 +1765,6 @@
       <c r="D29" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1869,8 +1773,6 @@
       <c r="G29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1894,7 +1796,6 @@
       <c r="D30" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -1903,8 +1804,6 @@
       <c r="G30" t="n">
         <v>20</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1928,7 +1827,6 @@
       <c r="D31" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -1937,8 +1835,6 @@
       <c r="G31" t="n">
         <v>20</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1962,7 +1858,6 @@
       <c r="D32" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -1971,8 +1866,6 @@
       <c r="G32" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1996,7 +1889,6 @@
       <c r="D33" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2005,8 +1897,6 @@
       <c r="G33" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2030,7 +1920,6 @@
       <c r="D34" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2039,8 +1928,6 @@
       <c r="G34" t="n">
         <v>322</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2064,7 +1951,6 @@
       <c r="D35" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2073,8 +1959,6 @@
       <c r="G35" t="n">
         <v>242</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2098,7 +1982,6 @@
       <c r="D36" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2107,8 +1990,6 @@
       <c r="G36" t="n">
         <v>194.5</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2132,7 +2013,6 @@
       <c r="D37" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2141,8 +2021,6 @@
       <c r="G37" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2166,7 +2044,6 @@
       <c r="D38" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2175,8 +2052,6 @@
       <c r="G38" t="n">
         <v>132.5</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2200,7 +2075,6 @@
       <c r="D39" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2209,8 +2083,6 @@
       <c r="G39" t="n">
         <v>101.3</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2234,7 +2106,6 @@
       <c r="D40" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2243,8 +2114,6 @@
       <c r="G40" t="n">
         <v>87</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2268,7 +2137,6 @@
       <c r="D41" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2277,8 +2145,6 @@
       <c r="G41" t="n">
         <v>80</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2302,7 +2168,6 @@
       <c r="D42" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2311,8 +2176,6 @@
       <c r="G42" t="n">
         <v>74</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2336,7 +2199,6 @@
       <c r="D43" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2345,8 +2207,6 @@
       <c r="G43" t="n">
         <v>72</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2370,7 +2230,6 @@
       <c r="D44" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2379,8 +2238,6 @@
       <c r="G44" t="n">
         <v>72</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2404,7 +2261,6 @@
       <c r="D45" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2413,8 +2269,6 @@
       <c r="G45" t="n">
         <v>52.5</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2438,7 +2292,6 @@
       <c r="D46" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2447,8 +2300,6 @@
       <c r="G46" t="n">
         <v>36</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2472,7 +2323,6 @@
       <c r="D47" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2481,8 +2331,6 @@
       <c r="G47" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2506,7 +2354,6 @@
       <c r="D48" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2515,8 +2362,6 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2540,7 +2385,6 @@
       <c r="D49" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2549,8 +2393,6 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2574,7 +2416,6 @@
       <c r="D50" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2583,8 +2424,6 @@
       <c r="G50" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2608,7 +2447,6 @@
       <c r="D51" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2617,8 +2455,6 @@
       <c r="G51" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2642,7 +2478,6 @@
       <c r="D52" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2651,8 +2486,6 @@
       <c r="G52" t="n">
         <v>322</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2676,7 +2509,6 @@
       <c r="D53" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2685,8 +2517,6 @@
       <c r="G53" t="n">
         <v>242</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2710,7 +2540,6 @@
       <c r="D54" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2719,8 +2548,6 @@
       <c r="G54" t="n">
         <v>194.5</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2744,7 +2571,6 @@
       <c r="D55" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2753,8 +2579,6 @@
       <c r="G55" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2778,7 +2602,6 @@
       <c r="D56" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2787,8 +2610,6 @@
       <c r="G56" t="n">
         <v>132.5</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2812,7 +2633,6 @@
       <c r="D57" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2821,8 +2641,6 @@
       <c r="G57" t="n">
         <v>101.3</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2846,7 +2664,6 @@
       <c r="D58" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2855,8 +2672,6 @@
       <c r="G58" t="n">
         <v>87</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2880,7 +2695,6 @@
       <c r="D59" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2889,8 +2703,6 @@
       <c r="G59" t="n">
         <v>80</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2914,7 +2726,6 @@
       <c r="D60" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2923,8 +2734,6 @@
       <c r="G60" t="n">
         <v>74</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2948,7 +2757,6 @@
       <c r="D61" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2957,8 +2765,6 @@
       <c r="G61" t="n">
         <v>72</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2982,7 +2788,6 @@
       <c r="D62" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2991,8 +2796,6 @@
       <c r="G62" t="n">
         <v>72</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3016,7 +2819,6 @@
       <c r="D63" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3025,8 +2827,6 @@
       <c r="G63" t="n">
         <v>52.5</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3050,7 +2850,6 @@
       <c r="D64" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3059,8 +2858,6 @@
       <c r="G64" t="n">
         <v>36</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3084,7 +2881,6 @@
       <c r="D65" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3093,8 +2889,6 @@
       <c r="G65" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3118,7 +2912,6 @@
       <c r="D66" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3127,8 +2920,6 @@
       <c r="G66" t="n">
         <v>20</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3152,7 +2943,6 @@
       <c r="D67" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3161,8 +2951,6 @@
       <c r="G67" t="n">
         <v>20</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3186,7 +2974,6 @@
       <c r="D68" t="n">
         <v>2750.6769</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3195,8 +2982,6 @@
       <c r="G68" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -3220,7 +3005,6 @@
       <c r="D69" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3229,8 +3013,6 @@
       <c r="G69" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3254,7 +3036,6 @@
       <c r="D70" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3263,8 +3044,6 @@
       <c r="G70" t="n">
         <v>322</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3288,7 +3067,6 @@
       <c r="D71" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3297,8 +3075,6 @@
       <c r="G71" t="n">
         <v>242</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3322,7 +3098,6 @@
       <c r="D72" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3331,8 +3106,6 @@
       <c r="G72" t="n">
         <v>194.5</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3356,7 +3129,6 @@
       <c r="D73" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -3365,8 +3137,6 @@
       <c r="G73" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3390,7 +3160,6 @@
       <c r="D74" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -3399,8 +3168,6 @@
       <c r="G74" t="n">
         <v>132.5</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3424,7 +3191,6 @@
       <c r="D75" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -3433,8 +3199,6 @@
       <c r="G75" t="n">
         <v>101.3</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3458,7 +3222,6 @@
       <c r="D76" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -3467,8 +3230,6 @@
       <c r="G76" t="n">
         <v>87</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3492,7 +3253,6 @@
       <c r="D77" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -3501,8 +3261,6 @@
       <c r="G77" t="n">
         <v>80</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3526,7 +3284,6 @@
       <c r="D78" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -3535,8 +3292,6 @@
       <c r="G78" t="n">
         <v>74</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3560,7 +3315,6 @@
       <c r="D79" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -3569,8 +3323,6 @@
       <c r="G79" t="n">
         <v>72</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3594,7 +3346,6 @@
       <c r="D80" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -3603,8 +3354,6 @@
       <c r="G80" t="n">
         <v>72</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3628,7 +3377,6 @@
       <c r="D81" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3637,8 +3385,6 @@
       <c r="G81" t="n">
         <v>52.5</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3662,7 +3408,6 @@
       <c r="D82" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3671,8 +3416,6 @@
       <c r="G82" t="n">
         <v>36</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3696,7 +3439,6 @@
       <c r="D83" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3705,8 +3447,6 @@
       <c r="G83" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3730,7 +3470,6 @@
       <c r="D84" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3739,8 +3478,6 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3764,7 +3501,6 @@
       <c r="D85" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3773,8 +3509,6 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3798,7 +3532,6 @@
       <c r="D86" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3807,8 +3540,6 @@
       <c r="G86" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3832,7 +3563,6 @@
       <c r="D87" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -3841,8 +3571,6 @@
       <c r="G87" t="n">
         <v>100</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3866,7 +3594,6 @@
       <c r="D88" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -3875,8 +3602,6 @@
       <c r="G88" t="n">
         <v>80</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3900,7 +3625,6 @@
       <c r="D89" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -3909,8 +3633,6 @@
       <c r="G89" t="n">
         <v>60</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3934,7 +3656,6 @@
       <c r="D90" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -3943,8 +3664,6 @@
       <c r="G90" t="n">
         <v>50</v>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3968,7 +3687,6 @@
       <c r="D91" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -3977,8 +3695,6 @@
       <c r="G91" t="n">
         <v>40</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4002,7 +3718,6 @@
       <c r="D92" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4011,8 +3726,6 @@
       <c r="G92" t="n">
         <v>30</v>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4036,7 +3749,6 @@
       <c r="D93" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4045,8 +3757,6 @@
       <c r="G93" t="n">
         <v>20</v>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4070,7 +3780,6 @@
       <c r="D94" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -4079,8 +3788,6 @@
       <c r="G94" t="n">
         <v>20</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4104,7 +3811,6 @@
       <c r="D95" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -4113,8 +3819,6 @@
       <c r="G95" t="n">
         <v>20</v>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4138,7 +3842,6 @@
       <c r="D96" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -4147,8 +3850,6 @@
       <c r="G96" t="n">
         <v>24.3901</v>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4172,7 +3873,6 @@
       <c r="D97" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -4181,8 +3881,6 @@
       <c r="G97" t="n">
         <v>954.7757</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4206,7 +3904,6 @@
       <c r="D98" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -4215,8 +3912,6 @@
       <c r="G98" t="n">
         <v>322</v>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4240,7 +3935,6 @@
       <c r="D99" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -4249,8 +3943,6 @@
       <c r="G99" t="n">
         <v>242</v>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4274,7 +3966,6 @@
       <c r="D100" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -4283,8 +3974,6 @@
       <c r="G100" t="n">
         <v>194.5</v>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4308,7 +3997,6 @@
       <c r="D101" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4317,8 +4005,6 @@
       <c r="G101" t="n">
         <v>215.9091</v>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4342,7 +4028,6 @@
       <c r="D102" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4351,8 +4036,6 @@
       <c r="G102" t="n">
         <v>132.5</v>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4376,7 +4059,6 @@
       <c r="D103" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4385,8 +4067,6 @@
       <c r="G103" t="n">
         <v>101.3</v>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4410,7 +4090,6 @@
       <c r="D104" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4419,8 +4098,6 @@
       <c r="G104" t="n">
         <v>87</v>
       </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4444,7 +4121,6 @@
       <c r="D105" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -4453,8 +4129,6 @@
       <c r="G105" t="n">
         <v>80</v>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4478,7 +4152,6 @@
       <c r="D106" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -4487,8 +4160,6 @@
       <c r="G106" t="n">
         <v>74</v>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4512,7 +4183,6 @@
       <c r="D107" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -4521,8 +4191,6 @@
       <c r="G107" t="n">
         <v>72</v>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4546,7 +4214,6 @@
       <c r="D108" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -4555,8 +4222,6 @@
       <c r="G108" t="n">
         <v>72</v>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4580,7 +4245,6 @@
       <c r="D109" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -4589,8 +4253,6 @@
       <c r="G109" t="n">
         <v>52.5</v>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4614,7 +4276,6 @@
       <c r="D110" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -4623,8 +4284,6 @@
       <c r="G110" t="n">
         <v>36</v>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4648,7 +4307,6 @@
       <c r="D111" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -4657,8 +4315,6 @@
       <c r="G111" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4682,7 +4338,6 @@
       <c r="D112" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -4691,8 +4346,6 @@
       <c r="G112" t="n">
         <v>20</v>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4716,7 +4369,6 @@
       <c r="D113" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -4725,8 +4377,6 @@
       <c r="G113" t="n">
         <v>20</v>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4750,7 +4400,6 @@
       <c r="D114" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -4759,8 +4408,6 @@
       <c r="G114" t="n">
         <v>26.7678</v>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4784,7 +4431,6 @@
       <c r="D115" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -4793,8 +4439,6 @@
       <c r="G115" t="n">
         <v>100</v>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4818,7 +4462,6 @@
       <c r="D116" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -4827,8 +4470,6 @@
       <c r="G116" t="n">
         <v>80</v>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4852,7 +4493,6 @@
       <c r="D117" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -4861,8 +4501,6 @@
       <c r="G117" t="n">
         <v>60</v>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4886,7 +4524,6 @@
       <c r="D118" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -4895,8 +4532,6 @@
       <c r="G118" t="n">
         <v>50</v>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4920,7 +4555,6 @@
       <c r="D119" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -4929,8 +4563,6 @@
       <c r="G119" t="n">
         <v>40</v>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4954,7 +4586,6 @@
       <c r="D120" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4963,8 +4594,6 @@
       <c r="G120" t="n">
         <v>30</v>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4988,7 +4617,6 @@
       <c r="D121" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4997,8 +4625,6 @@
       <c r="G121" t="n">
         <v>20</v>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5022,7 +4648,6 @@
       <c r="D122" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -5031,8 +4656,6 @@
       <c r="G122" t="n">
         <v>20</v>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5056,7 +4679,6 @@
       <c r="D123" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -5065,8 +4687,6 @@
       <c r="G123" t="n">
         <v>20</v>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5090,7 +4710,6 @@
       <c r="D124" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -5099,8 +4718,6 @@
       <c r="G124" t="n">
         <v>24.3901</v>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5124,7 +4741,6 @@
       <c r="D125" t="n">
         <v>3186.8556</v>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -5133,8 +4749,6 @@
       <c r="G125" t="n">
         <v>11.7886</v>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -5158,7 +4772,6 @@
       <c r="D126" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -5167,8 +4780,6 @@
       <c r="G126" t="n">
         <v>9236.4177</v>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5192,7 +4803,6 @@
       <c r="D127" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -5201,8 +4811,6 @@
       <c r="G127" t="n">
         <v>3220</v>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5226,7 +4834,6 @@
       <c r="D128" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -5235,8 +4842,6 @@
       <c r="G128" t="n">
         <v>3102</v>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5260,7 +4865,6 @@
       <c r="D129" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -5269,8 +4873,6 @@
       <c r="G129" t="n">
         <v>2960</v>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5294,7 +4896,6 @@
       <c r="D130" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -5303,8 +4904,6 @@
       <c r="G130" t="n">
         <v>2875</v>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5328,7 +4927,6 @@
       <c r="D131" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -5337,8 +4935,6 @@
       <c r="G131" t="n">
         <v>2015</v>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5362,7 +4958,6 @@
       <c r="D132" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -5371,8 +4966,6 @@
       <c r="G132" t="n">
         <v>1542</v>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5396,7 +4989,6 @@
       <c r="D133" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -5405,8 +4997,6 @@
       <c r="G133" t="n">
         <v>1322</v>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5430,7 +5020,6 @@
       <c r="D134" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5439,8 +5028,6 @@
       <c r="G134" t="n">
         <v>1216</v>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5464,7 +5051,6 @@
       <c r="D135" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -5473,8 +5059,6 @@
       <c r="G135" t="n">
         <v>1125</v>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5498,7 +5082,6 @@
       <c r="D136" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -5507,8 +5090,6 @@
       <c r="G136" t="n">
         <v>1095</v>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5532,7 +5113,6 @@
       <c r="D137" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -5541,8 +5121,6 @@
       <c r="G137" t="n">
         <v>1095</v>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5566,7 +5144,6 @@
       <c r="D138" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -5575,8 +5152,6 @@
       <c r="G138" t="n">
         <v>798</v>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5600,7 +5175,6 @@
       <c r="D139" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -5609,8 +5183,6 @@
       <c r="G139" t="n">
         <v>547</v>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5634,7 +5206,6 @@
       <c r="D140" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -5643,8 +5214,6 @@
       <c r="G140" t="n">
         <v>140</v>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5668,7 +5237,6 @@
       <c r="D141" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -5677,8 +5245,6 @@
       <c r="G141" t="n">
         <v>304</v>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5702,7 +5268,6 @@
       <c r="D142" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -5711,8 +5276,6 @@
       <c r="G142" t="n">
         <v>304</v>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5736,7 +5299,6 @@
       <c r="D143" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -5745,8 +5307,6 @@
       <c r="G143" t="n">
         <v>407</v>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5770,7 +5330,6 @@
       <c r="D144" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5779,8 +5338,6 @@
       <c r="G144" t="n">
         <v>1520</v>
       </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5804,7 +5361,6 @@
       <c r="D145" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -5813,8 +5369,6 @@
       <c r="G145" t="n">
         <v>1216</v>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5838,7 +5392,6 @@
       <c r="D146" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -5847,8 +5400,6 @@
       <c r="G146" t="n">
         <v>912</v>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5872,7 +5423,6 @@
       <c r="D147" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -5881,8 +5431,6 @@
       <c r="G147" t="n">
         <v>760</v>
       </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5906,7 +5454,6 @@
       <c r="D148" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -5915,8 +5462,6 @@
       <c r="G148" t="n">
         <v>608</v>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5940,7 +5485,6 @@
       <c r="D149" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -5949,8 +5493,6 @@
       <c r="G149" t="n">
         <v>456</v>
       </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -5974,7 +5516,6 @@
       <c r="D150" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -5983,8 +5524,6 @@
       <c r="G150" t="n">
         <v>304</v>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6008,7 +5547,6 @@
       <c r="D151" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6017,8 +5555,6 @@
       <c r="G151" t="n">
         <v>304</v>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6042,7 +5578,6 @@
       <c r="D152" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6051,8 +5586,6 @@
       <c r="G152" t="n">
         <v>304</v>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6076,7 +5609,6 @@
       <c r="D153" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6085,8 +5617,6 @@
       <c r="G153" t="n">
         <v>370.8394</v>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6110,7 +5640,6 @@
       <c r="D154" t="n">
         <v>36648.8394</v>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -6119,8 +5648,6 @@
       <c r="G154" t="n">
         <v>179</v>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -6144,7 +5671,6 @@
       <c r="D155" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -6153,7 +5679,6 @@
       <c r="G155" t="n">
         <v>803.1668</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
         <v>25.2961</v>
       </c>
@@ -6180,7 +5705,6 @@
       <c r="D156" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -6189,7 +5713,6 @@
       <c r="G156" t="n">
         <v>280</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
         <v>8.8187</v>
       </c>
@@ -6216,7 +5739,6 @@
       <c r="D157" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -6225,7 +5747,6 @@
       <c r="G157" t="n">
         <v>270</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
         <v>8.5038</v>
       </c>
@@ -6252,7 +5773,6 @@
       <c r="D158" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -6261,7 +5781,6 @@
       <c r="G158" t="n">
         <v>257.4</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
         <v>8.1069</v>
       </c>
@@ -6288,7 +5807,6 @@
       <c r="D159" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -6297,7 +5815,6 @@
       <c r="G159" t="n">
         <v>250.0615</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
         <v>7.8758</v>
       </c>
@@ -6324,7 +5841,6 @@
       <c r="D160" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -6333,7 +5849,6 @@
       <c r="G160" t="n">
         <v>175.1887</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
         <v>5.5176</v>
       </c>
@@ -6360,7 +5875,6 @@
       <c r="D161" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -6369,7 +5883,6 @@
       <c r="G161" t="n">
         <v>157.1815</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
         <v>4.9505</v>
       </c>
@@ -6396,7 +5909,6 @@
       <c r="D162" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -6405,7 +5917,6 @@
       <c r="G162" t="n">
         <v>134.15</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
         <v>4.2251</v>
       </c>
@@ -6432,7 +5943,6 @@
       <c r="D163" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -6441,7 +5951,6 @@
       <c r="G163" t="n">
         <v>126.3621</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
         <v>3.9798</v>
       </c>
@@ -6468,7 +5977,6 @@
       <c r="D164" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -6477,7 +5985,6 @@
       <c r="G164" t="n">
         <v>114.9389</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
         <v>3.62</v>
       </c>
@@ -6504,7 +6011,6 @@
       <c r="D165" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -6513,7 +6019,6 @@
       <c r="G165" t="n">
         <v>69.48</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
         <v>2.1883</v>
       </c>
@@ -6540,7 +6045,6 @@
       <c r="D166" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>潘鼎</t>
@@ -6549,7 +6053,6 @@
       <c r="G166" t="n">
         <v>63.2</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
         <v>1.9905</v>
       </c>
@@ -6576,7 +6079,6 @@
       <c r="D167" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -6585,7 +6087,6 @@
       <c r="G167" t="n">
         <v>62.8726</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>1.9802</v>
       </c>
@@ -6612,7 +6113,6 @@
       <c r="D168" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -6621,7 +6121,6 @@
       <c r="G168" t="n">
         <v>62.8726</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>1.9802</v>
       </c>
@@ -6648,7 +6147,6 @@
       <c r="D169" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -6657,7 +6155,6 @@
       <c r="G169" t="n">
         <v>47.4</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>1.4929</v>
       </c>
@@ -6684,7 +6181,6 @@
       <c r="D170" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -6693,7 +6189,6 @@
       <c r="G170" t="n">
         <v>46.1846</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>1.4546</v>
       </c>
@@ -6720,7 +6215,6 @@
       <c r="D171" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -6729,7 +6223,6 @@
       <c r="G171" t="n">
         <v>40</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
         <v>1.2598</v>
       </c>
@@ -6756,7 +6249,6 @@
       <c r="D172" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6765,7 +6257,6 @@
       <c r="G172" t="n">
         <v>39.2954</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>1.2376</v>
       </c>
@@ -6792,7 +6283,6 @@
       <c r="D173" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>陈志华</t>
@@ -6801,7 +6291,6 @@
       <c r="G173" t="n">
         <v>30.04</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
         <v>0.9461000000000001</v>
       </c>
@@ -6828,7 +6317,6 @@
       <c r="D174" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>耿卫东</t>
@@ -6837,7 +6325,6 @@
       <c r="G174" t="n">
         <v>30</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
         <v>0.9449</v>
       </c>
@@ -6864,7 +6351,6 @@
       <c r="D175" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6873,7 +6359,6 @@
       <c r="G175" t="n">
         <v>23.5772</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0.7426</v>
       </c>
@@ -6900,7 +6385,6 @@
       <c r="D176" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -6909,7 +6393,6 @@
       <c r="G176" t="n">
         <v>20</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
         <v>0.6299</v>
       </c>
@@ -6936,7 +6419,6 @@
       <c r="D177" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -6945,7 +6427,6 @@
       <c r="G177" t="n">
         <v>19.4081</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
         <v>0.6113</v>
       </c>
@@ -6972,7 +6453,6 @@
       <c r="D178" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6981,7 +6461,6 @@
       <c r="G178" t="n">
         <v>15.7182</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0.4951</v>
       </c>
@@ -7008,7 +6487,6 @@
       <c r="D179" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -7017,7 +6495,6 @@
       <c r="G179" t="n">
         <v>15.5625</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>0.4901</v>
       </c>
@@ -7044,7 +6521,6 @@
       <c r="D180" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -7053,7 +6529,6 @@
       <c r="G180" t="n">
         <v>12.0034</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>0.3781</v>
       </c>
@@ -7080,7 +6555,6 @@
       <c r="D181" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -7089,7 +6563,6 @@
       <c r="G181" t="n">
         <v>3.0041</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
         <v>0.0946</v>
       </c>
@@ -7116,7 +6589,6 @@
       <c r="D182" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -7125,7 +6597,6 @@
       <c r="G182" t="n">
         <v>2.8079</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
         <v>0.08840000000000001</v>
       </c>
@@ -7152,7 +6623,6 @@
       <c r="D183" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -7161,7 +6631,6 @@
       <c r="G183" t="n">
         <v>2.0654</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
         <v>0.06510000000000001</v>
       </c>
@@ -7188,7 +6657,6 @@
       <c r="D184" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -7197,7 +6665,6 @@
       <c r="G184" t="n">
         <v>0.9699</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>0.0305</v>
       </c>
@@ -7224,7 +6691,6 @@
       <c r="D185" t="n">
         <v>3175.067</v>
       </c>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -7233,13 +6699,149 @@
       <c r="G185" t="n">
         <v>0.1556</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.0049</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴15条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量184条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>转让2条</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>31股东</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>比例合计100.00%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -6719,7 +6719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6730,20 +6730,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>时点</t>
+          <t>PDF页码</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>股东</t>
+          <t>股东/认购方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额(万股)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>校验结果</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -6758,17 +6783,22 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>认缴15条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>认缴流量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段完整</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15条,字段完整</t>
         </is>
       </c>
     </row>
@@ -6781,67 +6811,5604 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>存量184条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>股权存量</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>184条,t0存在</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>cross_check_total</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>转让2条</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>已合并</t>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2408</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6158.9225</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-3446.4699</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2712.4526</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6463.3751</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3156.8427</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-3306.5324</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3156.8427</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6907.7652</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3168.6313</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-3739.1339</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3168.6313</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6919.5538</v>
+      </c>
+      <c r="G9" t="n">
+        <v>40237.2571</v>
+      </c>
+      <c r="H9" t="n">
+        <v>33317.7033</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>40237.2571</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43988.1796</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-40813.1126</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>322</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>322</v>
+      </c>
+      <c r="G13" t="n">
+        <v>322</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="G15" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-3535.0134</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>80</v>
+      </c>
+      <c r="H16" t="n">
+        <v>80</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H17" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>36</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>36</v>
+      </c>
+      <c r="G19" t="n">
+        <v>36</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>87</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>87</v>
+      </c>
+      <c r="G20" t="n">
+        <v>87</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>74</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>74</v>
+      </c>
+      <c r="G21" t="n">
+        <v>74</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>72</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>72</v>
+      </c>
+      <c r="G24" t="n">
+        <v>72</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>72</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>72</v>
+      </c>
+      <c r="G26" t="n">
+        <v>72</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>220</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>220</v>
+      </c>
+      <c r="G27" t="n">
+        <v>220</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1035</v>
+      </c>
+      <c r="G28" t="n">
+        <v>976.7757</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-58.2243</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>322</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>322</v>
+      </c>
+      <c r="G31" t="n">
+        <v>322</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>20</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G33" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>80</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>80</v>
+      </c>
+      <c r="G34" t="n">
+        <v>80</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G35" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>20</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>36</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>36</v>
+      </c>
+      <c r="G37" t="n">
+        <v>36</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>87</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>87</v>
+      </c>
+      <c r="G38" t="n">
+        <v>87</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>74</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>74</v>
+      </c>
+      <c r="G39" t="n">
+        <v>74</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>72</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>72</v>
+      </c>
+      <c r="G42" t="n">
+        <v>72</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>72</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>72</v>
+      </c>
+      <c r="G44" t="n">
+        <v>72</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>220</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>220</v>
+      </c>
+      <c r="G45" t="n">
+        <v>242</v>
+      </c>
+      <c r="H45" t="n">
+        <v>22</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>976.7757</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>976.7757</v>
+      </c>
+      <c r="G46" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>322</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>322</v>
+      </c>
+      <c r="G49" t="n">
+        <v>322</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" t="n">
+        <v>20</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G51" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>80</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>80</v>
+      </c>
+      <c r="G52" t="n">
+        <v>80</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G53" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>20</v>
+      </c>
+      <c r="G54" t="n">
+        <v>20</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>36</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>36</v>
+      </c>
+      <c r="G55" t="n">
+        <v>36</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>87</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>87</v>
+      </c>
+      <c r="G56" t="n">
+        <v>87</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>74</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>74</v>
+      </c>
+      <c r="G57" t="n">
+        <v>74</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>72</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>72</v>
+      </c>
+      <c r="G60" t="n">
+        <v>72</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>72</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>72</v>
+      </c>
+      <c r="G62" t="n">
+        <v>72</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>242</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>242</v>
+      </c>
+      <c r="G63" t="n">
+        <v>242</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="G64" t="n">
+        <v>954.7757</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G66" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="H67" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>322</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>322</v>
+      </c>
+      <c r="G68" t="n">
+        <v>322</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>20</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" t="n">
+        <v>20</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G70" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>50</v>
+      </c>
+      <c r="H71" t="n">
+        <v>50</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>40</v>
+      </c>
+      <c r="H73" t="n">
+        <v>40</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>20</v>
+      </c>
+      <c r="H74" t="n">
+        <v>20</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>80</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>80</v>
+      </c>
+      <c r="G75" t="n">
+        <v>80</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>20</v>
+      </c>
+      <c r="H76" t="n">
+        <v>20</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G77" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>20</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20</v>
+      </c>
+      <c r="G78" t="n">
+        <v>20</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>36</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>36</v>
+      </c>
+      <c r="G79" t="n">
+        <v>36</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>100</v>
+      </c>
+      <c r="H80" t="n">
+        <v>100</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>80</v>
+      </c>
+      <c r="H81" t="n">
+        <v>80</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>20</v>
+      </c>
+      <c r="H82" t="n">
+        <v>20</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>87</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>87</v>
+      </c>
+      <c r="G83" t="n">
+        <v>87</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>74</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>74</v>
+      </c>
+      <c r="G84" t="n">
+        <v>74</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G86" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="G87" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>322</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>322</v>
+      </c>
+      <c r="G88" t="n">
+        <v>322</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>20</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>20</v>
+      </c>
+      <c r="G89" t="n">
+        <v>20</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G90" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-3750.9225</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>50</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>50</v>
+      </c>
+      <c r="G91" t="n">
+        <v>50</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>30</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>30</v>
+      </c>
+      <c r="G92" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>40</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>40</v>
+      </c>
+      <c r="G93" t="n">
+        <v>40</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>20</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>20</v>
+      </c>
+      <c r="G94" t="n">
+        <v>20</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>80</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>80</v>
+      </c>
+      <c r="G95" t="n">
+        <v>80</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>20</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>20</v>
+      </c>
+      <c r="G96" t="n">
+        <v>20</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G97" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>20</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>20</v>
+      </c>
+      <c r="G98" t="n">
+        <v>20</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>36</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>36</v>
+      </c>
+      <c r="G99" t="n">
+        <v>36</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>100</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>100</v>
+      </c>
+      <c r="G100" t="n">
+        <v>100</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>80</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>80</v>
+      </c>
+      <c r="G101" t="n">
+        <v>80</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>20</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>20</v>
+      </c>
+      <c r="G102" t="n">
+        <v>20</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="H103" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>87</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>87</v>
+      </c>
+      <c r="G104" t="n">
+        <v>87</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1882.5</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G106" t="n">
+        <v>140</v>
+      </c>
+      <c r="H106" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>24.3901</v>
+      </c>
+      <c r="G107" t="n">
+        <v>370.8394</v>
+      </c>
+      <c r="H107" t="n">
+        <v>346.4493</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>322</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>322</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3220</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2898</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>20</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>20</v>
+      </c>
+      <c r="G109" t="n">
+        <v>304</v>
+      </c>
+      <c r="H109" t="n">
+        <v>284</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>215.9091</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F110" t="n">
+        <v>3966.8316</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2875</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-1091.8316</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>50</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>50</v>
+      </c>
+      <c r="G111" t="n">
+        <v>760</v>
+      </c>
+      <c r="H111" t="n">
+        <v>710</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>30</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>30</v>
+      </c>
+      <c r="G112" t="n">
+        <v>456</v>
+      </c>
+      <c r="H112" t="n">
+        <v>426</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>40</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>40</v>
+      </c>
+      <c r="G113" t="n">
+        <v>608</v>
+      </c>
+      <c r="H113" t="n">
+        <v>568</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>20</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>20</v>
+      </c>
+      <c r="G114" t="n">
+        <v>304</v>
+      </c>
+      <c r="H114" t="n">
+        <v>284</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>80</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>80</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1136</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>20</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>20</v>
+      </c>
+      <c r="G116" t="n">
+        <v>304</v>
+      </c>
+      <c r="H116" t="n">
+        <v>284</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>26.7678</v>
+      </c>
+      <c r="G117" t="n">
+        <v>407</v>
+      </c>
+      <c r="H117" t="n">
+        <v>380.2322</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>20</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>20</v>
+      </c>
+      <c r="G118" t="n">
+        <v>304</v>
+      </c>
+      <c r="H118" t="n">
+        <v>284</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>36</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>36</v>
+      </c>
+      <c r="G119" t="n">
+        <v>547</v>
+      </c>
+      <c r="H119" t="n">
+        <v>511</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>100</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>100</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1520</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>80</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>80</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1136</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>20</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>20</v>
+      </c>
+      <c r="G122" t="n">
+        <v>304</v>
+      </c>
+      <c r="H122" t="n">
+        <v>284</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="G123" t="n">
+        <v>179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>167.2114</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>87</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>87</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1322</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1235</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>t5-&gt;t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G125" t="n">
+        <v>175.1887</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-1839.8113</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>140</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>140</v>
+      </c>
+      <c r="G126" t="n">
+        <v>12.0034</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-127.9966</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>370.8394</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>370.8394</v>
+      </c>
+      <c r="G127" t="n">
+        <v>15.7182</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-355.1212</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>3220</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3220</v>
+      </c>
+      <c r="G128" t="n">
+        <v>280</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-2940</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>304</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>304</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3.0041</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-300.9959</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2875</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3750.9225</v>
+      </c>
+      <c r="F130" t="n">
+        <v>6625.9225</v>
+      </c>
+      <c r="G130" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-6375.861</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>760</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>760</v>
+      </c>
+      <c r="G131" t="n">
+        <v>46.1846</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-713.8154</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>456</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>456</v>
+      </c>
+      <c r="G132" t="n">
+        <v>15.5625</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-440.4375</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>608</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>608</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-607.0300999999999</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>304</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>304</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-303.8444</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1216</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1216</v>
+      </c>
+      <c r="G135" t="n">
+        <v>126.3621</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-1089.6379</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>304</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>304</v>
+      </c>
+      <c r="G136" t="n">
+        <v>39.2954</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-264.7046</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>407</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>407</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2.0654</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-404.9346</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>304</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>304</v>
+      </c>
+      <c r="G138" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-284.5919</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>547</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>547</v>
+      </c>
+      <c r="G139" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-499.6</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1520</v>
+      </c>
+      <c r="G140" t="n">
+        <v>157.1815</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-1362.8185</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>潘鼎</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1216</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1216</v>
+      </c>
+      <c r="G142" t="n">
+        <v>62.8726</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-1153.1274</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>304</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>304</v>
+      </c>
+      <c r="G143" t="n">
+        <v>23.5772</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-280.4228</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>耿卫东</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>30</v>
+      </c>
+      <c r="H144" t="n">
+        <v>30</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>t6-&gt;发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
           <t>ratio_check</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>发行前（第59页股东表）</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>13股东</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>t0比例合计97.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>18股东</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>t1比例合计102.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>18股东</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>t2比例合计102.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>18股东</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>t3比例合计102.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>28股东</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>t4比例合计116.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>29股东</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>t5比例合计116.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>29股东</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>t6比例合计116.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
         <is>
           <t>31股东</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>比例合计100.00%</t>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）比例合计100.00%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +474,7 @@
       <c r="E2" t="n">
         <v>13500</v>
       </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -501,6 +501,7 @@
       <c r="E3" t="n">
         <v>13500</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -527,6 +528,7 @@
       <c r="E4" t="n">
         <v>13500</v>
       </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -553,6 +555,7 @@
       <c r="E5" t="n">
         <v>13500</v>
       </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -579,6 +582,7 @@
       <c r="E6" t="n">
         <v>13500</v>
       </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -605,6 +609,7 @@
       <c r="E7" t="n">
         <v>13500</v>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -631,6 +636,7 @@
       <c r="E8" t="n">
         <v>13500</v>
       </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -657,6 +663,7 @@
       <c r="E9" t="n">
         <v>13500</v>
       </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -683,6 +690,7 @@
       <c r="E10" t="n">
         <v>13500</v>
       </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -709,6 +717,7 @@
       <c r="E11" t="n">
         <v>13500</v>
       </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -735,6 +744,7 @@
       <c r="E12" t="n">
         <v>13500</v>
       </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -761,6 +771,7 @@
       <c r="E13" t="n">
         <v>13500</v>
       </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -787,6 +798,7 @@
       <c r="E14" t="n">
         <v>13500</v>
       </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -813,6 +825,7 @@
       <c r="E15" t="n">
         <v>13500</v>
       </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
@@ -839,9 +852,329 @@
       <c r="E16" t="n">
         <v>13500</v>
       </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>59</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>157.1815</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Markdown: 源峰磐赛认购1571815股/20000.0万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>59</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>62.8726</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Markdown: 珠海峦恒认购628726股/8000.0万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>59</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>62.8726</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Markdown: 高瓴祈睿认购628726股/8000.0万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>59</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>46.1846</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5876.59</v>
+      </c>
+      <c r="F20" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Markdown: 国药中生认购461846股/5876.59万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>59</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="E21" t="n">
+        <v>123.41</v>
+      </c>
+      <c r="F21" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Markdown: 圣成投资认购9699股/123.41万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>59</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15.5625</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1980.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Markdown: 国药二期认购155625股/1980.2万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>59</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="E23" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Markdown: 圣祁投资认购1556股/19.8万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>59</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>39.2954</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Markdown: 夏尔巴二期认购392954股/5000.0万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>59</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>23.5772</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Markdown: 甘李药业认购235772股/3000.0万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>59</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>15.7182</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Markdown: 吴征涛认购157182股/2000.0万元@127.24元/股</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>60</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2021-12-06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.7886</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F27" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>赛分科技增发股份117,886股,由聚贝投资以1500万元认购</t>
         </is>
       </c>
     </row>
@@ -928,6 +1261,7 @@
       <c r="D2" t="n">
         <v>2408</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -935,6 +1269,12 @@
       </c>
       <c r="G2" t="n">
         <v>1035</v>
+      </c>
+      <c r="H2" t="n">
+        <v>900</v>
+      </c>
+      <c r="I2" t="n">
+        <v>45.59</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -959,6 +1299,7 @@
       <c r="D3" t="n">
         <v>2408</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -966,6 +1307,12 @@
       </c>
       <c r="G3" t="n">
         <v>322</v>
+      </c>
+      <c r="H3" t="n">
+        <v>280</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.1793</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -990,6 +1337,7 @@
       <c r="D4" t="n">
         <v>2408</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -997,6 +1345,12 @@
       </c>
       <c r="G4" t="n">
         <v>220</v>
+      </c>
+      <c r="H4" t="n">
+        <v>248</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.815799999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1021,6 +1375,7 @@
       <c r="D5" t="n">
         <v>2408</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1028,6 +1383,12 @@
       </c>
       <c r="G5" t="n">
         <v>194.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.357699999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1052,6 +1413,7 @@
       <c r="D6" t="n">
         <v>2408</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1059,6 +1421,12 @@
       </c>
       <c r="G6" t="n">
         <v>132.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.3689</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1083,6 +1451,7 @@
       <c r="D7" t="n">
         <v>2408</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1090,6 +1459,12 @@
       </c>
       <c r="G7" t="n">
         <v>101.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.877</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1114,6 +1489,7 @@
       <c r="D8" t="n">
         <v>2408</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1121,6 +1497,12 @@
       </c>
       <c r="G8" t="n">
         <v>87</v>
+      </c>
+      <c r="H8" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.1786</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1145,6 +1527,7 @@
       <c r="D9" t="n">
         <v>2408</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1152,6 +1535,12 @@
       </c>
       <c r="G9" t="n">
         <v>52.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5259</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1176,6 +1565,7 @@
       <c r="D10" t="n">
         <v>2408</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1183,6 +1573,12 @@
       </c>
       <c r="G10" t="n">
         <v>36</v>
+      </c>
+      <c r="H10" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.7232</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1207,6 +1603,7 @@
       <c r="D11" t="n">
         <v>2408</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1214,6 +1611,12 @@
       </c>
       <c r="G11" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4364</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1238,6 +1641,7 @@
       <c r="D12" t="n">
         <v>2408</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1245,6 +1649,12 @@
       </c>
       <c r="G12" t="n">
         <v>72</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7271</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1269,6 +1679,7 @@
       <c r="D13" t="n">
         <v>2408</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1276,6 +1687,12 @@
       </c>
       <c r="G13" t="n">
         <v>72</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1021</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1300,6 +1717,7 @@
       <c r="D14" t="n">
         <v>2408</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1307,6 +1725,12 @@
       </c>
       <c r="G14" t="n">
         <v>74</v>
+      </c>
+      <c r="H14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.4542</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1331,6 +1755,7 @@
       <c r="D15" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1338,6 +1763,12 @@
       </c>
       <c r="G15" t="n">
         <v>976.7757</v>
+      </c>
+      <c r="H15" t="n">
+        <v>900</v>
+      </c>
+      <c r="I15" t="n">
+        <v>45.59</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1362,6 +1793,7 @@
       <c r="D16" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1369,6 +1801,12 @@
       </c>
       <c r="G16" t="n">
         <v>322</v>
+      </c>
+      <c r="H16" t="n">
+        <v>280</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.1793</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1393,6 +1831,7 @@
       <c r="D17" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1400,6 +1839,12 @@
       </c>
       <c r="G17" t="n">
         <v>220</v>
+      </c>
+      <c r="H17" t="n">
+        <v>248</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.815799999999999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1424,6 +1869,7 @@
       <c r="D18" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1431,6 +1877,12 @@
       </c>
       <c r="G18" t="n">
         <v>194.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.357699999999999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1455,6 +1907,7 @@
       <c r="D19" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -1463,6 +1916,8 @@
       <c r="G19" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -1486,6 +1941,7 @@
       <c r="D20" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -1493,6 +1949,12 @@
       </c>
       <c r="G20" t="n">
         <v>132.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.3689</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1517,6 +1979,7 @@
       <c r="D21" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -1524,6 +1987,12 @@
       </c>
       <c r="G21" t="n">
         <v>101.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.877</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1548,6 +2017,7 @@
       <c r="D22" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -1555,6 +2025,12 @@
       </c>
       <c r="G22" t="n">
         <v>87</v>
+      </c>
+      <c r="H22" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.1786</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1579,6 +2055,7 @@
       <c r="D23" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -1586,6 +2063,12 @@
       </c>
       <c r="G23" t="n">
         <v>80</v>
+      </c>
+      <c r="H23" t="n">
+        <v>89.0431</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.5939</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1610,6 +2093,7 @@
       <c r="D24" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -1617,6 +2101,12 @@
       </c>
       <c r="G24" t="n">
         <v>74</v>
+      </c>
+      <c r="H24" t="n">
+        <v>40</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.4542</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1641,6 +2131,7 @@
       <c r="D25" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -1648,6 +2139,12 @@
       </c>
       <c r="G25" t="n">
         <v>72</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7271</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1672,6 +2169,7 @@
       <c r="D26" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -1679,6 +2177,12 @@
       </c>
       <c r="G26" t="n">
         <v>72</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1021</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1703,6 +2207,7 @@
       <c r="D27" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -1710,6 +2215,12 @@
       </c>
       <c r="G27" t="n">
         <v>52.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.5259</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1734,6 +2245,7 @@
       <c r="D28" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -1741,6 +2253,12 @@
       </c>
       <c r="G28" t="n">
         <v>36</v>
+      </c>
+      <c r="H28" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.7232</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1765,6 +2283,7 @@
       <c r="D29" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -1772,6 +2291,12 @@
       </c>
       <c r="G29" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4364</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1796,6 +2321,7 @@
       <c r="D30" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -1803,6 +2329,12 @@
       </c>
       <c r="G30" t="n">
         <v>20</v>
+      </c>
+      <c r="H30" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7056</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1827,6 +2359,7 @@
       <c r="D31" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -1834,6 +2367,12 @@
       </c>
       <c r="G31" t="n">
         <v>20</v>
+      </c>
+      <c r="H31" t="n">
+        <v>45.7143</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1092</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1858,6 +2397,7 @@
       <c r="D32" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -1865,6 +2405,12 @@
       </c>
       <c r="G32" t="n">
         <v>26.7678</v>
+      </c>
+      <c r="H32" t="n">
+        <v>31.4286</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.0751</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1889,6 +2435,7 @@
       <c r="D33" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -1896,6 +2443,12 @@
       </c>
       <c r="G33" t="n">
         <v>954.7757</v>
+      </c>
+      <c r="H33" t="n">
+        <v>900</v>
+      </c>
+      <c r="I33" t="n">
+        <v>45.59</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1920,6 +2473,7 @@
       <c r="D34" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -1927,6 +2481,12 @@
       </c>
       <c r="G34" t="n">
         <v>322</v>
+      </c>
+      <c r="H34" t="n">
+        <v>280</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.1793</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1951,6 +2511,7 @@
       <c r="D35" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -1958,6 +2519,12 @@
       </c>
       <c r="G35" t="n">
         <v>242</v>
+      </c>
+      <c r="H35" t="n">
+        <v>248</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9.815799999999999</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1982,6 +2549,7 @@
       <c r="D36" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -1989,6 +2557,12 @@
       </c>
       <c r="G36" t="n">
         <v>194.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>9.357699999999999</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2013,6 +2587,7 @@
       <c r="D37" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2021,6 +2596,8 @@
       <c r="G37" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>本次股权转让后，赛分有限的股权结构如下：</t>
@@ -2044,6 +2621,7 @@
       <c r="D38" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2051,6 +2629,12 @@
       </c>
       <c r="G38" t="n">
         <v>132.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6.3689</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2075,6 +2659,7 @@
       <c r="D39" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2082,6 +2667,12 @@
       </c>
       <c r="G39" t="n">
         <v>101.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.877</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2106,6 +2697,7 @@
       <c r="D40" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2113,6 +2705,12 @@
       </c>
       <c r="G40" t="n">
         <v>87</v>
+      </c>
+      <c r="H40" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.1786</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2137,6 +2735,7 @@
       <c r="D41" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2144,6 +2743,12 @@
       </c>
       <c r="G41" t="n">
         <v>80</v>
+      </c>
+      <c r="H41" t="n">
+        <v>89.0431</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4.5939</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2168,6 +2773,7 @@
       <c r="D42" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2175,6 +2781,12 @@
       </c>
       <c r="G42" t="n">
         <v>74</v>
+      </c>
+      <c r="H42" t="n">
+        <v>40</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.4542</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2199,6 +2811,7 @@
       <c r="D43" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2206,6 +2819,12 @@
       </c>
       <c r="G43" t="n">
         <v>72</v>
+      </c>
+      <c r="H43" t="n">
+        <v>20</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7271</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2230,6 +2849,7 @@
       <c r="D44" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2237,6 +2857,12 @@
       </c>
       <c r="G44" t="n">
         <v>72</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1021</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2261,6 +2887,7 @@
       <c r="D45" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2268,6 +2895,12 @@
       </c>
       <c r="G45" t="n">
         <v>52.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.5259</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2292,6 +2925,7 @@
       <c r="D46" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2299,6 +2933,12 @@
       </c>
       <c r="G46" t="n">
         <v>36</v>
+      </c>
+      <c r="H46" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.7232</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2323,6 +2963,7 @@
       <c r="D47" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2330,6 +2971,12 @@
       </c>
       <c r="G47" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="H47" t="n">
+        <v>12</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.4364</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2354,6 +3001,7 @@
       <c r="D48" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2361,6 +3009,12 @@
       </c>
       <c r="G48" t="n">
         <v>20</v>
+      </c>
+      <c r="H48" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7056</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2385,6 +3039,7 @@
       <c r="D49" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2392,6 +3047,12 @@
       </c>
       <c r="G49" t="n">
         <v>20</v>
+      </c>
+      <c r="H49" t="n">
+        <v>45.7143</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1092</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2416,6 +3077,7 @@
       <c r="D50" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2423,6 +3085,12 @@
       </c>
       <c r="G50" t="n">
         <v>26.7678</v>
+      </c>
+      <c r="H50" t="n">
+        <v>31.4286</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.0751</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2447,6 +3115,7 @@
       <c r="D51" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -2454,6 +3123,12 @@
       </c>
       <c r="G51" t="n">
         <v>954.7757</v>
+      </c>
+      <c r="H51" t="n">
+        <v>900</v>
+      </c>
+      <c r="I51" t="n">
+        <v>45.59</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2478,6 +3153,7 @@
       <c r="D52" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -2485,6 +3161,12 @@
       </c>
       <c r="G52" t="n">
         <v>322</v>
+      </c>
+      <c r="H52" t="n">
+        <v>280</v>
+      </c>
+      <c r="I52" t="n">
+        <v>10.1793</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2509,6 +3191,7 @@
       <c r="D53" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -2516,6 +3199,12 @@
       </c>
       <c r="G53" t="n">
         <v>242</v>
+      </c>
+      <c r="H53" t="n">
+        <v>248</v>
+      </c>
+      <c r="I53" t="n">
+        <v>9.815799999999999</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2540,6 +3229,7 @@
       <c r="D54" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -2547,6 +3237,12 @@
       </c>
       <c r="G54" t="n">
         <v>194.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="I54" t="n">
+        <v>9.357699999999999</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2571,6 +3267,7 @@
       <c r="D55" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -2579,6 +3276,8 @@
       <c r="G55" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>整体变更为股份有限公司后，赛分科技的股权结构如下：</t>
@@ -2602,6 +3301,7 @@
       <c r="D56" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -2609,6 +3309,12 @@
       </c>
       <c r="G56" t="n">
         <v>132.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="I56" t="n">
+        <v>6.3689</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2633,6 +3339,7 @@
       <c r="D57" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -2640,6 +3347,12 @@
       </c>
       <c r="G57" t="n">
         <v>101.3</v>
+      </c>
+      <c r="H57" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="I57" t="n">
+        <v>4.877</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2664,6 +3377,7 @@
       <c r="D58" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -2671,6 +3385,12 @@
       </c>
       <c r="G58" t="n">
         <v>87</v>
+      </c>
+      <c r="H58" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4.1786</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2695,6 +3415,7 @@
       <c r="D59" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -2702,6 +3423,12 @@
       </c>
       <c r="G59" t="n">
         <v>80</v>
+      </c>
+      <c r="H59" t="n">
+        <v>89.0431</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4.5939</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2726,6 +3453,7 @@
       <c r="D60" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -2733,6 +3461,12 @@
       </c>
       <c r="G60" t="n">
         <v>74</v>
+      </c>
+      <c r="H60" t="n">
+        <v>40</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.4542</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2757,6 +3491,7 @@
       <c r="D61" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -2764,6 +3499,12 @@
       </c>
       <c r="G61" t="n">
         <v>72</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.7271</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2788,6 +3529,7 @@
       <c r="D62" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -2795,6 +3537,12 @@
       </c>
       <c r="G62" t="n">
         <v>72</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.1021</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2819,6 +3567,7 @@
       <c r="D63" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -2826,6 +3575,12 @@
       </c>
       <c r="G63" t="n">
         <v>52.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.5259</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2850,6 +3605,7 @@
       <c r="D64" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -2857,6 +3613,12 @@
       </c>
       <c r="G64" t="n">
         <v>36</v>
+      </c>
+      <c r="H64" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.7232</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2881,6 +3643,7 @@
       <c r="D65" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -2888,6 +3651,12 @@
       </c>
       <c r="G65" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="H65" t="n">
+        <v>12</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.4364</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2912,6 +3681,7 @@
       <c r="D66" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -2919,6 +3689,12 @@
       </c>
       <c r="G66" t="n">
         <v>20</v>
+      </c>
+      <c r="H66" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.7056</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2943,6 +3719,7 @@
       <c r="D67" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -2950,6 +3727,12 @@
       </c>
       <c r="G67" t="n">
         <v>20</v>
+      </c>
+      <c r="H67" t="n">
+        <v>45.7143</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.1092</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2974,6 +3757,7 @@
       <c r="D68" t="n">
         <v>2750.6769</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -2981,6 +3765,12 @@
       </c>
       <c r="G68" t="n">
         <v>26.7678</v>
+      </c>
+      <c r="H68" t="n">
+        <v>31.4286</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.0751</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3005,6 +3795,7 @@
       <c r="D69" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3012,6 +3803,12 @@
       </c>
       <c r="G69" t="n">
         <v>954.7757</v>
+      </c>
+      <c r="H69" t="n">
+        <v>900</v>
+      </c>
+      <c r="I69" t="n">
+        <v>45.59</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3036,6 +3833,7 @@
       <c r="D70" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3043,6 +3841,12 @@
       </c>
       <c r="G70" t="n">
         <v>322</v>
+      </c>
+      <c r="H70" t="n">
+        <v>280</v>
+      </c>
+      <c r="I70" t="n">
+        <v>10.1793</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3067,6 +3871,7 @@
       <c r="D71" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3074,6 +3879,12 @@
       </c>
       <c r="G71" t="n">
         <v>242</v>
+      </c>
+      <c r="H71" t="n">
+        <v>248</v>
+      </c>
+      <c r="I71" t="n">
+        <v>9.815799999999999</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3098,6 +3909,7 @@
       <c r="D72" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3105,6 +3917,12 @@
       </c>
       <c r="G72" t="n">
         <v>194.5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="I72" t="n">
+        <v>9.357699999999999</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3129,6 +3947,7 @@
       <c r="D73" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -3137,6 +3956,8 @@
       <c r="G73" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -3160,6 +3981,7 @@
       <c r="D74" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -3167,6 +3989,12 @@
       </c>
       <c r="G74" t="n">
         <v>132.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6.3689</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3191,6 +4019,7 @@
       <c r="D75" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -3198,6 +4027,12 @@
       </c>
       <c r="G75" t="n">
         <v>101.3</v>
+      </c>
+      <c r="H75" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="I75" t="n">
+        <v>4.877</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3222,6 +4057,7 @@
       <c r="D76" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -3229,6 +4065,12 @@
       </c>
       <c r="G76" t="n">
         <v>87</v>
+      </c>
+      <c r="H76" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="I76" t="n">
+        <v>4.1786</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3253,6 +4095,7 @@
       <c r="D77" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -3260,6 +4103,12 @@
       </c>
       <c r="G77" t="n">
         <v>80</v>
+      </c>
+      <c r="H77" t="n">
+        <v>89.0431</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4.5939</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3284,6 +4133,7 @@
       <c r="D78" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -3291,6 +4141,12 @@
       </c>
       <c r="G78" t="n">
         <v>74</v>
+      </c>
+      <c r="H78" t="n">
+        <v>40</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1.4542</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3315,6 +4171,7 @@
       <c r="D79" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -3322,6 +4179,12 @@
       </c>
       <c r="G79" t="n">
         <v>72</v>
+      </c>
+      <c r="H79" t="n">
+        <v>20</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.7271</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3346,6 +4209,7 @@
       <c r="D80" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -3353,6 +4217,12 @@
       </c>
       <c r="G80" t="n">
         <v>72</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.1021</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3377,6 +4247,7 @@
       <c r="D81" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -3384,6 +4255,12 @@
       </c>
       <c r="G81" t="n">
         <v>52.5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.5259</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3408,6 +4285,7 @@
       <c r="D82" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -3415,6 +4293,12 @@
       </c>
       <c r="G82" t="n">
         <v>36</v>
+      </c>
+      <c r="H82" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.7232</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3439,6 +4323,7 @@
       <c r="D83" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -3446,6 +4331,12 @@
       </c>
       <c r="G83" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="H83" t="n">
+        <v>12</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.4364</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3470,6 +4361,7 @@
       <c r="D84" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -3477,6 +4369,12 @@
       </c>
       <c r="G84" t="n">
         <v>20</v>
+      </c>
+      <c r="H84" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.7056</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3501,6 +4399,7 @@
       <c r="D85" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -3508,6 +4407,12 @@
       </c>
       <c r="G85" t="n">
         <v>20</v>
+      </c>
+      <c r="H85" t="n">
+        <v>45.7143</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.1092</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3532,6 +4437,7 @@
       <c r="D86" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -3539,6 +4445,12 @@
       </c>
       <c r="G86" t="n">
         <v>26.7678</v>
+      </c>
+      <c r="H86" t="n">
+        <v>31.4286</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.0751</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3563,6 +4475,7 @@
       <c r="D87" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -3570,6 +4483,10 @@
       </c>
       <c r="G87" t="n">
         <v>100</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>4.9505</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3594,6 +4511,7 @@
       <c r="D88" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -3601,6 +4519,10 @@
       </c>
       <c r="G88" t="n">
         <v>80</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>1.9802</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3625,6 +4547,7 @@
       <c r="D89" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -3632,6 +4555,10 @@
       </c>
       <c r="G89" t="n">
         <v>60</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>1.9802</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -3656,6 +4583,7 @@
       <c r="D90" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -3663,6 +4591,10 @@
       </c>
       <c r="G90" t="n">
         <v>50</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>1.4546</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3687,6 +4619,7 @@
       <c r="D91" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -3694,6 +4627,10 @@
       </c>
       <c r="G91" t="n">
         <v>40</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>0.0305</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3718,6 +4655,7 @@
       <c r="D92" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -3725,6 +4663,10 @@
       </c>
       <c r="G92" t="n">
         <v>30</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>0.4901</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3749,6 +4691,7 @@
       <c r="D93" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -3756,6 +4699,10 @@
       </c>
       <c r="G93" t="n">
         <v>20</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>0.0049</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3780,6 +4727,7 @@
       <c r="D94" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -3787,6 +4735,10 @@
       </c>
       <c r="G94" t="n">
         <v>20</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>1.2376</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -3811,6 +4763,7 @@
       <c r="D95" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -3818,6 +4771,10 @@
       </c>
       <c r="G95" t="n">
         <v>20</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>0.7426</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -3842,6 +4799,7 @@
       <c r="D96" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -3849,6 +4807,10 @@
       </c>
       <c r="G96" t="n">
         <v>24.3901</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>0.4951</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -3873,6 +4835,7 @@
       <c r="D97" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -3880,6 +4843,12 @@
       </c>
       <c r="G97" t="n">
         <v>954.7757</v>
+      </c>
+      <c r="H97" t="n">
+        <v>900</v>
+      </c>
+      <c r="I97" t="n">
+        <v>45.59</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -3904,6 +4873,7 @@
       <c r="D98" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -3911,6 +4881,12 @@
       </c>
       <c r="G98" t="n">
         <v>322</v>
+      </c>
+      <c r="H98" t="n">
+        <v>280</v>
+      </c>
+      <c r="I98" t="n">
+        <v>10.1793</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -3935,6 +4911,7 @@
       <c r="D99" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -3942,6 +4919,12 @@
       </c>
       <c r="G99" t="n">
         <v>242</v>
+      </c>
+      <c r="H99" t="n">
+        <v>248</v>
+      </c>
+      <c r="I99" t="n">
+        <v>9.815799999999999</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -3966,6 +4949,7 @@
       <c r="D100" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -3973,6 +4957,12 @@
       </c>
       <c r="G100" t="n">
         <v>194.5</v>
+      </c>
+      <c r="H100" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="I100" t="n">
+        <v>9.357699999999999</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -3997,6 +4987,7 @@
       <c r="D101" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4005,6 +4996,8 @@
       <c r="G101" t="n">
         <v>215.9091</v>
       </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>本次增资完成后，赛分科技的股权结构如下：</t>
@@ -4028,6 +5021,7 @@
       <c r="D102" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4035,6 +5029,12 @@
       </c>
       <c r="G102" t="n">
         <v>132.5</v>
+      </c>
+      <c r="H102" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="I102" t="n">
+        <v>6.3689</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4059,6 +5059,7 @@
       <c r="D103" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4066,6 +5067,12 @@
       </c>
       <c r="G103" t="n">
         <v>101.3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="I103" t="n">
+        <v>4.877</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4090,6 +5097,7 @@
       <c r="D104" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4097,6 +5105,12 @@
       </c>
       <c r="G104" t="n">
         <v>87</v>
+      </c>
+      <c r="H104" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="I104" t="n">
+        <v>4.1786</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4121,6 +5135,7 @@
       <c r="D105" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -4128,6 +5143,12 @@
       </c>
       <c r="G105" t="n">
         <v>80</v>
+      </c>
+      <c r="H105" t="n">
+        <v>89.0431</v>
+      </c>
+      <c r="I105" t="n">
+        <v>4.5939</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4152,6 +5173,7 @@
       <c r="D106" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -4159,6 +5181,12 @@
       </c>
       <c r="G106" t="n">
         <v>74</v>
+      </c>
+      <c r="H106" t="n">
+        <v>40</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1.4542</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4183,6 +5211,7 @@
       <c r="D107" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -4190,6 +5219,12 @@
       </c>
       <c r="G107" t="n">
         <v>72</v>
+      </c>
+      <c r="H107" t="n">
+        <v>20</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.7271</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4214,6 +5249,7 @@
       <c r="D108" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -4221,6 +5257,12 @@
       </c>
       <c r="G108" t="n">
         <v>72</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.1021</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4245,6 +5287,7 @@
       <c r="D109" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -4252,6 +5295,12 @@
       </c>
       <c r="G109" t="n">
         <v>52.5</v>
+      </c>
+      <c r="H109" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="I109" t="n">
+        <v>2.5259</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4276,6 +5325,7 @@
       <c r="D110" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -4283,6 +5333,12 @@
       </c>
       <c r="G110" t="n">
         <v>36</v>
+      </c>
+      <c r="H110" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1.7232</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4307,6 +5363,7 @@
       <c r="D111" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -4314,6 +5371,12 @@
       </c>
       <c r="G111" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="H111" t="n">
+        <v>12</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.4364</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -4338,6 +5401,7 @@
       <c r="D112" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -4345,6 +5409,12 @@
       </c>
       <c r="G112" t="n">
         <v>20</v>
+      </c>
+      <c r="H112" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.7056</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4369,6 +5439,7 @@
       <c r="D113" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -4376,6 +5447,12 @@
       </c>
       <c r="G113" t="n">
         <v>20</v>
+      </c>
+      <c r="H113" t="n">
+        <v>45.7143</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.1092</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -4400,6 +5477,7 @@
       <c r="D114" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -4407,6 +5485,12 @@
       </c>
       <c r="G114" t="n">
         <v>26.7678</v>
+      </c>
+      <c r="H114" t="n">
+        <v>31.4286</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.0751</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4431,6 +5515,7 @@
       <c r="D115" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -4438,6 +5523,10 @@
       </c>
       <c r="G115" t="n">
         <v>100</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="n">
+        <v>4.9505</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4462,6 +5551,7 @@
       <c r="D116" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -4469,6 +5559,10 @@
       </c>
       <c r="G116" t="n">
         <v>80</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>1.9802</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4493,6 +5587,7 @@
       <c r="D117" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -4500,6 +5595,10 @@
       </c>
       <c r="G117" t="n">
         <v>60</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>1.9802</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4524,6 +5623,7 @@
       <c r="D118" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -4531,6 +5631,10 @@
       </c>
       <c r="G118" t="n">
         <v>50</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>1.4546</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4555,6 +5659,7 @@
       <c r="D119" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -4562,6 +5667,10 @@
       </c>
       <c r="G119" t="n">
         <v>40</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>0.0305</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4586,6 +5695,7 @@
       <c r="D120" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -4593,6 +5703,10 @@
       </c>
       <c r="G120" t="n">
         <v>30</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="n">
+        <v>0.4901</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -4617,6 +5731,7 @@
       <c r="D121" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -4624,6 +5739,10 @@
       </c>
       <c r="G121" t="n">
         <v>20</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>0.0049</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -4648,6 +5767,7 @@
       <c r="D122" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -4655,6 +5775,10 @@
       </c>
       <c r="G122" t="n">
         <v>20</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>1.2376</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -4679,6 +5803,7 @@
       <c r="D123" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -4686,6 +5811,10 @@
       </c>
       <c r="G123" t="n">
         <v>20</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>0.7426</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -4710,6 +5839,7 @@
       <c r="D124" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -4717,6 +5847,10 @@
       </c>
       <c r="G124" t="n">
         <v>24.3901</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>0.4951</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -4741,6 +5875,7 @@
       <c r="D125" t="n">
         <v>3186.8556</v>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -4748,6 +5883,10 @@
       </c>
       <c r="G125" t="n">
         <v>11.7886</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>0.3699</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -4772,6 +5911,7 @@
       <c r="D126" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -4779,6 +5919,12 @@
       </c>
       <c r="G126" t="n">
         <v>9236.4177</v>
+      </c>
+      <c r="H126" t="n">
+        <v>900</v>
+      </c>
+      <c r="I126" t="n">
+        <v>45.59</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -4803,6 +5949,7 @@
       <c r="D127" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>周金清</t>
@@ -4810,6 +5957,12 @@
       </c>
       <c r="G127" t="n">
         <v>3220</v>
+      </c>
+      <c r="H127" t="n">
+        <v>280</v>
+      </c>
+      <c r="I127" t="n">
+        <v>10.1793</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -4834,6 +5987,7 @@
       <c r="D128" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -4841,6 +5995,12 @@
       </c>
       <c r="G128" t="n">
         <v>3102</v>
+      </c>
+      <c r="H128" t="n">
+        <v>248</v>
+      </c>
+      <c r="I128" t="n">
+        <v>9.815799999999999</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -4865,6 +6025,7 @@
       <c r="D129" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>陆民</t>
@@ -4872,6 +6033,12 @@
       </c>
       <c r="G129" t="n">
         <v>2960</v>
+      </c>
+      <c r="H129" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="I129" t="n">
+        <v>9.357699999999999</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -4896,6 +6063,7 @@
       <c r="D130" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -4904,6 +6072,8 @@
       <c r="G130" t="n">
         <v>2875</v>
       </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
@@ -4927,6 +6097,7 @@
       <c r="D131" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -4934,6 +6105,12 @@
       </c>
       <c r="G131" t="n">
         <v>2015</v>
+      </c>
+      <c r="H131" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="I131" t="n">
+        <v>6.3689</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -4958,6 +6135,7 @@
       <c r="D132" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>苏州贤达</t>
@@ -4965,6 +6143,12 @@
       </c>
       <c r="G132" t="n">
         <v>1542</v>
+      </c>
+      <c r="H132" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="I132" t="n">
+        <v>4.877</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -4989,6 +6173,7 @@
       <c r="D133" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -4996,6 +6181,12 @@
       </c>
       <c r="G133" t="n">
         <v>1322</v>
+      </c>
+      <c r="H133" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="I133" t="n">
+        <v>4.1786</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -5020,6 +6211,7 @@
       <c r="D134" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5027,6 +6219,12 @@
       </c>
       <c r="G134" t="n">
         <v>1216</v>
+      </c>
+      <c r="H134" t="n">
+        <v>89.0431</v>
+      </c>
+      <c r="I134" t="n">
+        <v>4.5939</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -5051,6 +6249,7 @@
       <c r="D135" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>苏州敦行</t>
@@ -5058,6 +6257,12 @@
       </c>
       <c r="G135" t="n">
         <v>1125</v>
+      </c>
+      <c r="H135" t="n">
+        <v>40</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.4542</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -5082,6 +6287,7 @@
       <c r="D136" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>骏耀投资</t>
@@ -5089,6 +6295,12 @@
       </c>
       <c r="G136" t="n">
         <v>1095</v>
+      </c>
+      <c r="H136" t="n">
+        <v>20</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.7271</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -5113,6 +6325,7 @@
       <c r="D137" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -5120,6 +6333,12 @@
       </c>
       <c r="G137" t="n">
         <v>1095</v>
+      </c>
+      <c r="H137" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.1021</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -5144,6 +6363,7 @@
       <c r="D138" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
@@ -5151,6 +6371,12 @@
       </c>
       <c r="G138" t="n">
         <v>798</v>
+      </c>
+      <c r="H138" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="I138" t="n">
+        <v>2.5259</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -5175,6 +6401,7 @@
       <c r="D139" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>海佳同康</t>
@@ -5182,6 +6409,12 @@
       </c>
       <c r="G139" t="n">
         <v>547</v>
+      </c>
+      <c r="H139" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1.7232</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -5206,6 +6439,7 @@
       <c r="D140" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -5213,6 +6447,12 @@
       </c>
       <c r="G140" t="n">
         <v>140</v>
+      </c>
+      <c r="H140" t="n">
+        <v>12</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.4364</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -5237,6 +6477,7 @@
       <c r="D141" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>朱勤华</t>
@@ -5244,6 +6485,12 @@
       </c>
       <c r="G141" t="n">
         <v>304</v>
+      </c>
+      <c r="H141" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.7056</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -5268,6 +6515,7 @@
       <c r="D142" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -5275,6 +6523,12 @@
       </c>
       <c r="G142" t="n">
         <v>304</v>
+      </c>
+      <c r="H142" t="n">
+        <v>45.7143</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.1092</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -5299,6 +6553,7 @@
       <c r="D143" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -5306,6 +6561,12 @@
       </c>
       <c r="G143" t="n">
         <v>407</v>
+      </c>
+      <c r="H143" t="n">
+        <v>31.4286</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.0751</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -5330,6 +6591,7 @@
       <c r="D144" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5337,6 +6599,10 @@
       </c>
       <c r="G144" t="n">
         <v>1520</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="n">
+        <v>4.9505</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -5361,6 +6627,7 @@
       <c r="D145" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -5368,6 +6635,10 @@
       </c>
       <c r="G145" t="n">
         <v>1216</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="n">
+        <v>1.9802</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -5392,6 +6663,7 @@
       <c r="D146" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -5399,6 +6671,10 @@
       </c>
       <c r="G146" t="n">
         <v>912</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="n">
+        <v>1.9802</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -5423,6 +6699,7 @@
       <c r="D147" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -5430,6 +6707,10 @@
       </c>
       <c r="G147" t="n">
         <v>760</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="n">
+        <v>1.4546</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -5454,6 +6735,7 @@
       <c r="D148" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -5461,6 +6743,10 @@
       </c>
       <c r="G148" t="n">
         <v>608</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="n">
+        <v>0.0305</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -5485,6 +6771,7 @@
       <c r="D149" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -5492,6 +6779,10 @@
       </c>
       <c r="G149" t="n">
         <v>456</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="n">
+        <v>0.4901</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -5516,6 +6807,7 @@
       <c r="D150" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -5523,6 +6815,10 @@
       </c>
       <c r="G150" t="n">
         <v>304</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="n">
+        <v>0.0049</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -5547,6 +6843,7 @@
       <c r="D151" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -5554,6 +6851,10 @@
       </c>
       <c r="G151" t="n">
         <v>304</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="n">
+        <v>1.2376</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -5578,6 +6879,7 @@
       <c r="D152" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -5585,6 +6887,10 @@
       </c>
       <c r="G152" t="n">
         <v>304</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="n">
+        <v>0.7426</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -5609,6 +6915,7 @@
       <c r="D153" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -5616,6 +6923,10 @@
       </c>
       <c r="G153" t="n">
         <v>370.8394</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="n">
+        <v>0.4951</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -5640,6 +6951,7 @@
       <c r="D154" t="n">
         <v>36648.8394</v>
       </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>聚贝投资</t>
@@ -5647,6 +6959,10 @@
       </c>
       <c r="G154" t="n">
         <v>179</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="n">
+        <v>0.3699</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -5671,6 +6987,7 @@
       <c r="D155" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>黄学英</t>
@@ -5678,6 +6995,9 @@
       </c>
       <c r="G155" t="n">
         <v>803.1668</v>
+      </c>
+      <c r="H155" t="n">
+        <v>900</v>
       </c>
       <c r="I155" t="n">
         <v>25.2961</v>
@@ -5705,12 +7025,16 @@
       <c r="D156" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>周金清</t>
         </is>
       </c>
       <c r="G156" t="n">
+        <v>280</v>
+      </c>
+      <c r="H156" t="n">
         <v>280</v>
       </c>
       <c r="I156" t="n">
@@ -5739,6 +7063,7 @@
       <c r="D157" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>高新同华</t>
@@ -5746,6 +7071,9 @@
       </c>
       <c r="G157" t="n">
         <v>270</v>
+      </c>
+      <c r="H157" t="n">
+        <v>248</v>
       </c>
       <c r="I157" t="n">
         <v>8.5038</v>
@@ -5773,12 +7101,16 @@
       <c r="D158" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>陆民</t>
         </is>
       </c>
       <c r="G158" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="H158" t="n">
         <v>257.4</v>
       </c>
       <c r="I158" t="n">
@@ -5807,6 +7139,7 @@
       <c r="D159" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>国寿疌泉</t>
@@ -5815,6 +7148,7 @@
       <c r="G159" t="n">
         <v>250.0615</v>
       </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
         <v>7.8758</v>
       </c>
@@ -5841,6 +7175,7 @@
       <c r="D160" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>华泰大健康一号</t>
@@ -5848,6 +7183,9 @@
       </c>
       <c r="G160" t="n">
         <v>175.1887</v>
+      </c>
+      <c r="H160" t="n">
+        <v>175.19</v>
       </c>
       <c r="I160" t="n">
         <v>5.5176</v>
@@ -5875,6 +7213,7 @@
       <c r="D161" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>源峰磐赛</t>
@@ -5883,6 +7222,7 @@
       <c r="G161" t="n">
         <v>157.1815</v>
       </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
         <v>4.9505</v>
       </c>
@@ -5909,12 +7249,16 @@
       <c r="D162" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>苏州贤达</t>
         </is>
       </c>
       <c r="G162" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="H162" t="n">
         <v>134.15</v>
       </c>
       <c r="I162" t="n">
@@ -5943,6 +7287,7 @@
       <c r="D163" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>复星惟盈</t>
@@ -5950,6 +7295,9 @@
       </c>
       <c r="G163" t="n">
         <v>126.3621</v>
+      </c>
+      <c r="H163" t="n">
+        <v>89.0431</v>
       </c>
       <c r="I163" t="n">
         <v>3.9798</v>
@@ -5977,6 +7325,7 @@
       <c r="D164" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>苏州博达</t>
@@ -5984,6 +7333,9 @@
       </c>
       <c r="G164" t="n">
         <v>114.9389</v>
+      </c>
+      <c r="H164" t="n">
+        <v>114.94</v>
       </c>
       <c r="I164" t="n">
         <v>3.62</v>
@@ -6011,12 +7363,16 @@
       <c r="D165" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>苏州杰贤</t>
         </is>
       </c>
       <c r="G165" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="H165" t="n">
         <v>69.48</v>
       </c>
       <c r="I165" t="n">
@@ -6045,6 +7401,7 @@
       <c r="D166" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>潘鼎</t>
@@ -6052,6 +7409,9 @@
       </c>
       <c r="G166" t="n">
         <v>63.2</v>
+      </c>
+      <c r="H166" t="n">
+        <v>50</v>
       </c>
       <c r="I166" t="n">
         <v>1.9905</v>
@@ -6079,6 +7439,7 @@
       <c r="D167" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>珠海峦恒</t>
@@ -6087,6 +7448,7 @@
       <c r="G167" t="n">
         <v>62.8726</v>
       </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
         <v>1.9802</v>
       </c>
@@ -6113,6 +7475,7 @@
       <c r="D168" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>高瓴祈睿</t>
@@ -6121,6 +7484,7 @@
       <c r="G168" t="n">
         <v>62.8726</v>
       </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
         <v>1.9802</v>
       </c>
@@ -6147,12 +7511,16 @@
       <c r="D169" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>海佳同康</t>
         </is>
       </c>
       <c r="G169" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H169" t="n">
         <v>47.4</v>
       </c>
       <c r="I169" t="n">
@@ -6181,6 +7549,7 @@
       <c r="D170" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>国药中生</t>
@@ -6189,6 +7558,7 @@
       <c r="G170" t="n">
         <v>46.1846</v>
       </c>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
         <v>1.4546</v>
       </c>
@@ -6215,12 +7585,16 @@
       <c r="D171" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>苏州敦行</t>
         </is>
       </c>
       <c r="G171" t="n">
+        <v>40</v>
+      </c>
+      <c r="H171" t="n">
         <v>40</v>
       </c>
       <c r="I171" t="n">
@@ -6249,6 +7623,7 @@
       <c r="D172" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>夏尔巴二期</t>
@@ -6257,6 +7632,7 @@
       <c r="G172" t="n">
         <v>39.2954</v>
       </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
         <v>1.2376</v>
       </c>
@@ -6283,12 +7659,16 @@
       <c r="D173" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>陈志华</t>
         </is>
       </c>
       <c r="G173" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="H173" t="n">
         <v>30.04</v>
       </c>
       <c r="I173" t="n">
@@ -6317,12 +7697,16 @@
       <c r="D174" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>耿卫东</t>
         </is>
       </c>
       <c r="G174" t="n">
+        <v>30</v>
+      </c>
+      <c r="H174" t="n">
         <v>30</v>
       </c>
       <c r="I174" t="n">
@@ -6351,6 +7735,7 @@
       <c r="D175" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>甘李药业</t>
@@ -6359,6 +7744,7 @@
       <c r="G175" t="n">
         <v>23.5772</v>
       </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0.7426</v>
       </c>
@@ -6385,12 +7771,16 @@
       <c r="D176" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>骏耀投资</t>
         </is>
       </c>
       <c r="G176" t="n">
+        <v>20</v>
+      </c>
+      <c r="H176" t="n">
         <v>20</v>
       </c>
       <c r="I176" t="n">
@@ -6419,12 +7809,16 @@
       <c r="D177" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>朱勤华</t>
         </is>
       </c>
       <c r="G177" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="H177" t="n">
         <v>19.4081</v>
       </c>
       <c r="I177" t="n">
@@ -6453,6 +7847,7 @@
       <c r="D178" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>吴征涛</t>
@@ -6461,6 +7856,7 @@
       <c r="G178" t="n">
         <v>15.7182</v>
       </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0.4951</v>
       </c>
@@ -6487,6 +7883,7 @@
       <c r="D179" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>国药二期</t>
@@ -6495,6 +7892,7 @@
       <c r="G179" t="n">
         <v>15.5625</v>
       </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
         <v>0.4901</v>
       </c>
@@ -6521,6 +7919,7 @@
       <c r="D180" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>华泰大健康二号</t>
@@ -6528,6 +7927,9 @@
       </c>
       <c r="G180" t="n">
         <v>12.0034</v>
+      </c>
+      <c r="H180" t="n">
+        <v>12</v>
       </c>
       <c r="I180" t="n">
         <v>0.3781</v>
@@ -6555,6 +7957,7 @@
       <c r="D181" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>唐斌</t>
@@ -6562,6 +7965,9 @@
       </c>
       <c r="G181" t="n">
         <v>3.0041</v>
+      </c>
+      <c r="H181" t="n">
+        <v>45.7143</v>
       </c>
       <c r="I181" t="n">
         <v>0.0946</v>
@@ -6589,6 +7995,7 @@
       <c r="D182" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>道兴投资</t>
@@ -6596,6 +8003,9 @@
       </c>
       <c r="G182" t="n">
         <v>2.8079</v>
+      </c>
+      <c r="H182" t="n">
+        <v>2.81</v>
       </c>
       <c r="I182" t="n">
         <v>0.08840000000000001</v>
@@ -6623,6 +8033,7 @@
       <c r="D183" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>张敏</t>
@@ -6630,6 +8041,9 @@
       </c>
       <c r="G183" t="n">
         <v>2.0654</v>
+      </c>
+      <c r="H183" t="n">
+        <v>31.4286</v>
       </c>
       <c r="I183" t="n">
         <v>0.06510000000000001</v>
@@ -6657,6 +8071,7 @@
       <c r="D184" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>圣成投资</t>
@@ -6665,6 +8080,7 @@
       <c r="G184" t="n">
         <v>0.9699</v>
       </c>
+      <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
         <v>0.0305</v>
       </c>
@@ -6691,6 +8107,7 @@
       <c r="D185" t="n">
         <v>3175.067</v>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>圣祁投资</t>
@@ -6699,5716 +8116,13 @@
       <c r="G185" t="n">
         <v>0.1556</v>
       </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.0049</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J152"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PDF页码</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东/认购方</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额(万股)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>15条,字段完整</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>184条,t0存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2408</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6158.9225</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-3446.4699</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2712.4526</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6463.3751</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3156.8427</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-3306.5324</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3156.8427</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6907.7652</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3168.6313</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-3739.1339</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3168.6313</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6919.5538</v>
-      </c>
-      <c r="G9" t="n">
-        <v>40237.2571</v>
-      </c>
-      <c r="H9" t="n">
-        <v>33317.7033</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>40237.2571</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F10" t="n">
-        <v>43988.1796</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3175.067</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-40813.1126</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>322</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>322</v>
-      </c>
-      <c r="G13" t="n">
-        <v>322</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H14" t="n">
-        <v>20</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="G15" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-3535.0134</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>80</v>
-      </c>
-      <c r="H16" t="n">
-        <v>80</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H17" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>20</v>
-      </c>
-      <c r="H18" t="n">
-        <v>20</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>36</v>
-      </c>
-      <c r="G19" t="n">
-        <v>36</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>87</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>87</v>
-      </c>
-      <c r="G20" t="n">
-        <v>87</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>74</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>74</v>
-      </c>
-      <c r="G21" t="n">
-        <v>74</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G23" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>72</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>72</v>
-      </c>
-      <c r="G24" t="n">
-        <v>72</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>72</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>72</v>
-      </c>
-      <c r="G26" t="n">
-        <v>72</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>220</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>220</v>
-      </c>
-      <c r="G27" t="n">
-        <v>220</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1035</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1035</v>
-      </c>
-      <c r="G28" t="n">
-        <v>976.7757</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-58.2243</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>322</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>322</v>
-      </c>
-      <c r="G31" t="n">
-        <v>322</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>20</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>20</v>
-      </c>
-      <c r="G32" t="n">
-        <v>20</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F33" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G33" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>80</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>80</v>
-      </c>
-      <c r="G34" t="n">
-        <v>80</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G35" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>20</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>20</v>
-      </c>
-      <c r="G36" t="n">
-        <v>20</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>36</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>36</v>
-      </c>
-      <c r="G37" t="n">
-        <v>36</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>87</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>87</v>
-      </c>
-      <c r="G38" t="n">
-        <v>87</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>74</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>74</v>
-      </c>
-      <c r="G39" t="n">
-        <v>74</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G40" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G41" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>72</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>72</v>
-      </c>
-      <c r="G42" t="n">
-        <v>72</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G43" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>72</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>72</v>
-      </c>
-      <c r="G44" t="n">
-        <v>72</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>220</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>220</v>
-      </c>
-      <c r="G45" t="n">
-        <v>242</v>
-      </c>
-      <c r="H45" t="n">
-        <v>22</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>976.7757</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>976.7757</v>
-      </c>
-      <c r="G46" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G47" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G48" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>322</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>322</v>
-      </c>
-      <c r="G49" t="n">
-        <v>322</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>20</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>20</v>
-      </c>
-      <c r="G50" t="n">
-        <v>20</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G51" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>80</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>80</v>
-      </c>
-      <c r="G52" t="n">
-        <v>80</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G53" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>20</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>20</v>
-      </c>
-      <c r="G54" t="n">
-        <v>20</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>36</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>36</v>
-      </c>
-      <c r="G55" t="n">
-        <v>36</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>87</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>87</v>
-      </c>
-      <c r="G56" t="n">
-        <v>87</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>74</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>74</v>
-      </c>
-      <c r="G57" t="n">
-        <v>74</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>苏州杰贤</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G58" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G59" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>道兴投资</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>72</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>72</v>
-      </c>
-      <c r="G60" t="n">
-        <v>72</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>骏耀投资</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>72</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>72</v>
-      </c>
-      <c r="G62" t="n">
-        <v>72</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>242</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>242</v>
-      </c>
-      <c r="G63" t="n">
-        <v>242</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="G64" t="n">
-        <v>954.7757</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G66" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="H67" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>322</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>322</v>
-      </c>
-      <c r="G68" t="n">
-        <v>322</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>20</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>20</v>
-      </c>
-      <c r="G69" t="n">
-        <v>20</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E70" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F70" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G70" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>50</v>
-      </c>
-      <c r="H71" t="n">
-        <v>50</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>30</v>
-      </c>
-      <c r="H72" t="n">
-        <v>30</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>40</v>
-      </c>
-      <c r="H73" t="n">
-        <v>40</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>20</v>
-      </c>
-      <c r="H74" t="n">
-        <v>20</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>80</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>80</v>
-      </c>
-      <c r="G75" t="n">
-        <v>80</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>20</v>
-      </c>
-      <c r="H76" t="n">
-        <v>20</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G77" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>20</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>20</v>
-      </c>
-      <c r="G78" t="n">
-        <v>20</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>36</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>36</v>
-      </c>
-      <c r="G79" t="n">
-        <v>36</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>100</v>
-      </c>
-      <c r="H80" t="n">
-        <v>100</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>80</v>
-      </c>
-      <c r="H81" t="n">
-        <v>80</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>20</v>
-      </c>
-      <c r="H82" t="n">
-        <v>20</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>87</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>87</v>
-      </c>
-      <c r="G83" t="n">
-        <v>87</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>苏州敦行</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>74</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>74</v>
-      </c>
-      <c r="G84" t="n">
-        <v>74</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G85" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G86" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="G87" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>322</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>322</v>
-      </c>
-      <c r="G88" t="n">
-        <v>322</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>20</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>20</v>
-      </c>
-      <c r="G89" t="n">
-        <v>20</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E90" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F90" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G90" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-3750.9225</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>50</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>50</v>
-      </c>
-      <c r="G91" t="n">
-        <v>50</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>30</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>30</v>
-      </c>
-      <c r="G92" t="n">
-        <v>30</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>40</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>40</v>
-      </c>
-      <c r="G93" t="n">
-        <v>40</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>20</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>20</v>
-      </c>
-      <c r="G94" t="n">
-        <v>20</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>80</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>80</v>
-      </c>
-      <c r="G95" t="n">
-        <v>80</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>20</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>20</v>
-      </c>
-      <c r="G96" t="n">
-        <v>20</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G97" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>20</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>20</v>
-      </c>
-      <c r="G98" t="n">
-        <v>20</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>36</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>36</v>
-      </c>
-      <c r="G99" t="n">
-        <v>36</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>100</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>100</v>
-      </c>
-      <c r="G100" t="n">
-        <v>100</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>80</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>80</v>
-      </c>
-      <c r="G101" t="n">
-        <v>80</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>20</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>20</v>
-      </c>
-      <c r="G102" t="n">
-        <v>20</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>聚贝投资</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="n">
-        <v>11.7886</v>
-      </c>
-      <c r="H103" t="n">
-        <v>11.7886</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>87</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>87</v>
-      </c>
-      <c r="G104" t="n">
-        <v>87</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G105" t="n">
-        <v>2015</v>
-      </c>
-      <c r="H105" t="n">
-        <v>1882.5</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G106" t="n">
-        <v>140</v>
-      </c>
-      <c r="H106" t="n">
-        <v>130.8</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>24.3901</v>
-      </c>
-      <c r="G107" t="n">
-        <v>370.8394</v>
-      </c>
-      <c r="H107" t="n">
-        <v>346.4493</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>322</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>322</v>
-      </c>
-      <c r="G108" t="n">
-        <v>3220</v>
-      </c>
-      <c r="H108" t="n">
-        <v>2898</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>20</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>20</v>
-      </c>
-      <c r="G109" t="n">
-        <v>304</v>
-      </c>
-      <c r="H109" t="n">
-        <v>284</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>215.9091</v>
-      </c>
-      <c r="E110" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F110" t="n">
-        <v>3966.8316</v>
-      </c>
-      <c r="G110" t="n">
-        <v>2875</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-1091.8316</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>50</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>50</v>
-      </c>
-      <c r="G111" t="n">
-        <v>760</v>
-      </c>
-      <c r="H111" t="n">
-        <v>710</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>30</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>30</v>
-      </c>
-      <c r="G112" t="n">
-        <v>456</v>
-      </c>
-      <c r="H112" t="n">
-        <v>426</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>40</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>40</v>
-      </c>
-      <c r="G113" t="n">
-        <v>608</v>
-      </c>
-      <c r="H113" t="n">
-        <v>568</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>20</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>20</v>
-      </c>
-      <c r="G114" t="n">
-        <v>304</v>
-      </c>
-      <c r="H114" t="n">
-        <v>284</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>80</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>80</v>
-      </c>
-      <c r="G115" t="n">
-        <v>1216</v>
-      </c>
-      <c r="H115" t="n">
-        <v>1136</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>20</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>20</v>
-      </c>
-      <c r="G116" t="n">
-        <v>304</v>
-      </c>
-      <c r="H116" t="n">
-        <v>284</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="E117" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" t="n">
-        <v>26.7678</v>
-      </c>
-      <c r="G117" t="n">
-        <v>407</v>
-      </c>
-      <c r="H117" t="n">
-        <v>380.2322</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>20</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>20</v>
-      </c>
-      <c r="G118" t="n">
-        <v>304</v>
-      </c>
-      <c r="H118" t="n">
-        <v>284</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>36</v>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="n">
-        <v>36</v>
-      </c>
-      <c r="G119" t="n">
-        <v>547</v>
-      </c>
-      <c r="H119" t="n">
-        <v>511</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>100</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>100</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1520</v>
-      </c>
-      <c r="H120" t="n">
-        <v>1420</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>80</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>80</v>
-      </c>
-      <c r="G121" t="n">
-        <v>1216</v>
-      </c>
-      <c r="H121" t="n">
-        <v>1136</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>20</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="n">
-        <v>20</v>
-      </c>
-      <c r="G122" t="n">
-        <v>304</v>
-      </c>
-      <c r="H122" t="n">
-        <v>284</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>聚贝投资</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.7886</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" t="n">
-        <v>11.7886</v>
-      </c>
-      <c r="G123" t="n">
-        <v>179</v>
-      </c>
-      <c r="H123" t="n">
-        <v>167.2114</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>苏州博达</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>87</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>87</v>
-      </c>
-      <c r="G124" t="n">
-        <v>1322</v>
-      </c>
-      <c r="H124" t="n">
-        <v>1235</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>t5-&gt;t6</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>2015</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>2015</v>
-      </c>
-      <c r="G125" t="n">
-        <v>175.1887</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-1839.8113</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>华泰大健康二号</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>140</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>140</v>
-      </c>
-      <c r="G126" t="n">
-        <v>12.0034</v>
-      </c>
-      <c r="H126" t="n">
-        <v>-127.9966</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>370.8394</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" t="n">
-        <v>370.8394</v>
-      </c>
-      <c r="G127" t="n">
-        <v>15.7182</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-355.1212</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>3220</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>3220</v>
-      </c>
-      <c r="G128" t="n">
-        <v>280</v>
-      </c>
-      <c r="H128" t="n">
-        <v>-2940</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>唐斌</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>304</v>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>304</v>
-      </c>
-      <c r="G129" t="n">
-        <v>3.0041</v>
-      </c>
-      <c r="H129" t="n">
-        <v>-300.9959</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>2875</v>
-      </c>
-      <c r="E130" t="n">
-        <v>3750.9225</v>
-      </c>
-      <c r="F130" t="n">
-        <v>6625.9225</v>
-      </c>
-      <c r="G130" t="n">
-        <v>250.0615</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-6375.861</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>760</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" t="n">
-        <v>760</v>
-      </c>
-      <c r="G131" t="n">
-        <v>46.1846</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-713.8154</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>456</v>
-      </c>
-      <c r="E132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" t="n">
-        <v>456</v>
-      </c>
-      <c r="G132" t="n">
-        <v>15.5625</v>
-      </c>
-      <c r="H132" t="n">
-        <v>-440.4375</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>608</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>608</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0.9699</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-607.0300999999999</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>304</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="n">
-        <v>304</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0.1556</v>
-      </c>
-      <c r="H134" t="n">
-        <v>-303.8444</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>1216</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>1216</v>
-      </c>
-      <c r="G135" t="n">
-        <v>126.3621</v>
-      </c>
-      <c r="H135" t="n">
-        <v>-1089.6379</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>304</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" t="n">
-        <v>304</v>
-      </c>
-      <c r="G136" t="n">
-        <v>39.2954</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-264.7046</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>张敏</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>407</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" t="n">
-        <v>407</v>
-      </c>
-      <c r="G137" t="n">
-        <v>2.0654</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-404.9346</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>朱勤华</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>304</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="n">
-        <v>304</v>
-      </c>
-      <c r="G138" t="n">
-        <v>19.4081</v>
-      </c>
-      <c r="H138" t="n">
-        <v>-284.5919</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>海佳同康</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>547</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" t="n">
-        <v>547</v>
-      </c>
-      <c r="G139" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-499.6</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>1520</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" t="n">
-        <v>1520</v>
-      </c>
-      <c r="G140" t="n">
-        <v>157.1815</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-1362.8185</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>潘鼎</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="H141" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>1216</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" t="n">
-        <v>1216</v>
-      </c>
-      <c r="G142" t="n">
-        <v>62.8726</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-1153.1274</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>304</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" t="n">
-        <v>304</v>
-      </c>
-      <c r="G143" t="n">
-        <v>23.5772</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-280.4228</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>耿卫东</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="n">
-        <v>30</v>
-      </c>
-      <c r="H144" t="n">
-        <v>30</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>t6-&gt;发行前（第59页股东表）</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>13股东</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>t0比例合计97.34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>18股东</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>t1比例合计102.82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>18股东</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>t2比例合计102.82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>18股东</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>t3比例合计102.82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>28股东</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>t4比例合计116.19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>29股东</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>t5比例合计116.56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>29股东</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>t6比例合计116.56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>31股东</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>发行前（第59页股东表）比例合计100.00%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
+++ b/outputs/week2_excel/688758_赛分科技_三表抽取.xlsx
@@ -474,10 +474,12 @@
       <c r="E2" t="n">
         <v>13500</v>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -501,10 +503,12 @@
       <c r="E3" t="n">
         <v>13500</v>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -528,10 +532,12 @@
       <c r="E4" t="n">
         <v>13500</v>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -555,10 +561,12 @@
       <c r="E5" t="n">
         <v>13500</v>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -582,10 +590,12 @@
       <c r="E6" t="n">
         <v>13500</v>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -609,10 +619,12 @@
       <c r="E7" t="n">
         <v>13500</v>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -636,10 +648,12 @@
       <c r="E8" t="n">
         <v>13500</v>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -663,10 +677,12 @@
       <c r="E9" t="n">
         <v>13500</v>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -690,10 +706,12 @@
       <c r="E10" t="n">
         <v>13500</v>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -717,10 +735,12 @@
       <c r="E11" t="n">
         <v>13500</v>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -744,10 +764,12 @@
       <c r="E12" t="n">
         <v>13500</v>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -771,10 +793,12 @@
       <c r="E13" t="n">
         <v>13500</v>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -798,10 +822,12 @@
       <c r="E14" t="n">
         <v>13500</v>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -825,10 +851,12 @@
       <c r="E15" t="n">
         <v>13500</v>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
@@ -852,10 +880,12 @@
       <c r="E16" t="n">
         <v>13500</v>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>53.98</v>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。 [表格数据, 认购价格=18500万/342.6769万=53.98元/注册资本]</t>
         </is>
       </c>
     </row>
